--- a/excel_reports/backtest_compare/s10/compare_s10_H1_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s10/compare_s10_H1_20260528_0800_20260608_1000.xlsx
@@ -16,10 +16,10 @@
     <sheet name="Gap Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$28</definedName>
   </definedNames>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:24:25</t>
+          <t>2026-06-18 17:24:20</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK25"/>
+  <dimension ref="A1:BK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>46174.26783564815</v>
+        <v>46174.30950231481</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>4543.72</v>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="AO2" s="8" t="inlineStr">
         <is>
-          <t>LOOSE</t>
+          <t>NEAR</t>
         </is>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>379.74</v>
+        <v>220.74</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>37.95</v>
+        <v>22.05</v>
       </c>
       <c r="AR2" s="8" t="n">
         <v>0.24</v>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>46170.40681712963</v>
+        <v>46170.4484837963</v>
       </c>
       <c r="F3" s="10" t="n">
         <v>4401.5975</v>
@@ -1397,10 +1397,10 @@
       <c r="AZ3" s="10" t="inlineStr"/>
       <c r="BA3" s="10" t="inlineStr"/>
       <c r="BB3" s="11" t="n">
-        <v>46174.62569444445</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="BC3" s="10" t="n">
-        <v>4501.34</v>
+        <v>4494.38</v>
       </c>
       <c r="BD3" s="10" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="BE3" s="10" t="n">
-        <v>6098.12</v>
+        <v>6042.12</v>
       </c>
       <c r="BF3" s="10" t="n">
-        <v>100.3</v>
+        <v>93.34</v>
       </c>
       <c r="BG3" s="10" t="inlineStr"/>
       <c r="BH3" s="10" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>46170.80662037037</v>
+        <v>46170.84828703704</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>4385.587500000001</v>
@@ -1519,7 +1519,7 @@
         <v>46171.04236111111</v>
       </c>
       <c r="BC4" s="10" t="n">
-        <v>4508.41</v>
+        <v>4505.02</v>
       </c>
       <c r="BD4" s="10" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="BE4" s="10" t="n">
-        <v>344.87</v>
+        <v>284.87</v>
       </c>
       <c r="BF4" s="10" t="n">
-        <v>117.17</v>
+        <v>113.78</v>
       </c>
       <c r="BG4" s="10" t="inlineStr"/>
       <c r="BH4" s="10" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>4540.52</v>
@@ -1635,10 +1635,10 @@
       <c r="AZ5" s="10" t="inlineStr"/>
       <c r="BA5" s="10" t="inlineStr"/>
       <c r="BB5" s="11" t="n">
-        <v>46174.62569444445</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="BC5" s="10" t="n">
-        <v>4501.34</v>
+        <v>4494.38</v>
       </c>
       <c r="BD5" s="10" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="BE5" s="10" t="n">
-        <v>3544.43</v>
+        <v>3488.43</v>
       </c>
       <c r="BF5" s="10" t="n">
-        <v>40.62</v>
+        <v>47.58</v>
       </c>
       <c r="BG5" s="10" t="inlineStr"/>
       <c r="BH5" s="10" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>46178.3515162037</v>
+        <v>46178.39318287037</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>4450.29</v>
@@ -1754,10 +1754,10 @@
       <c r="AZ6" s="10" t="inlineStr"/>
       <c r="BA6" s="10" t="inlineStr"/>
       <c r="BB6" s="11" t="n">
-        <v>46178.33402777778</v>
+        <v>46178.37361111111</v>
       </c>
       <c r="BC6" s="10" t="n">
-        <v>4463.91</v>
+        <v>4464.44</v>
       </c>
       <c r="BD6" s="10" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="BE6" s="10" t="n">
-        <v>24.42</v>
+        <v>27.42</v>
       </c>
       <c r="BF6" s="10" t="n">
-        <v>10.91</v>
+        <v>11.44</v>
       </c>
       <c r="BG6" s="10" t="inlineStr"/>
       <c r="BH6" s="10" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46178.35137731482</v>
+        <v>46178.39304398148</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>46178.3515162037</v>
+        <v>46178.39318287037</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>4450.29</v>
@@ -1873,10 +1873,10 @@
       <c r="AZ7" s="10" t="inlineStr"/>
       <c r="BA7" s="10" t="inlineStr"/>
       <c r="BB7" s="11" t="n">
-        <v>46178.33402777778</v>
+        <v>46178.37361111111</v>
       </c>
       <c r="BC7" s="10" t="n">
-        <v>4463.91</v>
+        <v>4464.44</v>
       </c>
       <c r="BD7" s="10" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="BE7" s="10" t="n">
-        <v>24.98</v>
+        <v>27.98</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>11.69</v>
+        <v>12.22</v>
       </c>
       <c r="BG7" s="10" t="inlineStr"/>
       <c r="BH7" s="10" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>46179.13826388889</v>
+        <v>46179.17993055555</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>4315.41</v>
@@ -1992,10 +1992,10 @@
       <c r="AZ8" s="10" t="inlineStr"/>
       <c r="BA8" s="10" t="inlineStr"/>
       <c r="BB8" s="11" t="n">
-        <v>46179.00069444445</v>
+        <v>46179.00208333333</v>
       </c>
       <c r="BC8" s="10" t="n">
-        <v>4343.6</v>
+        <v>4340.18</v>
       </c>
       <c r="BD8" s="10" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="BE8" s="10" t="n">
-        <v>194.03</v>
+        <v>252.03</v>
       </c>
       <c r="BF8" s="10" t="n">
-        <v>28.06</v>
+        <v>24.64</v>
       </c>
       <c r="BG8" s="10" t="inlineStr"/>
       <c r="BH8" s="10" t="inlineStr"/>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>4508.41</v>
+        <v>4505.02</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>-26.72</v>
+        <v>-40.28</v>
       </c>
       <c r="AJ9" s="10" t="inlineStr"/>
       <c r="AK9" s="10" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
       <c r="BE9" s="10" t="inlineStr"/>
       <c r="BF9" s="10" t="inlineStr"/>
       <c r="BG9" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH9" s="10" t="n">
         <v>4391.24</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>344.87</v>
+        <v>284.87</v>
       </c>
       <c r="BK9" s="10" t="n">
-        <v>117.17</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="10">
@@ -2156,13 +2156,13 @@
       <c r="AB10" s="10" t="inlineStr"/>
       <c r="AC10" s="10" t="inlineStr"/>
       <c r="AD10" s="11" t="n">
-        <v>46171.08402777778</v>
+        <v>46171.04791666667</v>
       </c>
       <c r="AE10" s="11" t="n">
-        <v>46171.34305555555</v>
+        <v>46171.3375</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>4515.09</v>
+        <v>4500.15</v>
       </c>
       <c r="AG10" s="10" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="AH10" s="10" t="n">
-        <v>4501.55</v>
+        <v>4505.02</v>
       </c>
       <c r="AI10" s="10" t="n">
-        <v>-54.16</v>
+        <v>19.48</v>
       </c>
       <c r="AJ10" s="10" t="inlineStr"/>
       <c r="AK10" s="10" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       <c r="AM10" s="10" t="inlineStr"/>
       <c r="AN10" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="AO10" s="10" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       <c r="BE10" s="10" t="inlineStr"/>
       <c r="BF10" s="10" t="inlineStr"/>
       <c r="BG10" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH10" s="10" t="n">
         <v>4391.24</v>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="BJ10" s="10" t="n">
-        <v>404.87</v>
+        <v>292.87</v>
       </c>
       <c r="BK10" s="10" t="n">
-        <v>110.31</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="11">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>4494.89</v>
+        <v>4496.55</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>-24.84</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ11" s="10" t="inlineStr"/>
       <c r="AK11" s="10" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
       <c r="BE11" s="10" t="inlineStr"/>
       <c r="BF11" s="10" t="inlineStr"/>
       <c r="BG11" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH11" s="10" t="n">
         <v>4391.24</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="BJ11" s="10" t="n">
-        <v>764.87</v>
+        <v>704.87</v>
       </c>
       <c r="BK11" s="10" t="n">
-        <v>103.65</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="12">
@@ -2362,13 +2362,13 @@
       <c r="AB12" s="10" t="inlineStr"/>
       <c r="AC12" s="10" t="inlineStr"/>
       <c r="AD12" s="11" t="n">
-        <v>46171.75069444445</v>
+        <v>46171.33680555555</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>46171.82083333333</v>
+        <v>46171.3375</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>4513.3</v>
+        <v>4501.1</v>
       </c>
       <c r="AG12" s="10" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>4536.6</v>
+        <v>4496.55</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>93.2</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ12" s="10" t="inlineStr"/>
       <c r="AK12" s="10" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       <c r="AM12" s="10" t="inlineStr"/>
       <c r="AN12" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO12" s="10" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       <c r="BE12" s="10" t="inlineStr"/>
       <c r="BF12" s="10" t="inlineStr"/>
       <c r="BG12" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH12" s="10" t="n">
         <v>4391.24</v>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>1364.87</v>
+        <v>708.87</v>
       </c>
       <c r="BK12" s="10" t="n">
-        <v>145.36</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="13">
@@ -2465,24 +2465,24 @@
       <c r="AB13" s="10" t="inlineStr"/>
       <c r="AC13" s="10" t="inlineStr"/>
       <c r="AD13" s="11" t="n">
-        <v>46174.62569444445</v>
+        <v>46171.35</v>
       </c>
       <c r="AE13" s="11" t="n">
-        <v>46174.63611111111</v>
+        <v>46171.35069444445</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>4491.92</v>
+        <v>4501.1</v>
       </c>
       <c r="AG13" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>4501.34</v>
+        <v>4496.55</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>-37.68</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ13" s="10" t="inlineStr"/>
       <c r="AK13" s="10" t="inlineStr"/>
@@ -2512,21 +2512,21 @@
       <c r="BE13" s="10" t="inlineStr"/>
       <c r="BF13" s="10" t="inlineStr"/>
       <c r="BG13" s="11" t="n">
-        <v>46172.16428240741</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH13" s="10" t="n">
-        <v>4541.96</v>
+        <v>4391.24</v>
       </c>
       <c r="BI13" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[tp 4381.00]</t>
         </is>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>3544.43</v>
+        <v>727.87</v>
       </c>
       <c r="BK13" s="10" t="n">
-        <v>40.62</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="14">
@@ -2568,13 +2568,13 @@
       <c r="AB14" s="10" t="inlineStr"/>
       <c r="AC14" s="10" t="inlineStr"/>
       <c r="AD14" s="11" t="n">
-        <v>46174.79236111111</v>
+        <v>46171.36736111111</v>
       </c>
       <c r="AE14" s="11" t="n">
-        <v>46174.83541666667</v>
+        <v>46171.36805555555</v>
       </c>
       <c r="AF14" s="10" t="n">
-        <v>4496.2</v>
+        <v>4501.1</v>
       </c>
       <c r="AG14" s="10" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>4506.38</v>
+        <v>4496.55</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>40.72</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ14" s="10" t="inlineStr"/>
       <c r="AK14" s="10" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       <c r="AM14" s="10" t="inlineStr"/>
       <c r="AN14" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO14" s="10" t="inlineStr"/>
@@ -2615,21 +2615,21 @@
       <c r="BE14" s="10" t="inlineStr"/>
       <c r="BF14" s="10" t="inlineStr"/>
       <c r="BG14" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH14" s="10" t="n">
-        <v>4541.35</v>
+        <v>4391.24</v>
       </c>
       <c r="BI14" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>[tp 4381.00]</t>
         </is>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>756.95</v>
+        <v>752.87</v>
       </c>
       <c r="BK14" s="10" t="n">
-        <v>34.97</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="15">
@@ -2671,13 +2671,13 @@
       <c r="AB15" s="10" t="inlineStr"/>
       <c r="AC15" s="10" t="inlineStr"/>
       <c r="AD15" s="11" t="n">
-        <v>46175.62569444445</v>
+        <v>46171.75069444445</v>
       </c>
       <c r="AE15" s="11" t="n">
-        <v>46175.82847222222</v>
+        <v>46171.82083333333</v>
       </c>
       <c r="AF15" s="10" t="n">
-        <v>4516.97</v>
+        <v>4513.3</v>
       </c>
       <c r="AG15" s="10" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>4530.94</v>
+        <v>4537.98</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>55.88</v>
+        <v>98.72</v>
       </c>
       <c r="AJ15" s="10" t="inlineStr"/>
       <c r="AK15" s="10" t="inlineStr"/>
@@ -2718,21 +2718,21 @@
       <c r="BE15" s="10" t="inlineStr"/>
       <c r="BF15" s="10" t="inlineStr"/>
       <c r="BG15" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH15" s="10" t="n">
-        <v>4541.35</v>
+        <v>4391.24</v>
       </c>
       <c r="BI15" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>[tp 4381.00]</t>
         </is>
       </c>
       <c r="BJ15" s="10" t="n">
-        <v>1956.95</v>
+        <v>1304.87</v>
       </c>
       <c r="BK15" s="10" t="n">
-        <v>10.41</v>
+        <v>146.74</v>
       </c>
     </row>
     <row r="16">
@@ -2774,13 +2774,13 @@
       <c r="AB16" s="10" t="inlineStr"/>
       <c r="AC16" s="10" t="inlineStr"/>
       <c r="AD16" s="11" t="n">
-        <v>46175.70902777778</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="AE16" s="11" t="n">
-        <v>46175.82430555556</v>
+        <v>46174.63611111111</v>
       </c>
       <c r="AF16" s="10" t="n">
-        <v>4521.52</v>
+        <v>4491.92</v>
       </c>
       <c r="AG16" s="10" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>4530.48</v>
+        <v>4494.38</v>
       </c>
       <c r="AI16" s="10" t="n">
-        <v>-35.84</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ16" s="10" t="inlineStr"/>
       <c r="AK16" s="10" t="inlineStr"/>
@@ -2821,21 +2821,21 @@
       <c r="BE16" s="10" t="inlineStr"/>
       <c r="BF16" s="10" t="inlineStr"/>
       <c r="BG16" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH16" s="10" t="n">
-        <v>4453</v>
+        <v>4541.96</v>
       </c>
       <c r="BI16" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ16" s="10" t="n">
-        <v>3804.42</v>
+        <v>3488.43</v>
       </c>
       <c r="BK16" s="10" t="n">
-        <v>77.48</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="17">
@@ -2877,13 +2877,13 @@
       <c r="AB17" s="10" t="inlineStr"/>
       <c r="AC17" s="10" t="inlineStr"/>
       <c r="AD17" s="11" t="n">
-        <v>46176.08402777778</v>
+        <v>46174.64027777778</v>
       </c>
       <c r="AE17" s="11" t="n">
-        <v>46176.21388888889</v>
+        <v>46174.64097222222</v>
       </c>
       <c r="AF17" s="10" t="n">
-        <v>4493.07</v>
+        <v>4491.92</v>
       </c>
       <c r="AG17" s="10" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="AH17" s="10" t="n">
-        <v>4489.41</v>
+        <v>4494.38</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>14.64</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ17" s="10" t="inlineStr"/>
       <c r="AK17" s="10" t="inlineStr"/>
@@ -2902,7 +2902,7 @@
       <c r="AM17" s="10" t="inlineStr"/>
       <c r="AN17" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO17" s="10" t="inlineStr"/>
@@ -2924,21 +2924,21 @@
       <c r="BE17" s="10" t="inlineStr"/>
       <c r="BF17" s="10" t="inlineStr"/>
       <c r="BG17" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH17" s="10" t="n">
-        <v>4453</v>
+        <v>4541.96</v>
       </c>
       <c r="BI17" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ17" s="10" t="n">
-        <v>3264.42</v>
+        <v>3505.43</v>
       </c>
       <c r="BK17" s="10" t="n">
-        <v>36.41</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="18">
@@ -2980,13 +2980,13 @@
       <c r="AB18" s="10" t="inlineStr"/>
       <c r="AC18" s="10" t="inlineStr"/>
       <c r="AD18" s="11" t="n">
-        <v>46177.01180555556</v>
+        <v>46174.64513888889</v>
       </c>
       <c r="AE18" s="11" t="n">
-        <v>46177.02083333334</v>
+        <v>46174.68888888889</v>
       </c>
       <c r="AF18" s="10" t="n">
-        <v>4435.71</v>
+        <v>4491.92</v>
       </c>
       <c r="AG18" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="AH18" s="10" t="n">
-        <v>4441.57</v>
+        <v>4494.38</v>
       </c>
       <c r="AI18" s="10" t="n">
-        <v>-23.44</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ18" s="10" t="inlineStr"/>
       <c r="AK18" s="10" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
       <c r="AM18" s="10" t="inlineStr"/>
       <c r="AN18" s="10" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO18" s="10" t="inlineStr"/>
@@ -3027,21 +3027,21 @@
       <c r="BE18" s="10" t="inlineStr"/>
       <c r="BF18" s="10" t="inlineStr"/>
       <c r="BG18" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH18" s="10" t="n">
-        <v>4453</v>
+        <v>4541.96</v>
       </c>
       <c r="BI18" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>1928.42</v>
+        <v>3512.43</v>
       </c>
       <c r="BK18" s="10" t="n">
-        <v>11.43</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="19">
@@ -3083,24 +3083,24 @@
       <c r="AB19" s="10" t="inlineStr"/>
       <c r="AC19" s="10" t="inlineStr"/>
       <c r="AD19" s="11" t="n">
-        <v>46177.25138888889</v>
+        <v>46174.79583333333</v>
       </c>
       <c r="AE19" s="11" t="n">
-        <v>46177.28125</v>
+        <v>46174.83541666667</v>
       </c>
       <c r="AF19" s="10" t="n">
-        <v>4458.37</v>
+        <v>4496.2</v>
       </c>
       <c r="AG19" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH19" s="10" t="n">
-        <v>4447.32</v>
+        <v>4507.83</v>
       </c>
       <c r="AI19" s="10" t="n">
-        <v>44.2</v>
+        <v>46.52</v>
       </c>
       <c r="AJ19" s="10" t="inlineStr"/>
       <c r="AK19" s="10" t="inlineStr"/>
@@ -3130,21 +3130,21 @@
       <c r="BE19" s="10" t="inlineStr"/>
       <c r="BF19" s="10" t="inlineStr"/>
       <c r="BG19" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH19" s="10" t="n">
-        <v>4453</v>
+        <v>4541.35</v>
       </c>
       <c r="BI19" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ19" s="10" t="n">
-        <v>1583.42</v>
+        <v>701.95</v>
       </c>
       <c r="BK19" s="10" t="n">
-        <v>5.68</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="20">
@@ -3186,13 +3186,13 @@
       <c r="AB20" s="10" t="inlineStr"/>
       <c r="AC20" s="10" t="inlineStr"/>
       <c r="AD20" s="11" t="n">
-        <v>46177.33402777778</v>
+        <v>46175.62569444445</v>
       </c>
       <c r="AE20" s="11" t="n">
-        <v>46177.34166666667</v>
+        <v>46175.82847222222</v>
       </c>
       <c r="AF20" s="10" t="n">
-        <v>4465.22</v>
+        <v>4516.97</v>
       </c>
       <c r="AG20" s="10" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="AH20" s="10" t="n">
-        <v>4448.1</v>
+        <v>4530.94</v>
       </c>
       <c r="AI20" s="10" t="n">
-        <v>-68.48</v>
+        <v>55.88</v>
       </c>
       <c r="AJ20" s="10" t="inlineStr"/>
       <c r="AK20" s="10" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AM20" s="10" t="inlineStr"/>
       <c r="AN20" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO20" s="10" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
       <c r="BE20" s="10" t="inlineStr"/>
       <c r="BF20" s="10" t="inlineStr"/>
       <c r="BG20" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH20" s="10" t="n">
         <v>4541.35</v>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="BJ20" s="10" t="n">
-        <v>4416.95</v>
+        <v>1896.95</v>
       </c>
       <c r="BK20" s="10" t="n">
-        <v>93.25</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="21">
@@ -3289,13 +3289,13 @@
       <c r="AB21" s="10" t="inlineStr"/>
       <c r="AC21" s="10" t="inlineStr"/>
       <c r="AD21" s="11" t="n">
-        <v>46177.66736111111</v>
+        <v>46175.72291666667</v>
       </c>
       <c r="AE21" s="11" t="n">
-        <v>46177.7</v>
+        <v>46175.82430555556</v>
       </c>
       <c r="AF21" s="10" t="n">
-        <v>4470.76</v>
+        <v>4521.52</v>
       </c>
       <c r="AG21" s="10" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="AH21" s="10" t="n">
-        <v>4463.7</v>
+        <v>4526.71</v>
       </c>
       <c r="AI21" s="10" t="n">
-        <v>28.24</v>
+        <v>-20.76</v>
       </c>
       <c r="AJ21" s="10" t="inlineStr"/>
       <c r="AK21" s="10" t="inlineStr"/>
@@ -3314,7 +3314,7 @@
       <c r="AM21" s="10" t="inlineStr"/>
       <c r="AN21" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO21" s="10" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       <c r="BE21" s="10" t="inlineStr"/>
       <c r="BF21" s="10" t="inlineStr"/>
       <c r="BG21" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH21" s="10" t="n">
         <v>4453</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="BJ21" s="10" t="n">
-        <v>984.42</v>
+        <v>3844.42</v>
       </c>
       <c r="BK21" s="10" t="n">
-        <v>10.7</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr"/>
@@ -3392,13 +3392,13 @@
       <c r="AB22" s="10" t="inlineStr"/>
       <c r="AC22" s="10" t="inlineStr"/>
       <c r="AD22" s="11" t="n">
-        <v>46178.33402777778</v>
+        <v>46177.01944444444</v>
       </c>
       <c r="AE22" s="11" t="n">
-        <v>46178.35138888889</v>
+        <v>46177.14791666667</v>
       </c>
       <c r="AF22" s="10" t="n">
-        <v>4450.29</v>
+        <v>4433.27</v>
       </c>
       <c r="AG22" s="10" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="AH22" s="10" t="n">
-        <v>4463.91</v>
+        <v>4439.15</v>
       </c>
       <c r="AI22" s="10" t="n">
-        <v>-54.48</v>
+        <v>-23.52</v>
       </c>
       <c r="AJ22" s="10" t="inlineStr"/>
       <c r="AK22" s="10" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
       <c r="BE22" s="10" t="inlineStr"/>
       <c r="BF22" s="10" t="inlineStr"/>
       <c r="BG22" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH22" s="10" t="n">
         <v>4453</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="BJ22" s="10" t="n">
-        <v>24.42</v>
+        <v>1977.42</v>
       </c>
       <c r="BK22" s="10" t="n">
-        <v>10.91</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="23">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr"/>
@@ -3495,24 +3495,24 @@
       <c r="AB23" s="10" t="inlineStr"/>
       <c r="AC23" s="10" t="inlineStr"/>
       <c r="AD23" s="11" t="n">
-        <v>46178.45972222222</v>
+        <v>46177.33402777778</v>
       </c>
       <c r="AE23" s="11" t="n">
-        <v>46178.55208333334</v>
+        <v>46177.34166666667</v>
       </c>
       <c r="AF23" s="10" t="n">
-        <v>4434.75</v>
+        <v>4465.22</v>
       </c>
       <c r="AG23" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH23" s="10" t="n">
-        <v>4442.47</v>
+        <v>4451.86</v>
       </c>
       <c r="AI23" s="10" t="n">
-        <v>-30.88</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ23" s="10" t="inlineStr"/>
       <c r="AK23" s="10" t="inlineStr"/>
@@ -3542,21 +3542,21 @@
       <c r="BE23" s="10" t="inlineStr"/>
       <c r="BF23" s="10" t="inlineStr"/>
       <c r="BG23" s="11" t="n">
-        <v>46178.35137731482</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH23" s="10" t="n">
-        <v>4452.22</v>
+        <v>4541.35</v>
       </c>
       <c r="BI23" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ23" s="10" t="n">
-        <v>156.02</v>
+        <v>4356.95</v>
       </c>
       <c r="BK23" s="10" t="n">
-        <v>9.75</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3598,24 +3598,24 @@
       <c r="AB24" s="10" t="inlineStr"/>
       <c r="AC24" s="10" t="inlineStr"/>
       <c r="AD24" s="11" t="n">
-        <v>46179.00069444445</v>
+        <v>46177.34583333333</v>
       </c>
       <c r="AE24" s="11" t="n">
-        <v>46179.05138888889</v>
+        <v>46177.34722222222</v>
       </c>
       <c r="AF24" s="10" t="n">
-        <v>4322.93</v>
+        <v>4465.22</v>
       </c>
       <c r="AG24" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH24" s="10" t="n">
-        <v>4343.6</v>
+        <v>4451.86</v>
       </c>
       <c r="AI24" s="10" t="n">
-        <v>-82.68000000000001</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ24" s="10" t="inlineStr"/>
       <c r="AK24" s="10" t="inlineStr"/>
@@ -3645,21 +3645,21 @@
       <c r="BE24" s="10" t="inlineStr"/>
       <c r="BF24" s="10" t="inlineStr"/>
       <c r="BG24" s="11" t="n">
-        <v>46179.13543981482</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH24" s="10" t="n">
-        <v>4315.54</v>
+        <v>4541.35</v>
       </c>
       <c r="BI24" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill rou</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ24" s="10" t="n">
-        <v>194.03</v>
+        <v>4373.95</v>
       </c>
       <c r="BK24" s="10" t="n">
-        <v>28.06</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3701,13 +3701,13 @@
       <c r="AB25" s="10" t="inlineStr"/>
       <c r="AC25" s="10" t="inlineStr"/>
       <c r="AD25" s="11" t="n">
-        <v>46181.33402777778</v>
+        <v>46177.35347222222</v>
       </c>
       <c r="AE25" s="11" t="n">
-        <v>46181.34583333333</v>
+        <v>46177.35416666666</v>
       </c>
       <c r="AF25" s="10" t="n">
-        <v>4317.47</v>
+        <v>4465.22</v>
       </c>
       <c r="AG25" s="10" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="AH25" s="10" t="n">
-        <v>4342.78</v>
+        <v>4451.86</v>
       </c>
       <c r="AI25" s="10" t="n">
-        <v>101.24</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ25" s="10" t="inlineStr"/>
       <c r="AK25" s="10" t="inlineStr"/>
@@ -3726,7 +3726,7 @@
       <c r="AM25" s="10" t="inlineStr"/>
       <c r="AN25" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO25" s="10" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
       <c r="BE25" s="10" t="inlineStr"/>
       <c r="BF25" s="10" t="inlineStr"/>
       <c r="BG25" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH25" s="10" t="n">
         <v>4541.35</v>
@@ -3759,14 +3759,838 @@
         </is>
       </c>
       <c r="BJ25" s="10" t="n">
-        <v>10176.95</v>
+        <v>4384.95</v>
       </c>
       <c r="BK25" s="10" t="n">
-        <v>198.57</v>
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr"/>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="inlineStr"/>
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" s="10" t="inlineStr"/>
+      <c r="P26" s="10" t="inlineStr"/>
+      <c r="Q26" s="10" t="inlineStr"/>
+      <c r="R26" s="10" t="inlineStr"/>
+      <c r="S26" s="10" t="inlineStr"/>
+      <c r="T26" s="10" t="inlineStr"/>
+      <c r="U26" s="10" t="inlineStr"/>
+      <c r="V26" s="10" t="inlineStr"/>
+      <c r="W26" s="10" t="inlineStr"/>
+      <c r="X26" s="10" t="inlineStr"/>
+      <c r="Y26" s="10" t="inlineStr"/>
+      <c r="Z26" s="10" t="inlineStr"/>
+      <c r="AA26" s="10" t="inlineStr"/>
+      <c r="AB26" s="10" t="inlineStr"/>
+      <c r="AC26" s="10" t="inlineStr"/>
+      <c r="AD26" s="11" t="n">
+        <v>46177.3625</v>
+      </c>
+      <c r="AE26" s="11" t="n">
+        <v>46177.36597222222</v>
+      </c>
+      <c r="AF26" s="10" t="n">
+        <v>4465.22</v>
+      </c>
+      <c r="AG26" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH26" s="10" t="n">
+        <v>4451.86</v>
+      </c>
+      <c r="AI26" s="10" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AJ26" s="10" t="inlineStr"/>
+      <c r="AK26" s="10" t="inlineStr"/>
+      <c r="AL26" s="10" t="inlineStr"/>
+      <c r="AM26" s="10" t="inlineStr"/>
+      <c r="AN26" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO26" s="10" t="inlineStr"/>
+      <c r="AP26" s="10" t="inlineStr"/>
+      <c r="AQ26" s="10" t="inlineStr"/>
+      <c r="AR26" s="10" t="inlineStr"/>
+      <c r="AS26" s="10" t="inlineStr"/>
+      <c r="AT26" s="10" t="inlineStr"/>
+      <c r="AU26" s="10" t="inlineStr"/>
+      <c r="AV26" s="10" t="inlineStr"/>
+      <c r="AW26" s="10" t="inlineStr"/>
+      <c r="AX26" s="10" t="inlineStr"/>
+      <c r="AY26" s="10" t="inlineStr"/>
+      <c r="AZ26" s="10" t="inlineStr"/>
+      <c r="BA26" s="10" t="inlineStr"/>
+      <c r="BB26" s="10" t="inlineStr"/>
+      <c r="BC26" s="10" t="inlineStr"/>
+      <c r="BD26" s="10" t="inlineStr"/>
+      <c r="BE26" s="10" t="inlineStr"/>
+      <c r="BF26" s="10" t="inlineStr"/>
+      <c r="BG26" s="11" t="n">
+        <v>46174.30836805556</v>
+      </c>
+      <c r="BH26" s="10" t="n">
+        <v>4541.35</v>
+      </c>
+      <c r="BI26" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4543.72]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="10" t="n">
+        <v>4397.95</v>
+      </c>
+      <c r="BK26" s="10" t="n">
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr"/>
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" s="10" t="inlineStr"/>
+      <c r="Q27" s="10" t="inlineStr"/>
+      <c r="R27" s="10" t="inlineStr"/>
+      <c r="S27" s="10" t="inlineStr"/>
+      <c r="T27" s="10" t="inlineStr"/>
+      <c r="U27" s="10" t="inlineStr"/>
+      <c r="V27" s="10" t="inlineStr"/>
+      <c r="W27" s="10" t="inlineStr"/>
+      <c r="X27" s="10" t="inlineStr"/>
+      <c r="Y27" s="10" t="inlineStr"/>
+      <c r="Z27" s="10" t="inlineStr"/>
+      <c r="AA27" s="10" t="inlineStr"/>
+      <c r="AB27" s="10" t="inlineStr"/>
+      <c r="AC27" s="10" t="inlineStr"/>
+      <c r="AD27" s="11" t="n">
+        <v>46177.37152777778</v>
+      </c>
+      <c r="AE27" s="11" t="n">
+        <v>46177.37222222222</v>
+      </c>
+      <c r="AF27" s="10" t="n">
+        <v>4465.22</v>
+      </c>
+      <c r="AG27" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH27" s="10" t="n">
+        <v>4451.86</v>
+      </c>
+      <c r="AI27" s="10" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AJ27" s="10" t="inlineStr"/>
+      <c r="AK27" s="10" t="inlineStr"/>
+      <c r="AL27" s="10" t="inlineStr"/>
+      <c r="AM27" s="10" t="inlineStr"/>
+      <c r="AN27" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO27" s="10" t="inlineStr"/>
+      <c r="AP27" s="10" t="inlineStr"/>
+      <c r="AQ27" s="10" t="inlineStr"/>
+      <c r="AR27" s="10" t="inlineStr"/>
+      <c r="AS27" s="10" t="inlineStr"/>
+      <c r="AT27" s="10" t="inlineStr"/>
+      <c r="AU27" s="10" t="inlineStr"/>
+      <c r="AV27" s="10" t="inlineStr"/>
+      <c r="AW27" s="10" t="inlineStr"/>
+      <c r="AX27" s="10" t="inlineStr"/>
+      <c r="AY27" s="10" t="inlineStr"/>
+      <c r="AZ27" s="10" t="inlineStr"/>
+      <c r="BA27" s="10" t="inlineStr"/>
+      <c r="BB27" s="10" t="inlineStr"/>
+      <c r="BC27" s="10" t="inlineStr"/>
+      <c r="BD27" s="10" t="inlineStr"/>
+      <c r="BE27" s="10" t="inlineStr"/>
+      <c r="BF27" s="10" t="inlineStr"/>
+      <c r="BG27" s="11" t="n">
+        <v>46174.30836805556</v>
+      </c>
+      <c r="BH27" s="10" t="n">
+        <v>4541.35</v>
+      </c>
+      <c r="BI27" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4543.72]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="10" t="n">
+        <v>4410.95</v>
+      </c>
+      <c r="BK27" s="10" t="n">
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
+      <c r="H28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr"/>
+      <c r="P28" s="10" t="inlineStr"/>
+      <c r="Q28" s="10" t="inlineStr"/>
+      <c r="R28" s="10" t="inlineStr"/>
+      <c r="S28" s="10" t="inlineStr"/>
+      <c r="T28" s="10" t="inlineStr"/>
+      <c r="U28" s="10" t="inlineStr"/>
+      <c r="V28" s="10" t="inlineStr"/>
+      <c r="W28" s="10" t="inlineStr"/>
+      <c r="X28" s="10" t="inlineStr"/>
+      <c r="Y28" s="10" t="inlineStr"/>
+      <c r="Z28" s="10" t="inlineStr"/>
+      <c r="AA28" s="10" t="inlineStr"/>
+      <c r="AB28" s="10" t="inlineStr"/>
+      <c r="AC28" s="10" t="inlineStr"/>
+      <c r="AD28" s="11" t="n">
+        <v>46177.66736111111</v>
+      </c>
+      <c r="AE28" s="11" t="n">
+        <v>46177.7</v>
+      </c>
+      <c r="AF28" s="10" t="n">
+        <v>4470.76</v>
+      </c>
+      <c r="AG28" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH28" s="10" t="n">
+        <v>4463.7</v>
+      </c>
+      <c r="AI28" s="10" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AJ28" s="10" t="inlineStr"/>
+      <c r="AK28" s="10" t="inlineStr"/>
+      <c r="AL28" s="10" t="inlineStr"/>
+      <c r="AM28" s="10" t="inlineStr"/>
+      <c r="AN28" s="10" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="AO28" s="10" t="inlineStr"/>
+      <c r="AP28" s="10" t="inlineStr"/>
+      <c r="AQ28" s="10" t="inlineStr"/>
+      <c r="AR28" s="10" t="inlineStr"/>
+      <c r="AS28" s="10" t="inlineStr"/>
+      <c r="AT28" s="10" t="inlineStr"/>
+      <c r="AU28" s="10" t="inlineStr"/>
+      <c r="AV28" s="10" t="inlineStr"/>
+      <c r="AW28" s="10" t="inlineStr"/>
+      <c r="AX28" s="10" t="inlineStr"/>
+      <c r="AY28" s="10" t="inlineStr"/>
+      <c r="AZ28" s="10" t="inlineStr"/>
+      <c r="BA28" s="10" t="inlineStr"/>
+      <c r="BB28" s="10" t="inlineStr"/>
+      <c r="BC28" s="10" t="inlineStr"/>
+      <c r="BD28" s="10" t="inlineStr"/>
+      <c r="BE28" s="10" t="inlineStr"/>
+      <c r="BF28" s="10" t="inlineStr"/>
+      <c r="BG28" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH28" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI28" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="10" t="n">
+        <v>1044.42</v>
+      </c>
+      <c r="BK28" s="10" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" s="10" t="inlineStr"/>
+      <c r="Q29" s="10" t="inlineStr"/>
+      <c r="R29" s="10" t="inlineStr"/>
+      <c r="S29" s="10" t="inlineStr"/>
+      <c r="T29" s="10" t="inlineStr"/>
+      <c r="U29" s="10" t="inlineStr"/>
+      <c r="V29" s="10" t="inlineStr"/>
+      <c r="W29" s="10" t="inlineStr"/>
+      <c r="X29" s="10" t="inlineStr"/>
+      <c r="Y29" s="10" t="inlineStr"/>
+      <c r="Z29" s="10" t="inlineStr"/>
+      <c r="AA29" s="10" t="inlineStr"/>
+      <c r="AB29" s="10" t="inlineStr"/>
+      <c r="AC29" s="10" t="inlineStr"/>
+      <c r="AD29" s="11" t="n">
+        <v>46178.33402777778</v>
+      </c>
+      <c r="AE29" s="11" t="n">
+        <v>46178.35138888889</v>
+      </c>
+      <c r="AF29" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG29" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH29" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI29" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ29" s="10" t="inlineStr"/>
+      <c r="AK29" s="10" t="inlineStr"/>
+      <c r="AL29" s="10" t="inlineStr"/>
+      <c r="AM29" s="10" t="inlineStr"/>
+      <c r="AN29" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO29" s="10" t="inlineStr"/>
+      <c r="AP29" s="10" t="inlineStr"/>
+      <c r="AQ29" s="10" t="inlineStr"/>
+      <c r="AR29" s="10" t="inlineStr"/>
+      <c r="AS29" s="10" t="inlineStr"/>
+      <c r="AT29" s="10" t="inlineStr"/>
+      <c r="AU29" s="10" t="inlineStr"/>
+      <c r="AV29" s="10" t="inlineStr"/>
+      <c r="AW29" s="10" t="inlineStr"/>
+      <c r="AX29" s="10" t="inlineStr"/>
+      <c r="AY29" s="10" t="inlineStr"/>
+      <c r="AZ29" s="10" t="inlineStr"/>
+      <c r="BA29" s="10" t="inlineStr"/>
+      <c r="BB29" s="10" t="inlineStr"/>
+      <c r="BC29" s="10" t="inlineStr"/>
+      <c r="BD29" s="10" t="inlineStr"/>
+      <c r="BE29" s="10" t="inlineStr"/>
+      <c r="BF29" s="10" t="inlineStr"/>
+      <c r="BG29" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH29" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI29" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="10" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="BK29" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr"/>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+      <c r="K30" s="10" t="inlineStr"/>
+      <c r="L30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" s="10" t="inlineStr"/>
+      <c r="Q30" s="10" t="inlineStr"/>
+      <c r="R30" s="10" t="inlineStr"/>
+      <c r="S30" s="10" t="inlineStr"/>
+      <c r="T30" s="10" t="inlineStr"/>
+      <c r="U30" s="10" t="inlineStr"/>
+      <c r="V30" s="10" t="inlineStr"/>
+      <c r="W30" s="10" t="inlineStr"/>
+      <c r="X30" s="10" t="inlineStr"/>
+      <c r="Y30" s="10" t="inlineStr"/>
+      <c r="Z30" s="10" t="inlineStr"/>
+      <c r="AA30" s="10" t="inlineStr"/>
+      <c r="AB30" s="10" t="inlineStr"/>
+      <c r="AC30" s="10" t="inlineStr"/>
+      <c r="AD30" s="11" t="n">
+        <v>46178.35555555556</v>
+      </c>
+      <c r="AE30" s="11" t="n">
+        <v>46178.36041666667</v>
+      </c>
+      <c r="AF30" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG30" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH30" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI30" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ30" s="10" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
+      <c r="AL30" s="10" t="inlineStr"/>
+      <c r="AM30" s="10" t="inlineStr"/>
+      <c r="AN30" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO30" s="10" t="inlineStr"/>
+      <c r="AP30" s="10" t="inlineStr"/>
+      <c r="AQ30" s="10" t="inlineStr"/>
+      <c r="AR30" s="10" t="inlineStr"/>
+      <c r="AS30" s="10" t="inlineStr"/>
+      <c r="AT30" s="10" t="inlineStr"/>
+      <c r="AU30" s="10" t="inlineStr"/>
+      <c r="AV30" s="10" t="inlineStr"/>
+      <c r="AW30" s="10" t="inlineStr"/>
+      <c r="AX30" s="10" t="inlineStr"/>
+      <c r="AY30" s="10" t="inlineStr"/>
+      <c r="AZ30" s="10" t="inlineStr"/>
+      <c r="BA30" s="10" t="inlineStr"/>
+      <c r="BB30" s="10" t="inlineStr"/>
+      <c r="BC30" s="10" t="inlineStr"/>
+      <c r="BD30" s="10" t="inlineStr"/>
+      <c r="BE30" s="10" t="inlineStr"/>
+      <c r="BF30" s="10" t="inlineStr"/>
+      <c r="BG30" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH30" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI30" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="10" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="BK30" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr"/>
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" s="10" t="inlineStr"/>
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" s="10" t="inlineStr"/>
+      <c r="S31" s="10" t="inlineStr"/>
+      <c r="T31" s="10" t="inlineStr"/>
+      <c r="U31" s="10" t="inlineStr"/>
+      <c r="V31" s="10" t="inlineStr"/>
+      <c r="W31" s="10" t="inlineStr"/>
+      <c r="X31" s="10" t="inlineStr"/>
+      <c r="Y31" s="10" t="inlineStr"/>
+      <c r="Z31" s="10" t="inlineStr"/>
+      <c r="AA31" s="10" t="inlineStr"/>
+      <c r="AB31" s="10" t="inlineStr"/>
+      <c r="AC31" s="10" t="inlineStr"/>
+      <c r="AD31" s="11" t="n">
+        <v>46178.36875</v>
+      </c>
+      <c r="AE31" s="11" t="n">
+        <v>46178.36944444444</v>
+      </c>
+      <c r="AF31" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG31" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH31" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI31" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ31" s="10" t="inlineStr"/>
+      <c r="AK31" s="10" t="inlineStr"/>
+      <c r="AL31" s="10" t="inlineStr"/>
+      <c r="AM31" s="10" t="inlineStr"/>
+      <c r="AN31" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO31" s="10" t="inlineStr"/>
+      <c r="AP31" s="10" t="inlineStr"/>
+      <c r="AQ31" s="10" t="inlineStr"/>
+      <c r="AR31" s="10" t="inlineStr"/>
+      <c r="AS31" s="10" t="inlineStr"/>
+      <c r="AT31" s="10" t="inlineStr"/>
+      <c r="AU31" s="10" t="inlineStr"/>
+      <c r="AV31" s="10" t="inlineStr"/>
+      <c r="AW31" s="10" t="inlineStr"/>
+      <c r="AX31" s="10" t="inlineStr"/>
+      <c r="AY31" s="10" t="inlineStr"/>
+      <c r="AZ31" s="10" t="inlineStr"/>
+      <c r="BA31" s="10" t="inlineStr"/>
+      <c r="BB31" s="10" t="inlineStr"/>
+      <c r="BC31" s="10" t="inlineStr"/>
+      <c r="BD31" s="10" t="inlineStr"/>
+      <c r="BE31" s="10" t="inlineStr"/>
+      <c r="BF31" s="10" t="inlineStr"/>
+      <c r="BG31" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH31" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI31" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="10" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="BK31" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+      <c r="K32" s="10" t="inlineStr"/>
+      <c r="L32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" s="10" t="inlineStr"/>
+      <c r="Q32" s="10" t="inlineStr"/>
+      <c r="R32" s="10" t="inlineStr"/>
+      <c r="S32" s="10" t="inlineStr"/>
+      <c r="T32" s="10" t="inlineStr"/>
+      <c r="U32" s="10" t="inlineStr"/>
+      <c r="V32" s="10" t="inlineStr"/>
+      <c r="W32" s="10" t="inlineStr"/>
+      <c r="X32" s="10" t="inlineStr"/>
+      <c r="Y32" s="10" t="inlineStr"/>
+      <c r="Z32" s="10" t="inlineStr"/>
+      <c r="AA32" s="10" t="inlineStr"/>
+      <c r="AB32" s="10" t="inlineStr"/>
+      <c r="AC32" s="10" t="inlineStr"/>
+      <c r="AD32" s="11" t="n">
+        <v>46178.37361111111</v>
+      </c>
+      <c r="AE32" s="11" t="n">
+        <v>46178.37430555555</v>
+      </c>
+      <c r="AF32" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG32" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH32" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI32" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ32" s="10" t="inlineStr"/>
+      <c r="AK32" s="10" t="inlineStr"/>
+      <c r="AL32" s="10" t="inlineStr"/>
+      <c r="AM32" s="10" t="inlineStr"/>
+      <c r="AN32" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO32" s="10" t="inlineStr"/>
+      <c r="AP32" s="10" t="inlineStr"/>
+      <c r="AQ32" s="10" t="inlineStr"/>
+      <c r="AR32" s="10" t="inlineStr"/>
+      <c r="AS32" s="10" t="inlineStr"/>
+      <c r="AT32" s="10" t="inlineStr"/>
+      <c r="AU32" s="10" t="inlineStr"/>
+      <c r="AV32" s="10" t="inlineStr"/>
+      <c r="AW32" s="10" t="inlineStr"/>
+      <c r="AX32" s="10" t="inlineStr"/>
+      <c r="AY32" s="10" t="inlineStr"/>
+      <c r="AZ32" s="10" t="inlineStr"/>
+      <c r="BA32" s="10" t="inlineStr"/>
+      <c r="BB32" s="10" t="inlineStr"/>
+      <c r="BC32" s="10" t="inlineStr"/>
+      <c r="BD32" s="10" t="inlineStr"/>
+      <c r="BE32" s="10" t="inlineStr"/>
+      <c r="BF32" s="10" t="inlineStr"/>
+      <c r="BG32" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH32" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI32" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="10" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="BK32" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" s="10" t="inlineStr"/>
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" s="10" t="inlineStr"/>
+      <c r="S33" s="10" t="inlineStr"/>
+      <c r="T33" s="10" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr"/>
+      <c r="V33" s="10" t="inlineStr"/>
+      <c r="W33" s="10" t="inlineStr"/>
+      <c r="X33" s="10" t="inlineStr"/>
+      <c r="Y33" s="10" t="inlineStr"/>
+      <c r="Z33" s="10" t="inlineStr"/>
+      <c r="AA33" s="10" t="inlineStr"/>
+      <c r="AB33" s="10" t="inlineStr"/>
+      <c r="AC33" s="10" t="inlineStr"/>
+      <c r="AD33" s="11" t="n">
+        <v>46179.00208333333</v>
+      </c>
+      <c r="AE33" s="11" t="n">
+        <v>46179.05138888889</v>
+      </c>
+      <c r="AF33" s="10" t="n">
+        <v>4322.93</v>
+      </c>
+      <c r="AG33" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH33" s="10" t="n">
+        <v>4340.18</v>
+      </c>
+      <c r="AI33" s="10" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AJ33" s="10" t="inlineStr"/>
+      <c r="AK33" s="10" t="inlineStr"/>
+      <c r="AL33" s="10" t="inlineStr"/>
+      <c r="AM33" s="10" t="inlineStr"/>
+      <c r="AN33" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO33" s="10" t="inlineStr"/>
+      <c r="AP33" s="10" t="inlineStr"/>
+      <c r="AQ33" s="10" t="inlineStr"/>
+      <c r="AR33" s="10" t="inlineStr"/>
+      <c r="AS33" s="10" t="inlineStr"/>
+      <c r="AT33" s="10" t="inlineStr"/>
+      <c r="AU33" s="10" t="inlineStr"/>
+      <c r="AV33" s="10" t="inlineStr"/>
+      <c r="AW33" s="10" t="inlineStr"/>
+      <c r="AX33" s="10" t="inlineStr"/>
+      <c r="AY33" s="10" t="inlineStr"/>
+      <c r="AZ33" s="10" t="inlineStr"/>
+      <c r="BA33" s="10" t="inlineStr"/>
+      <c r="BB33" s="10" t="inlineStr"/>
+      <c r="BC33" s="10" t="inlineStr"/>
+      <c r="BD33" s="10" t="inlineStr"/>
+      <c r="BE33" s="10" t="inlineStr"/>
+      <c r="BF33" s="10" t="inlineStr"/>
+      <c r="BG33" s="11" t="n">
+        <v>46179.17710648148</v>
+      </c>
+      <c r="BH33" s="10" t="n">
+        <v>4315.54</v>
+      </c>
+      <c r="BI33" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill rou</t>
+        </is>
+      </c>
+      <c r="BJ33" s="10" t="n">
+        <v>252.03</v>
+      </c>
+      <c r="BK33" s="10" t="n">
+        <v>24.64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK25"/>
+  <autoFilter ref="A1:BK33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4179,10 +5003,10 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>46174.26783564815</v>
+        <v>46174.30950231481</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>4543.72</v>
@@ -4265,14 +5089,14 @@
       </c>
       <c r="AO2" s="8" t="inlineStr">
         <is>
-          <t>LOOSE</t>
+          <t>NEAR</t>
         </is>
       </c>
       <c r="AP2" s="8" t="n">
-        <v>379.74</v>
+        <v>220.74</v>
       </c>
       <c r="AQ2" s="8" t="n">
-        <v>37.95</v>
+        <v>22.05</v>
       </c>
       <c r="AR2" s="8" t="n">
         <v>0.24</v>
@@ -4715,10 +5539,10 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>46170.40681712963</v>
+        <v>46170.4484837963</v>
       </c>
       <c r="F2" s="10" t="n">
         <v>4401.5975</v>
@@ -4795,10 +5619,10 @@
       <c r="AZ2" s="10" t="inlineStr"/>
       <c r="BA2" s="10" t="inlineStr"/>
       <c r="BB2" s="11" t="n">
-        <v>46174.62569444445</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="BC2" s="10" t="n">
-        <v>4501.34</v>
+        <v>4494.38</v>
       </c>
       <c r="BD2" s="10" t="inlineStr">
         <is>
@@ -4806,10 +5630,10 @@
         </is>
       </c>
       <c r="BE2" s="10" t="n">
-        <v>6098.12</v>
+        <v>6042.12</v>
       </c>
       <c r="BF2" s="10" t="n">
-        <v>100.3</v>
+        <v>93.34</v>
       </c>
       <c r="BG2" s="10" t="inlineStr"/>
       <c r="BH2" s="10" t="inlineStr"/>
@@ -4834,10 +5658,10 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>46170.80662037037</v>
+        <v>46170.84828703704</v>
       </c>
       <c r="F3" s="10" t="n">
         <v>4385.587500000001</v>
@@ -4917,7 +5741,7 @@
         <v>46171.04236111111</v>
       </c>
       <c r="BC3" s="10" t="n">
-        <v>4508.41</v>
+        <v>4505.02</v>
       </c>
       <c r="BD3" s="10" t="inlineStr">
         <is>
@@ -4925,10 +5749,10 @@
         </is>
       </c>
       <c r="BE3" s="10" t="n">
-        <v>344.87</v>
+        <v>284.87</v>
       </c>
       <c r="BF3" s="10" t="n">
-        <v>117.17</v>
+        <v>113.78</v>
       </c>
       <c r="BG3" s="10" t="inlineStr"/>
       <c r="BH3" s="10" t="inlineStr"/>
@@ -4953,10 +5777,10 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>4540.52</v>
@@ -5033,10 +5857,10 @@
       <c r="AZ4" s="10" t="inlineStr"/>
       <c r="BA4" s="10" t="inlineStr"/>
       <c r="BB4" s="11" t="n">
-        <v>46174.62569444445</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="BC4" s="10" t="n">
-        <v>4501.34</v>
+        <v>4494.38</v>
       </c>
       <c r="BD4" s="10" t="inlineStr">
         <is>
@@ -5044,10 +5868,10 @@
         </is>
       </c>
       <c r="BE4" s="10" t="n">
-        <v>3544.43</v>
+        <v>3488.43</v>
       </c>
       <c r="BF4" s="10" t="n">
-        <v>40.62</v>
+        <v>47.58</v>
       </c>
       <c r="BG4" s="10" t="inlineStr"/>
       <c r="BH4" s="10" t="inlineStr"/>
@@ -5072,10 +5896,10 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>46178.3515162037</v>
+        <v>46178.39318287037</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>4450.29</v>
@@ -5152,10 +5976,10 @@
       <c r="AZ5" s="10" t="inlineStr"/>
       <c r="BA5" s="10" t="inlineStr"/>
       <c r="BB5" s="11" t="n">
-        <v>46178.33402777778</v>
+        <v>46178.37361111111</v>
       </c>
       <c r="BC5" s="10" t="n">
-        <v>4463.91</v>
+        <v>4464.44</v>
       </c>
       <c r="BD5" s="10" t="inlineStr">
         <is>
@@ -5163,10 +5987,10 @@
         </is>
       </c>
       <c r="BE5" s="10" t="n">
-        <v>24.42</v>
+        <v>27.42</v>
       </c>
       <c r="BF5" s="10" t="n">
-        <v>10.91</v>
+        <v>11.44</v>
       </c>
       <c r="BG5" s="10" t="inlineStr"/>
       <c r="BH5" s="10" t="inlineStr"/>
@@ -5191,10 +6015,10 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>46178.35137731482</v>
+        <v>46178.39304398148</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>46178.3515162037</v>
+        <v>46178.39318287037</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>4450.29</v>
@@ -5271,10 +6095,10 @@
       <c r="AZ6" s="10" t="inlineStr"/>
       <c r="BA6" s="10" t="inlineStr"/>
       <c r="BB6" s="11" t="n">
-        <v>46178.33402777778</v>
+        <v>46178.37361111111</v>
       </c>
       <c r="BC6" s="10" t="n">
-        <v>4463.91</v>
+        <v>4464.44</v>
       </c>
       <c r="BD6" s="10" t="inlineStr">
         <is>
@@ -5282,10 +6106,10 @@
         </is>
       </c>
       <c r="BE6" s="10" t="n">
-        <v>24.98</v>
+        <v>27.98</v>
       </c>
       <c r="BF6" s="10" t="n">
-        <v>11.69</v>
+        <v>12.22</v>
       </c>
       <c r="BG6" s="10" t="inlineStr"/>
       <c r="BH6" s="10" t="inlineStr"/>
@@ -5310,10 +6134,10 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>46179.13826388889</v>
+        <v>46179.17993055555</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>4315.41</v>
@@ -5390,10 +6214,10 @@
       <c r="AZ7" s="10" t="inlineStr"/>
       <c r="BA7" s="10" t="inlineStr"/>
       <c r="BB7" s="11" t="n">
-        <v>46179.00069444445</v>
+        <v>46179.00208333333</v>
       </c>
       <c r="BC7" s="10" t="n">
-        <v>4343.6</v>
+        <v>4340.18</v>
       </c>
       <c r="BD7" s="10" t="inlineStr">
         <is>
@@ -5401,10 +6225,10 @@
         </is>
       </c>
       <c r="BE7" s="10" t="n">
-        <v>194.03</v>
+        <v>252.03</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>28.06</v>
+        <v>24.64</v>
       </c>
       <c r="BG7" s="10" t="inlineStr"/>
       <c r="BH7" s="10" t="inlineStr"/>
@@ -5424,7 +6248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK18"/>
+  <dimension ref="A1:BK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5862,10 +6686,10 @@
         </is>
       </c>
       <c r="AH2" s="10" t="n">
-        <v>4508.41</v>
+        <v>4505.02</v>
       </c>
       <c r="AI2" s="10" t="n">
-        <v>-26.72</v>
+        <v>-40.28</v>
       </c>
       <c r="AJ2" s="10" t="inlineStr"/>
       <c r="AK2" s="10" t="inlineStr"/>
@@ -5895,7 +6719,7 @@
       <c r="BE2" s="10" t="inlineStr"/>
       <c r="BF2" s="10" t="inlineStr"/>
       <c r="BG2" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH2" s="10" t="n">
         <v>4391.24</v>
@@ -5906,10 +6730,10 @@
         </is>
       </c>
       <c r="BJ2" s="10" t="n">
-        <v>344.87</v>
+        <v>284.87</v>
       </c>
       <c r="BK2" s="10" t="n">
-        <v>117.17</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="3">
@@ -5951,13 +6775,13 @@
       <c r="AB3" s="10" t="inlineStr"/>
       <c r="AC3" s="10" t="inlineStr"/>
       <c r="AD3" s="11" t="n">
-        <v>46171.08402777778</v>
+        <v>46171.04791666667</v>
       </c>
       <c r="AE3" s="11" t="n">
-        <v>46171.34305555555</v>
+        <v>46171.3375</v>
       </c>
       <c r="AF3" s="10" t="n">
-        <v>4515.09</v>
+        <v>4500.15</v>
       </c>
       <c r="AG3" s="10" t="inlineStr">
         <is>
@@ -5965,10 +6789,10 @@
         </is>
       </c>
       <c r="AH3" s="10" t="n">
-        <v>4501.55</v>
+        <v>4505.02</v>
       </c>
       <c r="AI3" s="10" t="n">
-        <v>-54.16</v>
+        <v>19.48</v>
       </c>
       <c r="AJ3" s="10" t="inlineStr"/>
       <c r="AK3" s="10" t="inlineStr"/>
@@ -5976,7 +6800,7 @@
       <c r="AM3" s="10" t="inlineStr"/>
       <c r="AN3" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="AO3" s="10" t="inlineStr"/>
@@ -5998,7 +6822,7 @@
       <c r="BE3" s="10" t="inlineStr"/>
       <c r="BF3" s="10" t="inlineStr"/>
       <c r="BG3" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH3" s="10" t="n">
         <v>4391.24</v>
@@ -6009,10 +6833,10 @@
         </is>
       </c>
       <c r="BJ3" s="10" t="n">
-        <v>404.87</v>
+        <v>292.87</v>
       </c>
       <c r="BK3" s="10" t="n">
-        <v>110.31</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="4">
@@ -6068,10 +6892,10 @@
         </is>
       </c>
       <c r="AH4" s="10" t="n">
-        <v>4494.89</v>
+        <v>4496.55</v>
       </c>
       <c r="AI4" s="10" t="n">
-        <v>-24.84</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ4" s="10" t="inlineStr"/>
       <c r="AK4" s="10" t="inlineStr"/>
@@ -6101,7 +6925,7 @@
       <c r="BE4" s="10" t="inlineStr"/>
       <c r="BF4" s="10" t="inlineStr"/>
       <c r="BG4" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH4" s="10" t="n">
         <v>4391.24</v>
@@ -6112,10 +6936,10 @@
         </is>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>764.87</v>
+        <v>704.87</v>
       </c>
       <c r="BK4" s="10" t="n">
-        <v>103.65</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="5">
@@ -6157,13 +6981,13 @@
       <c r="AB5" s="10" t="inlineStr"/>
       <c r="AC5" s="10" t="inlineStr"/>
       <c r="AD5" s="11" t="n">
-        <v>46171.75069444445</v>
+        <v>46171.33680555555</v>
       </c>
       <c r="AE5" s="11" t="n">
-        <v>46171.82083333333</v>
+        <v>46171.3375</v>
       </c>
       <c r="AF5" s="10" t="n">
-        <v>4513.3</v>
+        <v>4501.1</v>
       </c>
       <c r="AG5" s="10" t="inlineStr">
         <is>
@@ -6171,10 +6995,10 @@
         </is>
       </c>
       <c r="AH5" s="10" t="n">
-        <v>4536.6</v>
+        <v>4496.55</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>93.2</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ5" s="10" t="inlineStr"/>
       <c r="AK5" s="10" t="inlineStr"/>
@@ -6182,7 +7006,7 @@
       <c r="AM5" s="10" t="inlineStr"/>
       <c r="AN5" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO5" s="10" t="inlineStr"/>
@@ -6204,7 +7028,7 @@
       <c r="BE5" s="10" t="inlineStr"/>
       <c r="BF5" s="10" t="inlineStr"/>
       <c r="BG5" s="11" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH5" s="10" t="n">
         <v>4391.24</v>
@@ -6215,10 +7039,10 @@
         </is>
       </c>
       <c r="BJ5" s="10" t="n">
-        <v>1364.87</v>
+        <v>708.87</v>
       </c>
       <c r="BK5" s="10" t="n">
-        <v>145.36</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="6">
@@ -6260,24 +7084,24 @@
       <c r="AB6" s="10" t="inlineStr"/>
       <c r="AC6" s="10" t="inlineStr"/>
       <c r="AD6" s="11" t="n">
-        <v>46174.62569444445</v>
+        <v>46171.35</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>46174.63611111111</v>
+        <v>46171.35069444445</v>
       </c>
       <c r="AF6" s="10" t="n">
-        <v>4491.92</v>
+        <v>4501.1</v>
       </c>
       <c r="AG6" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH6" s="10" t="n">
-        <v>4501.34</v>
+        <v>4496.55</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>-37.68</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ6" s="10" t="inlineStr"/>
       <c r="AK6" s="10" t="inlineStr"/>
@@ -6307,21 +7131,21 @@
       <c r="BE6" s="10" t="inlineStr"/>
       <c r="BF6" s="10" t="inlineStr"/>
       <c r="BG6" s="11" t="n">
-        <v>46172.16428240741</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH6" s="10" t="n">
-        <v>4541.96</v>
+        <v>4391.24</v>
       </c>
       <c r="BI6" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[tp 4381.00]</t>
         </is>
       </c>
       <c r="BJ6" s="10" t="n">
-        <v>3544.43</v>
+        <v>727.87</v>
       </c>
       <c r="BK6" s="10" t="n">
-        <v>40.62</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="7">
@@ -6363,13 +7187,13 @@
       <c r="AB7" s="10" t="inlineStr"/>
       <c r="AC7" s="10" t="inlineStr"/>
       <c r="AD7" s="11" t="n">
-        <v>46174.79236111111</v>
+        <v>46171.36736111111</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>46174.83541666667</v>
+        <v>46171.36805555555</v>
       </c>
       <c r="AF7" s="10" t="n">
-        <v>4496.2</v>
+        <v>4501.1</v>
       </c>
       <c r="AG7" s="10" t="inlineStr">
         <is>
@@ -6377,10 +7201,10 @@
         </is>
       </c>
       <c r="AH7" s="10" t="n">
-        <v>4506.38</v>
+        <v>4496.55</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>40.72</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ7" s="10" t="inlineStr"/>
       <c r="AK7" s="10" t="inlineStr"/>
@@ -6388,7 +7212,7 @@
       <c r="AM7" s="10" t="inlineStr"/>
       <c r="AN7" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO7" s="10" t="inlineStr"/>
@@ -6410,21 +7234,21 @@
       <c r="BE7" s="10" t="inlineStr"/>
       <c r="BF7" s="10" t="inlineStr"/>
       <c r="BG7" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH7" s="10" t="n">
-        <v>4541.35</v>
+        <v>4391.24</v>
       </c>
       <c r="BI7" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>[tp 4381.00]</t>
         </is>
       </c>
       <c r="BJ7" s="10" t="n">
-        <v>756.95</v>
+        <v>752.87</v>
       </c>
       <c r="BK7" s="10" t="n">
-        <v>34.97</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="8">
@@ -6466,13 +7290,13 @@
       <c r="AB8" s="10" t="inlineStr"/>
       <c r="AC8" s="10" t="inlineStr"/>
       <c r="AD8" s="11" t="n">
-        <v>46175.62569444445</v>
+        <v>46171.75069444445</v>
       </c>
       <c r="AE8" s="11" t="n">
-        <v>46175.82847222222</v>
+        <v>46171.82083333333</v>
       </c>
       <c r="AF8" s="10" t="n">
-        <v>4516.97</v>
+        <v>4513.3</v>
       </c>
       <c r="AG8" s="10" t="inlineStr">
         <is>
@@ -6480,10 +7304,10 @@
         </is>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>4530.94</v>
+        <v>4537.98</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>55.88</v>
+        <v>98.72</v>
       </c>
       <c r="AJ8" s="10" t="inlineStr"/>
       <c r="AK8" s="10" t="inlineStr"/>
@@ -6513,21 +7337,21 @@
       <c r="BE8" s="10" t="inlineStr"/>
       <c r="BF8" s="10" t="inlineStr"/>
       <c r="BG8" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="BH8" s="10" t="n">
-        <v>4541.35</v>
+        <v>4391.24</v>
       </c>
       <c r="BI8" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>[tp 4381.00]</t>
         </is>
       </c>
       <c r="BJ8" s="10" t="n">
-        <v>1956.95</v>
+        <v>1304.87</v>
       </c>
       <c r="BK8" s="10" t="n">
-        <v>10.41</v>
+        <v>146.74</v>
       </c>
     </row>
     <row r="9">
@@ -6569,13 +7393,13 @@
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="10" t="inlineStr"/>
       <c r="AD9" s="11" t="n">
-        <v>46175.70902777778</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="AE9" s="11" t="n">
-        <v>46175.82430555556</v>
+        <v>46174.63611111111</v>
       </c>
       <c r="AF9" s="10" t="n">
-        <v>4521.52</v>
+        <v>4491.92</v>
       </c>
       <c r="AG9" s="10" t="inlineStr">
         <is>
@@ -6583,10 +7407,10 @@
         </is>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>4530.48</v>
+        <v>4494.38</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>-35.84</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ9" s="10" t="inlineStr"/>
       <c r="AK9" s="10" t="inlineStr"/>
@@ -6616,21 +7440,21 @@
       <c r="BE9" s="10" t="inlineStr"/>
       <c r="BF9" s="10" t="inlineStr"/>
       <c r="BG9" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH9" s="10" t="n">
-        <v>4453</v>
+        <v>4541.96</v>
       </c>
       <c r="BI9" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>3804.42</v>
+        <v>3488.43</v>
       </c>
       <c r="BK9" s="10" t="n">
-        <v>77.48</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="10">
@@ -6672,13 +7496,13 @@
       <c r="AB10" s="10" t="inlineStr"/>
       <c r="AC10" s="10" t="inlineStr"/>
       <c r="AD10" s="11" t="n">
-        <v>46176.08402777778</v>
+        <v>46174.64027777778</v>
       </c>
       <c r="AE10" s="11" t="n">
-        <v>46176.21388888889</v>
+        <v>46174.64097222222</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>4493.07</v>
+        <v>4491.92</v>
       </c>
       <c r="AG10" s="10" t="inlineStr">
         <is>
@@ -6686,10 +7510,10 @@
         </is>
       </c>
       <c r="AH10" s="10" t="n">
-        <v>4489.41</v>
+        <v>4494.38</v>
       </c>
       <c r="AI10" s="10" t="n">
-        <v>14.64</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ10" s="10" t="inlineStr"/>
       <c r="AK10" s="10" t="inlineStr"/>
@@ -6697,7 +7521,7 @@
       <c r="AM10" s="10" t="inlineStr"/>
       <c r="AN10" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO10" s="10" t="inlineStr"/>
@@ -6719,21 +7543,21 @@
       <c r="BE10" s="10" t="inlineStr"/>
       <c r="BF10" s="10" t="inlineStr"/>
       <c r="BG10" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH10" s="10" t="n">
-        <v>4453</v>
+        <v>4541.96</v>
       </c>
       <c r="BI10" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ10" s="10" t="n">
-        <v>3264.42</v>
+        <v>3505.43</v>
       </c>
       <c r="BK10" s="10" t="n">
-        <v>36.41</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="11">
@@ -6775,13 +7599,13 @@
       <c r="AB11" s="10" t="inlineStr"/>
       <c r="AC11" s="10" t="inlineStr"/>
       <c r="AD11" s="11" t="n">
-        <v>46177.01180555556</v>
+        <v>46174.64513888889</v>
       </c>
       <c r="AE11" s="11" t="n">
-        <v>46177.02083333334</v>
+        <v>46174.68888888889</v>
       </c>
       <c r="AF11" s="10" t="n">
-        <v>4435.71</v>
+        <v>4491.92</v>
       </c>
       <c r="AG11" s="10" t="inlineStr">
         <is>
@@ -6789,10 +7613,10 @@
         </is>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>4441.57</v>
+        <v>4494.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>-23.44</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ11" s="10" t="inlineStr"/>
       <c r="AK11" s="10" t="inlineStr"/>
@@ -6800,7 +7624,7 @@
       <c r="AM11" s="10" t="inlineStr"/>
       <c r="AN11" s="10" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO11" s="10" t="inlineStr"/>
@@ -6822,21 +7646,21 @@
       <c r="BE11" s="10" t="inlineStr"/>
       <c r="BF11" s="10" t="inlineStr"/>
       <c r="BG11" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH11" s="10" t="n">
-        <v>4453</v>
+        <v>4541.96</v>
       </c>
       <c r="BI11" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ11" s="10" t="n">
-        <v>1928.42</v>
+        <v>3512.43</v>
       </c>
       <c r="BK11" s="10" t="n">
-        <v>11.43</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="12">
@@ -6878,24 +7702,24 @@
       <c r="AB12" s="10" t="inlineStr"/>
       <c r="AC12" s="10" t="inlineStr"/>
       <c r="AD12" s="11" t="n">
-        <v>46177.25138888889</v>
+        <v>46174.79583333333</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>46177.28125</v>
+        <v>46174.83541666667</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>4458.37</v>
+        <v>4496.2</v>
       </c>
       <c r="AG12" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>4447.32</v>
+        <v>4507.83</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>44.2</v>
+        <v>46.52</v>
       </c>
       <c r="AJ12" s="10" t="inlineStr"/>
       <c r="AK12" s="10" t="inlineStr"/>
@@ -6925,21 +7749,21 @@
       <c r="BE12" s="10" t="inlineStr"/>
       <c r="BF12" s="10" t="inlineStr"/>
       <c r="BG12" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH12" s="10" t="n">
-        <v>4453</v>
+        <v>4541.35</v>
       </c>
       <c r="BI12" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>1583.42</v>
+        <v>701.95</v>
       </c>
       <c r="BK12" s="10" t="n">
-        <v>5.68</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="13">
@@ -6981,13 +7805,13 @@
       <c r="AB13" s="10" t="inlineStr"/>
       <c r="AC13" s="10" t="inlineStr"/>
       <c r="AD13" s="11" t="n">
-        <v>46177.33402777778</v>
+        <v>46175.62569444445</v>
       </c>
       <c r="AE13" s="11" t="n">
-        <v>46177.34166666667</v>
+        <v>46175.82847222222</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>4465.22</v>
+        <v>4516.97</v>
       </c>
       <c r="AG13" s="10" t="inlineStr">
         <is>
@@ -6995,10 +7819,10 @@
         </is>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>4448.1</v>
+        <v>4530.94</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>-68.48</v>
+        <v>55.88</v>
       </c>
       <c r="AJ13" s="10" t="inlineStr"/>
       <c r="AK13" s="10" t="inlineStr"/>
@@ -7006,7 +7830,7 @@
       <c r="AM13" s="10" t="inlineStr"/>
       <c r="AN13" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO13" s="10" t="inlineStr"/>
@@ -7028,7 +7852,7 @@
       <c r="BE13" s="10" t="inlineStr"/>
       <c r="BF13" s="10" t="inlineStr"/>
       <c r="BG13" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH13" s="10" t="n">
         <v>4541.35</v>
@@ -7039,10 +7863,10 @@
         </is>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>4416.95</v>
+        <v>1896.95</v>
       </c>
       <c r="BK13" s="10" t="n">
-        <v>93.25</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="14">
@@ -7084,13 +7908,13 @@
       <c r="AB14" s="10" t="inlineStr"/>
       <c r="AC14" s="10" t="inlineStr"/>
       <c r="AD14" s="11" t="n">
-        <v>46177.66736111111</v>
+        <v>46175.72291666667</v>
       </c>
       <c r="AE14" s="11" t="n">
-        <v>46177.7</v>
+        <v>46175.82430555556</v>
       </c>
       <c r="AF14" s="10" t="n">
-        <v>4470.76</v>
+        <v>4521.52</v>
       </c>
       <c r="AG14" s="10" t="inlineStr">
         <is>
@@ -7098,10 +7922,10 @@
         </is>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>4463.7</v>
+        <v>4526.71</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>28.24</v>
+        <v>-20.76</v>
       </c>
       <c r="AJ14" s="10" t="inlineStr"/>
       <c r="AK14" s="10" t="inlineStr"/>
@@ -7109,7 +7933,7 @@
       <c r="AM14" s="10" t="inlineStr"/>
       <c r="AN14" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO14" s="10" t="inlineStr"/>
@@ -7131,7 +7955,7 @@
       <c r="BE14" s="10" t="inlineStr"/>
       <c r="BF14" s="10" t="inlineStr"/>
       <c r="BG14" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH14" s="10" t="n">
         <v>4453</v>
@@ -7142,10 +7966,10 @@
         </is>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>984.42</v>
+        <v>3844.42</v>
       </c>
       <c r="BK14" s="10" t="n">
-        <v>10.7</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -7156,7 +7980,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
@@ -7187,13 +8011,13 @@
       <c r="AB15" s="10" t="inlineStr"/>
       <c r="AC15" s="10" t="inlineStr"/>
       <c r="AD15" s="11" t="n">
-        <v>46178.33402777778</v>
+        <v>46177.01944444444</v>
       </c>
       <c r="AE15" s="11" t="n">
-        <v>46178.35138888889</v>
+        <v>46177.14791666667</v>
       </c>
       <c r="AF15" s="10" t="n">
-        <v>4450.29</v>
+        <v>4433.27</v>
       </c>
       <c r="AG15" s="10" t="inlineStr">
         <is>
@@ -7201,10 +8025,10 @@
         </is>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>4463.91</v>
+        <v>4439.15</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>-54.48</v>
+        <v>-23.52</v>
       </c>
       <c r="AJ15" s="10" t="inlineStr"/>
       <c r="AK15" s="10" t="inlineStr"/>
@@ -7234,7 +8058,7 @@
       <c r="BE15" s="10" t="inlineStr"/>
       <c r="BF15" s="10" t="inlineStr"/>
       <c r="BG15" s="11" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH15" s="10" t="n">
         <v>4453</v>
@@ -7245,10 +8069,10 @@
         </is>
       </c>
       <c r="BJ15" s="10" t="n">
-        <v>24.42</v>
+        <v>1977.42</v>
       </c>
       <c r="BK15" s="10" t="n">
-        <v>10.91</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="16">
@@ -7259,7 +8083,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>ENTRY_TOO_FAR</t>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr"/>
@@ -7290,24 +8114,24 @@
       <c r="AB16" s="10" t="inlineStr"/>
       <c r="AC16" s="10" t="inlineStr"/>
       <c r="AD16" s="11" t="n">
-        <v>46178.45972222222</v>
+        <v>46177.33402777778</v>
       </c>
       <c r="AE16" s="11" t="n">
-        <v>46178.55208333334</v>
+        <v>46177.34166666667</v>
       </c>
       <c r="AF16" s="10" t="n">
-        <v>4434.75</v>
+        <v>4465.22</v>
       </c>
       <c r="AG16" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>4442.47</v>
+        <v>4451.86</v>
       </c>
       <c r="AI16" s="10" t="n">
-        <v>-30.88</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ16" s="10" t="inlineStr"/>
       <c r="AK16" s="10" t="inlineStr"/>
@@ -7337,21 +8161,21 @@
       <c r="BE16" s="10" t="inlineStr"/>
       <c r="BF16" s="10" t="inlineStr"/>
       <c r="BG16" s="11" t="n">
-        <v>46178.35137731482</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH16" s="10" t="n">
-        <v>4452.22</v>
+        <v>4541.35</v>
       </c>
       <c r="BI16" s="10" t="inlineStr">
         <is>
-          <t>[sl 4450.29]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ16" s="10" t="n">
-        <v>156.02</v>
+        <v>4356.95</v>
       </c>
       <c r="BK16" s="10" t="n">
-        <v>9.75</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -7393,24 +8217,24 @@
       <c r="AB17" s="10" t="inlineStr"/>
       <c r="AC17" s="10" t="inlineStr"/>
       <c r="AD17" s="11" t="n">
-        <v>46179.00069444445</v>
+        <v>46177.34583333333</v>
       </c>
       <c r="AE17" s="11" t="n">
-        <v>46179.05138888889</v>
+        <v>46177.34722222222</v>
       </c>
       <c r="AF17" s="10" t="n">
-        <v>4322.93</v>
+        <v>4465.22</v>
       </c>
       <c r="AG17" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH17" s="10" t="n">
-        <v>4343.6</v>
+        <v>4451.86</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>-82.68000000000001</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ17" s="10" t="inlineStr"/>
       <c r="AK17" s="10" t="inlineStr"/>
@@ -7440,21 +8264,21 @@
       <c r="BE17" s="10" t="inlineStr"/>
       <c r="BF17" s="10" t="inlineStr"/>
       <c r="BG17" s="11" t="n">
-        <v>46179.13543981482</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH17" s="10" t="n">
-        <v>4315.54</v>
+        <v>4541.35</v>
       </c>
       <c r="BI17" s="10" t="inlineStr">
         <is>
-          <t>PD Zone fill rou</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ17" s="10" t="n">
-        <v>194.03</v>
+        <v>4373.95</v>
       </c>
       <c r="BK17" s="10" t="n">
-        <v>28.06</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -7496,13 +8320,13 @@
       <c r="AB18" s="10" t="inlineStr"/>
       <c r="AC18" s="10" t="inlineStr"/>
       <c r="AD18" s="11" t="n">
-        <v>46181.33402777778</v>
+        <v>46177.35347222222</v>
       </c>
       <c r="AE18" s="11" t="n">
-        <v>46181.34583333333</v>
+        <v>46177.35416666666</v>
       </c>
       <c r="AF18" s="10" t="n">
-        <v>4317.47</v>
+        <v>4465.22</v>
       </c>
       <c r="AG18" s="10" t="inlineStr">
         <is>
@@ -7510,10 +8334,10 @@
         </is>
       </c>
       <c r="AH18" s="10" t="n">
-        <v>4342.78</v>
+        <v>4451.86</v>
       </c>
       <c r="AI18" s="10" t="n">
-        <v>101.24</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ18" s="10" t="inlineStr"/>
       <c r="AK18" s="10" t="inlineStr"/>
@@ -7521,7 +8345,7 @@
       <c r="AM18" s="10" t="inlineStr"/>
       <c r="AN18" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO18" s="10" t="inlineStr"/>
@@ -7543,7 +8367,7 @@
       <c r="BE18" s="10" t="inlineStr"/>
       <c r="BF18" s="10" t="inlineStr"/>
       <c r="BG18" s="11" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH18" s="10" t="n">
         <v>4541.35</v>
@@ -7554,14 +8378,838 @@
         </is>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>10176.95</v>
+        <v>4384.95</v>
       </c>
       <c r="BK18" s="10" t="n">
-        <v>198.57</v>
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" s="10" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr"/>
+      <c r="R19" s="10" t="inlineStr"/>
+      <c r="S19" s="10" t="inlineStr"/>
+      <c r="T19" s="10" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr"/>
+      <c r="V19" s="10" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr"/>
+      <c r="X19" s="10" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr"/>
+      <c r="Z19" s="10" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr"/>
+      <c r="AB19" s="10" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr"/>
+      <c r="AD19" s="11" t="n">
+        <v>46177.3625</v>
+      </c>
+      <c r="AE19" s="11" t="n">
+        <v>46177.36597222222</v>
+      </c>
+      <c r="AF19" s="10" t="n">
+        <v>4465.22</v>
+      </c>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH19" s="10" t="n">
+        <v>4451.86</v>
+      </c>
+      <c r="AI19" s="10" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AJ19" s="10" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr"/>
+      <c r="AL19" s="10" t="inlineStr"/>
+      <c r="AM19" s="10" t="inlineStr"/>
+      <c r="AN19" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO19" s="10" t="inlineStr"/>
+      <c r="AP19" s="10" t="inlineStr"/>
+      <c r="AQ19" s="10" t="inlineStr"/>
+      <c r="AR19" s="10" t="inlineStr"/>
+      <c r="AS19" s="10" t="inlineStr"/>
+      <c r="AT19" s="10" t="inlineStr"/>
+      <c r="AU19" s="10" t="inlineStr"/>
+      <c r="AV19" s="10" t="inlineStr"/>
+      <c r="AW19" s="10" t="inlineStr"/>
+      <c r="AX19" s="10" t="inlineStr"/>
+      <c r="AY19" s="10" t="inlineStr"/>
+      <c r="AZ19" s="10" t="inlineStr"/>
+      <c r="BA19" s="10" t="inlineStr"/>
+      <c r="BB19" s="10" t="inlineStr"/>
+      <c r="BC19" s="10" t="inlineStr"/>
+      <c r="BD19" s="10" t="inlineStr"/>
+      <c r="BE19" s="10" t="inlineStr"/>
+      <c r="BF19" s="10" t="inlineStr"/>
+      <c r="BG19" s="11" t="n">
+        <v>46174.30836805556</v>
+      </c>
+      <c r="BH19" s="10" t="n">
+        <v>4541.35</v>
+      </c>
+      <c r="BI19" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4543.72]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="10" t="n">
+        <v>4397.95</v>
+      </c>
+      <c r="BK19" s="10" t="n">
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr"/>
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
+      <c r="P20" s="10" t="inlineStr"/>
+      <c r="Q20" s="10" t="inlineStr"/>
+      <c r="R20" s="10" t="inlineStr"/>
+      <c r="S20" s="10" t="inlineStr"/>
+      <c r="T20" s="10" t="inlineStr"/>
+      <c r="U20" s="10" t="inlineStr"/>
+      <c r="V20" s="10" t="inlineStr"/>
+      <c r="W20" s="10" t="inlineStr"/>
+      <c r="X20" s="10" t="inlineStr"/>
+      <c r="Y20" s="10" t="inlineStr"/>
+      <c r="Z20" s="10" t="inlineStr"/>
+      <c r="AA20" s="10" t="inlineStr"/>
+      <c r="AB20" s="10" t="inlineStr"/>
+      <c r="AC20" s="10" t="inlineStr"/>
+      <c r="AD20" s="11" t="n">
+        <v>46177.37152777778</v>
+      </c>
+      <c r="AE20" s="11" t="n">
+        <v>46177.37222222222</v>
+      </c>
+      <c r="AF20" s="10" t="n">
+        <v>4465.22</v>
+      </c>
+      <c r="AG20" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AH20" s="10" t="n">
+        <v>4451.86</v>
+      </c>
+      <c r="AI20" s="10" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AJ20" s="10" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
+      <c r="AL20" s="10" t="inlineStr"/>
+      <c r="AM20" s="10" t="inlineStr"/>
+      <c r="AN20" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO20" s="10" t="inlineStr"/>
+      <c r="AP20" s="10" t="inlineStr"/>
+      <c r="AQ20" s="10" t="inlineStr"/>
+      <c r="AR20" s="10" t="inlineStr"/>
+      <c r="AS20" s="10" t="inlineStr"/>
+      <c r="AT20" s="10" t="inlineStr"/>
+      <c r="AU20" s="10" t="inlineStr"/>
+      <c r="AV20" s="10" t="inlineStr"/>
+      <c r="AW20" s="10" t="inlineStr"/>
+      <c r="AX20" s="10" t="inlineStr"/>
+      <c r="AY20" s="10" t="inlineStr"/>
+      <c r="AZ20" s="10" t="inlineStr"/>
+      <c r="BA20" s="10" t="inlineStr"/>
+      <c r="BB20" s="10" t="inlineStr"/>
+      <c r="BC20" s="10" t="inlineStr"/>
+      <c r="BD20" s="10" t="inlineStr"/>
+      <c r="BE20" s="10" t="inlineStr"/>
+      <c r="BF20" s="10" t="inlineStr"/>
+      <c r="BG20" s="11" t="n">
+        <v>46174.30836805556</v>
+      </c>
+      <c r="BH20" s="10" t="n">
+        <v>4541.35</v>
+      </c>
+      <c r="BI20" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4543.72]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="10" t="n">
+        <v>4410.95</v>
+      </c>
+      <c r="BK20" s="10" t="n">
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr"/>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
+      <c r="P21" s="10" t="inlineStr"/>
+      <c r="Q21" s="10" t="inlineStr"/>
+      <c r="R21" s="10" t="inlineStr"/>
+      <c r="S21" s="10" t="inlineStr"/>
+      <c r="T21" s="10" t="inlineStr"/>
+      <c r="U21" s="10" t="inlineStr"/>
+      <c r="V21" s="10" t="inlineStr"/>
+      <c r="W21" s="10" t="inlineStr"/>
+      <c r="X21" s="10" t="inlineStr"/>
+      <c r="Y21" s="10" t="inlineStr"/>
+      <c r="Z21" s="10" t="inlineStr"/>
+      <c r="AA21" s="10" t="inlineStr"/>
+      <c r="AB21" s="10" t="inlineStr"/>
+      <c r="AC21" s="10" t="inlineStr"/>
+      <c r="AD21" s="11" t="n">
+        <v>46177.66736111111</v>
+      </c>
+      <c r="AE21" s="11" t="n">
+        <v>46177.7</v>
+      </c>
+      <c r="AF21" s="10" t="n">
+        <v>4470.76</v>
+      </c>
+      <c r="AG21" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH21" s="10" t="n">
+        <v>4463.7</v>
+      </c>
+      <c r="AI21" s="10" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AJ21" s="10" t="inlineStr"/>
+      <c r="AK21" s="10" t="inlineStr"/>
+      <c r="AL21" s="10" t="inlineStr"/>
+      <c r="AM21" s="10" t="inlineStr"/>
+      <c r="AN21" s="10" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="AO21" s="10" t="inlineStr"/>
+      <c r="AP21" s="10" t="inlineStr"/>
+      <c r="AQ21" s="10" t="inlineStr"/>
+      <c r="AR21" s="10" t="inlineStr"/>
+      <c r="AS21" s="10" t="inlineStr"/>
+      <c r="AT21" s="10" t="inlineStr"/>
+      <c r="AU21" s="10" t="inlineStr"/>
+      <c r="AV21" s="10" t="inlineStr"/>
+      <c r="AW21" s="10" t="inlineStr"/>
+      <c r="AX21" s="10" t="inlineStr"/>
+      <c r="AY21" s="10" t="inlineStr"/>
+      <c r="AZ21" s="10" t="inlineStr"/>
+      <c r="BA21" s="10" t="inlineStr"/>
+      <c r="BB21" s="10" t="inlineStr"/>
+      <c r="BC21" s="10" t="inlineStr"/>
+      <c r="BD21" s="10" t="inlineStr"/>
+      <c r="BE21" s="10" t="inlineStr"/>
+      <c r="BF21" s="10" t="inlineStr"/>
+      <c r="BG21" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH21" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI21" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="10" t="n">
+        <v>1044.42</v>
+      </c>
+      <c r="BK21" s="10" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr"/>
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
+      <c r="O22" s="10" t="inlineStr"/>
+      <c r="P22" s="10" t="inlineStr"/>
+      <c r="Q22" s="10" t="inlineStr"/>
+      <c r="R22" s="10" t="inlineStr"/>
+      <c r="S22" s="10" t="inlineStr"/>
+      <c r="T22" s="10" t="inlineStr"/>
+      <c r="U22" s="10" t="inlineStr"/>
+      <c r="V22" s="10" t="inlineStr"/>
+      <c r="W22" s="10" t="inlineStr"/>
+      <c r="X22" s="10" t="inlineStr"/>
+      <c r="Y22" s="10" t="inlineStr"/>
+      <c r="Z22" s="10" t="inlineStr"/>
+      <c r="AA22" s="10" t="inlineStr"/>
+      <c r="AB22" s="10" t="inlineStr"/>
+      <c r="AC22" s="10" t="inlineStr"/>
+      <c r="AD22" s="11" t="n">
+        <v>46178.33402777778</v>
+      </c>
+      <c r="AE22" s="11" t="n">
+        <v>46178.35138888889</v>
+      </c>
+      <c r="AF22" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG22" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH22" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI22" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ22" s="10" t="inlineStr"/>
+      <c r="AK22" s="10" t="inlineStr"/>
+      <c r="AL22" s="10" t="inlineStr"/>
+      <c r="AM22" s="10" t="inlineStr"/>
+      <c r="AN22" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO22" s="10" t="inlineStr"/>
+      <c r="AP22" s="10" t="inlineStr"/>
+      <c r="AQ22" s="10" t="inlineStr"/>
+      <c r="AR22" s="10" t="inlineStr"/>
+      <c r="AS22" s="10" t="inlineStr"/>
+      <c r="AT22" s="10" t="inlineStr"/>
+      <c r="AU22" s="10" t="inlineStr"/>
+      <c r="AV22" s="10" t="inlineStr"/>
+      <c r="AW22" s="10" t="inlineStr"/>
+      <c r="AX22" s="10" t="inlineStr"/>
+      <c r="AY22" s="10" t="inlineStr"/>
+      <c r="AZ22" s="10" t="inlineStr"/>
+      <c r="BA22" s="10" t="inlineStr"/>
+      <c r="BB22" s="10" t="inlineStr"/>
+      <c r="BC22" s="10" t="inlineStr"/>
+      <c r="BD22" s="10" t="inlineStr"/>
+      <c r="BE22" s="10" t="inlineStr"/>
+      <c r="BF22" s="10" t="inlineStr"/>
+      <c r="BG22" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH22" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI22" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="10" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="BK22" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr"/>
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" s="10" t="inlineStr"/>
+      <c r="P23" s="10" t="inlineStr"/>
+      <c r="Q23" s="10" t="inlineStr"/>
+      <c r="R23" s="10" t="inlineStr"/>
+      <c r="S23" s="10" t="inlineStr"/>
+      <c r="T23" s="10" t="inlineStr"/>
+      <c r="U23" s="10" t="inlineStr"/>
+      <c r="V23" s="10" t="inlineStr"/>
+      <c r="W23" s="10" t="inlineStr"/>
+      <c r="X23" s="10" t="inlineStr"/>
+      <c r="Y23" s="10" t="inlineStr"/>
+      <c r="Z23" s="10" t="inlineStr"/>
+      <c r="AA23" s="10" t="inlineStr"/>
+      <c r="AB23" s="10" t="inlineStr"/>
+      <c r="AC23" s="10" t="inlineStr"/>
+      <c r="AD23" s="11" t="n">
+        <v>46178.35555555556</v>
+      </c>
+      <c r="AE23" s="11" t="n">
+        <v>46178.36041666667</v>
+      </c>
+      <c r="AF23" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG23" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH23" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI23" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ23" s="10" t="inlineStr"/>
+      <c r="AK23" s="10" t="inlineStr"/>
+      <c r="AL23" s="10" t="inlineStr"/>
+      <c r="AM23" s="10" t="inlineStr"/>
+      <c r="AN23" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO23" s="10" t="inlineStr"/>
+      <c r="AP23" s="10" t="inlineStr"/>
+      <c r="AQ23" s="10" t="inlineStr"/>
+      <c r="AR23" s="10" t="inlineStr"/>
+      <c r="AS23" s="10" t="inlineStr"/>
+      <c r="AT23" s="10" t="inlineStr"/>
+      <c r="AU23" s="10" t="inlineStr"/>
+      <c r="AV23" s="10" t="inlineStr"/>
+      <c r="AW23" s="10" t="inlineStr"/>
+      <c r="AX23" s="10" t="inlineStr"/>
+      <c r="AY23" s="10" t="inlineStr"/>
+      <c r="AZ23" s="10" t="inlineStr"/>
+      <c r="BA23" s="10" t="inlineStr"/>
+      <c r="BB23" s="10" t="inlineStr"/>
+      <c r="BC23" s="10" t="inlineStr"/>
+      <c r="BD23" s="10" t="inlineStr"/>
+      <c r="BE23" s="10" t="inlineStr"/>
+      <c r="BF23" s="10" t="inlineStr"/>
+      <c r="BG23" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH23" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI23" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="10" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="BK23" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr"/>
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
+      <c r="O24" s="10" t="inlineStr"/>
+      <c r="P24" s="10" t="inlineStr"/>
+      <c r="Q24" s="10" t="inlineStr"/>
+      <c r="R24" s="10" t="inlineStr"/>
+      <c r="S24" s="10" t="inlineStr"/>
+      <c r="T24" s="10" t="inlineStr"/>
+      <c r="U24" s="10" t="inlineStr"/>
+      <c r="V24" s="10" t="inlineStr"/>
+      <c r="W24" s="10" t="inlineStr"/>
+      <c r="X24" s="10" t="inlineStr"/>
+      <c r="Y24" s="10" t="inlineStr"/>
+      <c r="Z24" s="10" t="inlineStr"/>
+      <c r="AA24" s="10" t="inlineStr"/>
+      <c r="AB24" s="10" t="inlineStr"/>
+      <c r="AC24" s="10" t="inlineStr"/>
+      <c r="AD24" s="11" t="n">
+        <v>46178.36875</v>
+      </c>
+      <c r="AE24" s="11" t="n">
+        <v>46178.36944444444</v>
+      </c>
+      <c r="AF24" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG24" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH24" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI24" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ24" s="10" t="inlineStr"/>
+      <c r="AK24" s="10" t="inlineStr"/>
+      <c r="AL24" s="10" t="inlineStr"/>
+      <c r="AM24" s="10" t="inlineStr"/>
+      <c r="AN24" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO24" s="10" t="inlineStr"/>
+      <c r="AP24" s="10" t="inlineStr"/>
+      <c r="AQ24" s="10" t="inlineStr"/>
+      <c r="AR24" s="10" t="inlineStr"/>
+      <c r="AS24" s="10" t="inlineStr"/>
+      <c r="AT24" s="10" t="inlineStr"/>
+      <c r="AU24" s="10" t="inlineStr"/>
+      <c r="AV24" s="10" t="inlineStr"/>
+      <c r="AW24" s="10" t="inlineStr"/>
+      <c r="AX24" s="10" t="inlineStr"/>
+      <c r="AY24" s="10" t="inlineStr"/>
+      <c r="AZ24" s="10" t="inlineStr"/>
+      <c r="BA24" s="10" t="inlineStr"/>
+      <c r="BB24" s="10" t="inlineStr"/>
+      <c r="BC24" s="10" t="inlineStr"/>
+      <c r="BD24" s="10" t="inlineStr"/>
+      <c r="BE24" s="10" t="inlineStr"/>
+      <c r="BF24" s="10" t="inlineStr"/>
+      <c r="BG24" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH24" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI24" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="10" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="BK24" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
+      <c r="O25" s="10" t="inlineStr"/>
+      <c r="P25" s="10" t="inlineStr"/>
+      <c r="Q25" s="10" t="inlineStr"/>
+      <c r="R25" s="10" t="inlineStr"/>
+      <c r="S25" s="10" t="inlineStr"/>
+      <c r="T25" s="10" t="inlineStr"/>
+      <c r="U25" s="10" t="inlineStr"/>
+      <c r="V25" s="10" t="inlineStr"/>
+      <c r="W25" s="10" t="inlineStr"/>
+      <c r="X25" s="10" t="inlineStr"/>
+      <c r="Y25" s="10" t="inlineStr"/>
+      <c r="Z25" s="10" t="inlineStr"/>
+      <c r="AA25" s="10" t="inlineStr"/>
+      <c r="AB25" s="10" t="inlineStr"/>
+      <c r="AC25" s="10" t="inlineStr"/>
+      <c r="AD25" s="11" t="n">
+        <v>46178.37361111111</v>
+      </c>
+      <c r="AE25" s="11" t="n">
+        <v>46178.37430555555</v>
+      </c>
+      <c r="AF25" s="10" t="n">
+        <v>4450.29</v>
+      </c>
+      <c r="AG25" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH25" s="10" t="n">
+        <v>4464.44</v>
+      </c>
+      <c r="AI25" s="10" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="AJ25" s="10" t="inlineStr"/>
+      <c r="AK25" s="10" t="inlineStr"/>
+      <c r="AL25" s="10" t="inlineStr"/>
+      <c r="AM25" s="10" t="inlineStr"/>
+      <c r="AN25" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO25" s="10" t="inlineStr"/>
+      <c r="AP25" s="10" t="inlineStr"/>
+      <c r="AQ25" s="10" t="inlineStr"/>
+      <c r="AR25" s="10" t="inlineStr"/>
+      <c r="AS25" s="10" t="inlineStr"/>
+      <c r="AT25" s="10" t="inlineStr"/>
+      <c r="AU25" s="10" t="inlineStr"/>
+      <c r="AV25" s="10" t="inlineStr"/>
+      <c r="AW25" s="10" t="inlineStr"/>
+      <c r="AX25" s="10" t="inlineStr"/>
+      <c r="AY25" s="10" t="inlineStr"/>
+      <c r="AZ25" s="10" t="inlineStr"/>
+      <c r="BA25" s="10" t="inlineStr"/>
+      <c r="BB25" s="10" t="inlineStr"/>
+      <c r="BC25" s="10" t="inlineStr"/>
+      <c r="BD25" s="10" t="inlineStr"/>
+      <c r="BE25" s="10" t="inlineStr"/>
+      <c r="BF25" s="10" t="inlineStr"/>
+      <c r="BG25" s="11" t="n">
+        <v>46178.39265046296</v>
+      </c>
+      <c r="BH25" s="10" t="n">
+        <v>4453</v>
+      </c>
+      <c r="BI25" s="10" t="inlineStr">
+        <is>
+          <t>[sl 4450.29]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="10" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="BK25" s="10" t="n">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>BACKTEST_ONLY</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr"/>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="inlineStr"/>
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" s="10" t="inlineStr"/>
+      <c r="P26" s="10" t="inlineStr"/>
+      <c r="Q26" s="10" t="inlineStr"/>
+      <c r="R26" s="10" t="inlineStr"/>
+      <c r="S26" s="10" t="inlineStr"/>
+      <c r="T26" s="10" t="inlineStr"/>
+      <c r="U26" s="10" t="inlineStr"/>
+      <c r="V26" s="10" t="inlineStr"/>
+      <c r="W26" s="10" t="inlineStr"/>
+      <c r="X26" s="10" t="inlineStr"/>
+      <c r="Y26" s="10" t="inlineStr"/>
+      <c r="Z26" s="10" t="inlineStr"/>
+      <c r="AA26" s="10" t="inlineStr"/>
+      <c r="AB26" s="10" t="inlineStr"/>
+      <c r="AC26" s="10" t="inlineStr"/>
+      <c r="AD26" s="11" t="n">
+        <v>46179.00208333333</v>
+      </c>
+      <c r="AE26" s="11" t="n">
+        <v>46179.05138888889</v>
+      </c>
+      <c r="AF26" s="10" t="n">
+        <v>4322.93</v>
+      </c>
+      <c r="AG26" s="10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AH26" s="10" t="n">
+        <v>4340.18</v>
+      </c>
+      <c r="AI26" s="10" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AJ26" s="10" t="inlineStr"/>
+      <c r="AK26" s="10" t="inlineStr"/>
+      <c r="AL26" s="10" t="inlineStr"/>
+      <c r="AM26" s="10" t="inlineStr"/>
+      <c r="AN26" s="10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="AO26" s="10" t="inlineStr"/>
+      <c r="AP26" s="10" t="inlineStr"/>
+      <c r="AQ26" s="10" t="inlineStr"/>
+      <c r="AR26" s="10" t="inlineStr"/>
+      <c r="AS26" s="10" t="inlineStr"/>
+      <c r="AT26" s="10" t="inlineStr"/>
+      <c r="AU26" s="10" t="inlineStr"/>
+      <c r="AV26" s="10" t="inlineStr"/>
+      <c r="AW26" s="10" t="inlineStr"/>
+      <c r="AX26" s="10" t="inlineStr"/>
+      <c r="AY26" s="10" t="inlineStr"/>
+      <c r="AZ26" s="10" t="inlineStr"/>
+      <c r="BA26" s="10" t="inlineStr"/>
+      <c r="BB26" s="10" t="inlineStr"/>
+      <c r="BC26" s="10" t="inlineStr"/>
+      <c r="BD26" s="10" t="inlineStr"/>
+      <c r="BE26" s="10" t="inlineStr"/>
+      <c r="BF26" s="10" t="inlineStr"/>
+      <c r="BG26" s="11" t="n">
+        <v>46179.17710648148</v>
+      </c>
+      <c r="BH26" s="10" t="n">
+        <v>4315.54</v>
+      </c>
+      <c r="BI26" s="10" t="inlineStr">
+        <is>
+          <t>PD Zone fill rou</t>
+        </is>
+      </c>
+      <c r="BJ26" s="10" t="n">
+        <v>252.03</v>
+      </c>
+      <c r="BK26" s="10" t="n">
+        <v>24.64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK18"/>
+  <autoFilter ref="A1:BK26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8106,10 +9754,10 @@
         <v>-18.04</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="G2" s="13" t="n">
-        <v>46178.35137731482</v>
+        <v>46178.39304398148</v>
       </c>
     </row>
     <row r="3">
@@ -8135,10 +9783,10 @@
         <v>-0.44</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
     </row>
     <row r="4">
@@ -8164,10 +9812,10 @@
         <v>2.23</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
     </row>
     <row r="5">
@@ -8193,10 +9841,10 @@
         <v>-5.76</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
     </row>
     <row r="6">
@@ -8222,10 +9870,10 @@
         <v>22.61</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
     </row>
     <row r="7">
@@ -8245,16 +9893,16 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-241.56</v>
+        <v>-369.2</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>46174.62569444445</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>46179.00069444445</v>
+        <v>46179.00208333333</v>
       </c>
     </row>
     <row r="8">
@@ -8274,16 +9922,16 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-174.2</v>
+        <v>-380.28</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>46171.04236111111</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>46177.33402777778</v>
+        <v>46177.37152777778</v>
       </c>
     </row>
     <row r="9">
@@ -8303,16 +9951,16 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>291.04</v>
+        <v>201.12</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>46171.75069444445</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>46181.33402777778</v>
+        <v>46175.62569444445</v>
       </c>
     </row>
     <row r="10">
@@ -8323,25 +9971,25 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>87.08</v>
+        <v>19.48</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>46176.08402777778</v>
+        <v>46171.04791666667</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>46177.66736111111</v>
+        <v>46171.04791666667</v>
       </c>
     </row>
     <row r="11">
@@ -8352,7 +10000,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -8364,13 +10012,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>-23.44</v>
+        <v>28.24</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>46177.01180555556</v>
+        <v>46177.66736111111</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>46177.01180555556</v>
+        <v>46177.66736111111</v>
       </c>
     </row>
     <row r="12">
@@ -8421,10 +10069,10 @@
         <v>19.08</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
     </row>
     <row r="14">
@@ -8450,10 +10098,10 @@
         <v>-18.04</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>46178.3509837963</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>46178.35137731482</v>
+        <v>46178.39304398148</v>
       </c>
     </row>
     <row r="15">
@@ -8479,10 +10127,10 @@
         <v>-0.44</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
     </row>
     <row r="16">
@@ -8502,16 +10150,16 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>24.28</v>
+        <v>-274.24</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>46171.04236111111</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>46181.33402777778</v>
+        <v>46179.00208333333</v>
       </c>
     </row>
     <row r="17">
@@ -8531,16 +10179,16 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>-85.36</v>
+        <v>-226.4</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>46178.33402777778</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>46178.45972222222</v>
+        <v>46178.37361111111</v>
       </c>
     </row>
     <row r="18">
@@ -8566,10 +10214,10 @@
         <v>-95.95999999999999</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
     </row>
     <row r="19">
@@ -8595,10 +10243,10 @@
         <v>-8.970000000000001</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
     </row>
     <row r="20">
@@ -8624,10 +10272,10 @@
         <v>-13.04</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>46172.16428240741</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>46178.35137731482</v>
+        <v>46178.39304398148</v>
       </c>
     </row>
     <row r="21">
@@ -8653,10 +10301,10 @@
         <v>22.61</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
     </row>
     <row r="22">
@@ -8682,10 +10330,10 @@
         <v>-95.95999999999999</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
     </row>
     <row r="23">
@@ -8711,10 +10359,10 @@
         <v>-22.01</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>46170.3908912037</v>
+        <v>46170.43255787037</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>46179.13543981482</v>
+        <v>46179.17710648148</v>
       </c>
     </row>
     <row r="24">
@@ -8740,10 +10388,10 @@
         <v>22.61</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>46170.80287037037</v>
+        <v>46170.84453703704</v>
       </c>
     </row>
     <row r="25">
@@ -8759,20 +10407,20 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>-177.92</v>
+        <v>-159.68</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>46174.62569444445</v>
+        <v>46171.04236111111</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>46179.00069444445</v>
+        <v>46177.37152777778</v>
       </c>
     </row>
     <row r="26">
@@ -8788,20 +10436,20 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>116.84</v>
+        <v>-340.96</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>46171.04236111111</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>46181.33402777778</v>
+        <v>46179.00208333333</v>
       </c>
     </row>
     <row r="27">
@@ -8827,10 +10475,10 @@
         <v>-95.95999999999999</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
     </row>
     <row r="28">
@@ -8856,10 +10504,10 @@
         <v>-95.95999999999999</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>46174.26670138889</v>
+        <v>46174.30836805556</v>
       </c>
     </row>
   </sheetData>

--- a/excel_reports/backtest_compare/s10/compare_s10_H1_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s10/compare_s10_H1_20260528_0800_20260608_1000.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Gap Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:24:20</t>
+          <t>2026-06-19 09:26:27</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK33"/>
+  <dimension ref="A1:BK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1754,7 +1754,7 @@
       <c r="AZ6" s="10" t="inlineStr"/>
       <c r="BA6" s="10" t="inlineStr"/>
       <c r="BB6" s="11" t="n">
-        <v>46178.37361111111</v>
+        <v>46178.33402777778</v>
       </c>
       <c r="BC6" s="10" t="n">
         <v>4464.44</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="BE6" s="10" t="n">
-        <v>27.42</v>
+        <v>84.42</v>
       </c>
       <c r="BF6" s="10" t="n">
         <v>11.44</v>
@@ -1873,7 +1873,7 @@
       <c r="AZ7" s="10" t="inlineStr"/>
       <c r="BA7" s="10" t="inlineStr"/>
       <c r="BB7" s="11" t="n">
-        <v>46178.37361111111</v>
+        <v>46178.33402777778</v>
       </c>
       <c r="BC7" s="10" t="n">
         <v>4464.44</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="BE7" s="10" t="n">
-        <v>27.98</v>
+        <v>84.98</v>
       </c>
       <c r="BF7" s="10" t="n">
         <v>12.22</v>
@@ -2156,13 +2156,13 @@
       <c r="AB10" s="10" t="inlineStr"/>
       <c r="AC10" s="10" t="inlineStr"/>
       <c r="AD10" s="11" t="n">
-        <v>46171.04791666667</v>
+        <v>46171.33402777778</v>
       </c>
       <c r="AE10" s="11" t="n">
-        <v>46171.3375</v>
+        <v>46171.33611111111</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>4500.15</v>
+        <v>4501.1</v>
       </c>
       <c r="AG10" s="10" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="AH10" s="10" t="n">
-        <v>4505.02</v>
+        <v>4496.55</v>
       </c>
       <c r="AI10" s="10" t="n">
-        <v>19.48</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ10" s="10" t="inlineStr"/>
       <c r="AK10" s="10" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       <c r="AM10" s="10" t="inlineStr"/>
       <c r="AN10" s="10" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO10" s="10" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="BJ10" s="10" t="n">
-        <v>292.87</v>
+        <v>704.87</v>
       </c>
       <c r="BK10" s="10" t="n">
-        <v>113.78</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="11">
@@ -2259,13 +2259,13 @@
       <c r="AB11" s="10" t="inlineStr"/>
       <c r="AC11" s="10" t="inlineStr"/>
       <c r="AD11" s="11" t="n">
-        <v>46171.33402777778</v>
+        <v>46171.75069444445</v>
       </c>
       <c r="AE11" s="11" t="n">
-        <v>46171.33611111111</v>
+        <v>46171.82083333333</v>
       </c>
       <c r="AF11" s="10" t="n">
-        <v>4501.1</v>
+        <v>4513.3</v>
       </c>
       <c r="AG11" s="10" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>4496.55</v>
+        <v>4537.98</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>-18.2</v>
+        <v>98.72</v>
       </c>
       <c r="AJ11" s="10" t="inlineStr"/>
       <c r="AK11" s="10" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
       <c r="AM11" s="10" t="inlineStr"/>
       <c r="AN11" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO11" s="10" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="BJ11" s="10" t="n">
-        <v>704.87</v>
+        <v>1304.87</v>
       </c>
       <c r="BK11" s="10" t="n">
-        <v>105.31</v>
+        <v>146.74</v>
       </c>
     </row>
     <row r="12">
@@ -2362,24 +2362,24 @@
       <c r="AB12" s="10" t="inlineStr"/>
       <c r="AC12" s="10" t="inlineStr"/>
       <c r="AD12" s="11" t="n">
-        <v>46171.33680555555</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>46171.3375</v>
+        <v>46174.63611111111</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>4501.1</v>
+        <v>4491.92</v>
       </c>
       <c r="AG12" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>4496.55</v>
+        <v>4494.38</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>-18.2</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ12" s="10" t="inlineStr"/>
       <c r="AK12" s="10" t="inlineStr"/>
@@ -2409,21 +2409,21 @@
       <c r="BE12" s="10" t="inlineStr"/>
       <c r="BF12" s="10" t="inlineStr"/>
       <c r="BG12" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH12" s="10" t="n">
-        <v>4391.24</v>
+        <v>4541.96</v>
       </c>
       <c r="BI12" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>708.87</v>
+        <v>3488.43</v>
       </c>
       <c r="BK12" s="10" t="n">
-        <v>105.31</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="13">
@@ -2465,13 +2465,13 @@
       <c r="AB13" s="10" t="inlineStr"/>
       <c r="AC13" s="10" t="inlineStr"/>
       <c r="AD13" s="11" t="n">
-        <v>46171.35</v>
+        <v>46174.79583333333</v>
       </c>
       <c r="AE13" s="11" t="n">
-        <v>46171.35069444445</v>
+        <v>46174.83541666667</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>4501.1</v>
+        <v>4496.2</v>
       </c>
       <c r="AG13" s="10" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>4496.55</v>
+        <v>4507.83</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>-18.2</v>
+        <v>46.52</v>
       </c>
       <c r="AJ13" s="10" t="inlineStr"/>
       <c r="AK13" s="10" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       <c r="AM13" s="10" t="inlineStr"/>
       <c r="AN13" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO13" s="10" t="inlineStr"/>
@@ -2512,21 +2512,21 @@
       <c r="BE13" s="10" t="inlineStr"/>
       <c r="BF13" s="10" t="inlineStr"/>
       <c r="BG13" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH13" s="10" t="n">
-        <v>4391.24</v>
+        <v>4541.35</v>
       </c>
       <c r="BI13" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>727.87</v>
+        <v>701.95</v>
       </c>
       <c r="BK13" s="10" t="n">
-        <v>105.31</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="14">
@@ -2568,13 +2568,13 @@
       <c r="AB14" s="10" t="inlineStr"/>
       <c r="AC14" s="10" t="inlineStr"/>
       <c r="AD14" s="11" t="n">
-        <v>46171.36736111111</v>
+        <v>46175.62569444445</v>
       </c>
       <c r="AE14" s="11" t="n">
-        <v>46171.36805555555</v>
+        <v>46175.82847222222</v>
       </c>
       <c r="AF14" s="10" t="n">
-        <v>4501.1</v>
+        <v>4516.97</v>
       </c>
       <c r="AG14" s="10" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>4496.55</v>
+        <v>4530.94</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>-18.2</v>
+        <v>55.88</v>
       </c>
       <c r="AJ14" s="10" t="inlineStr"/>
       <c r="AK14" s="10" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       <c r="AM14" s="10" t="inlineStr"/>
       <c r="AN14" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO14" s="10" t="inlineStr"/>
@@ -2615,21 +2615,21 @@
       <c r="BE14" s="10" t="inlineStr"/>
       <c r="BF14" s="10" t="inlineStr"/>
       <c r="BG14" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH14" s="10" t="n">
-        <v>4391.24</v>
+        <v>4541.35</v>
       </c>
       <c r="BI14" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>752.87</v>
+        <v>1896.95</v>
       </c>
       <c r="BK14" s="10" t="n">
-        <v>105.31</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="15">
@@ -2671,24 +2671,24 @@
       <c r="AB15" s="10" t="inlineStr"/>
       <c r="AC15" s="10" t="inlineStr"/>
       <c r="AD15" s="11" t="n">
-        <v>46171.75069444445</v>
+        <v>46175.72291666667</v>
       </c>
       <c r="AE15" s="11" t="n">
-        <v>46171.82083333333</v>
+        <v>46175.82430555556</v>
       </c>
       <c r="AF15" s="10" t="n">
-        <v>4513.3</v>
+        <v>4521.52</v>
       </c>
       <c r="AG15" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>4537.98</v>
+        <v>4526.71</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>98.72</v>
+        <v>-20.76</v>
       </c>
       <c r="AJ15" s="10" t="inlineStr"/>
       <c r="AK15" s="10" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
       <c r="AM15" s="10" t="inlineStr"/>
       <c r="AN15" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO15" s="10" t="inlineStr"/>
@@ -2718,21 +2718,21 @@
       <c r="BE15" s="10" t="inlineStr"/>
       <c r="BF15" s="10" t="inlineStr"/>
       <c r="BG15" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH15" s="10" t="n">
-        <v>4391.24</v>
+        <v>4453</v>
       </c>
       <c r="BI15" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ15" s="10" t="n">
-        <v>1304.87</v>
+        <v>3844.42</v>
       </c>
       <c r="BK15" s="10" t="n">
-        <v>146.74</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2774,13 +2774,13 @@
       <c r="AB16" s="10" t="inlineStr"/>
       <c r="AC16" s="10" t="inlineStr"/>
       <c r="AD16" s="11" t="n">
-        <v>46174.62847222222</v>
+        <v>46177.01944444444</v>
       </c>
       <c r="AE16" s="11" t="n">
-        <v>46174.63611111111</v>
+        <v>46177.02083333334</v>
       </c>
       <c r="AF16" s="10" t="n">
-        <v>4491.92</v>
+        <v>4435.71</v>
       </c>
       <c r="AG16" s="10" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>4494.38</v>
+        <v>4439.15</v>
       </c>
       <c r="AI16" s="10" t="n">
-        <v>-9.84</v>
+        <v>-13.76</v>
       </c>
       <c r="AJ16" s="10" t="inlineStr"/>
       <c r="AK16" s="10" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
       <c r="AM16" s="10" t="inlineStr"/>
       <c r="AN16" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="AO16" s="10" t="inlineStr"/>
@@ -2821,21 +2821,21 @@
       <c r="BE16" s="10" t="inlineStr"/>
       <c r="BF16" s="10" t="inlineStr"/>
       <c r="BG16" s="11" t="n">
-        <v>46172.20594907407</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH16" s="10" t="n">
-        <v>4541.96</v>
+        <v>4453</v>
       </c>
       <c r="BI16" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ16" s="10" t="n">
-        <v>3488.43</v>
+        <v>1977.42</v>
       </c>
       <c r="BK16" s="10" t="n">
-        <v>47.58</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="17">
@@ -2877,24 +2877,24 @@
       <c r="AB17" s="10" t="inlineStr"/>
       <c r="AC17" s="10" t="inlineStr"/>
       <c r="AD17" s="11" t="n">
-        <v>46174.64027777778</v>
+        <v>46177.33402777778</v>
       </c>
       <c r="AE17" s="11" t="n">
-        <v>46174.64097222222</v>
+        <v>46177.34166666667</v>
       </c>
       <c r="AF17" s="10" t="n">
-        <v>4491.92</v>
+        <v>4465.22</v>
       </c>
       <c r="AG17" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH17" s="10" t="n">
-        <v>4494.38</v>
+        <v>4451.86</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>-9.84</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ17" s="10" t="inlineStr"/>
       <c r="AK17" s="10" t="inlineStr"/>
@@ -2924,21 +2924,21 @@
       <c r="BE17" s="10" t="inlineStr"/>
       <c r="BF17" s="10" t="inlineStr"/>
       <c r="BG17" s="11" t="n">
-        <v>46172.20594907407</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH17" s="10" t="n">
-        <v>4541.96</v>
+        <v>4541.35</v>
       </c>
       <c r="BI17" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ17" s="10" t="n">
-        <v>3505.43</v>
+        <v>4356.95</v>
       </c>
       <c r="BK17" s="10" t="n">
-        <v>47.58</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2980,13 +2980,13 @@
       <c r="AB18" s="10" t="inlineStr"/>
       <c r="AC18" s="10" t="inlineStr"/>
       <c r="AD18" s="11" t="n">
-        <v>46174.64513888889</v>
+        <v>46177.66736111111</v>
       </c>
       <c r="AE18" s="11" t="n">
-        <v>46174.68888888889</v>
+        <v>46177.7</v>
       </c>
       <c r="AF18" s="10" t="n">
-        <v>4491.92</v>
+        <v>4470.76</v>
       </c>
       <c r="AG18" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="AH18" s="10" t="n">
-        <v>4494.38</v>
+        <v>4463.7</v>
       </c>
       <c r="AI18" s="10" t="n">
-        <v>-9.84</v>
+        <v>28.24</v>
       </c>
       <c r="AJ18" s="10" t="inlineStr"/>
       <c r="AK18" s="10" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
       <c r="AM18" s="10" t="inlineStr"/>
       <c r="AN18" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO18" s="10" t="inlineStr"/>
@@ -3027,21 +3027,21 @@
       <c r="BE18" s="10" t="inlineStr"/>
       <c r="BF18" s="10" t="inlineStr"/>
       <c r="BG18" s="11" t="n">
-        <v>46172.20594907407</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH18" s="10" t="n">
-        <v>4541.96</v>
+        <v>4453</v>
       </c>
       <c r="BI18" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>3512.43</v>
+        <v>1044.42</v>
       </c>
       <c r="BK18" s="10" t="n">
-        <v>47.58</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="19">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr"/>
@@ -3083,24 +3083,24 @@
       <c r="AB19" s="10" t="inlineStr"/>
       <c r="AC19" s="10" t="inlineStr"/>
       <c r="AD19" s="11" t="n">
-        <v>46174.79583333333</v>
+        <v>46178.33402777778</v>
       </c>
       <c r="AE19" s="11" t="n">
-        <v>46174.83541666667</v>
+        <v>46178.35138888889</v>
       </c>
       <c r="AF19" s="10" t="n">
-        <v>4496.2</v>
+        <v>4450.29</v>
       </c>
       <c r="AG19" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH19" s="10" t="n">
-        <v>4507.83</v>
+        <v>4464.44</v>
       </c>
       <c r="AI19" s="10" t="n">
-        <v>46.52</v>
+        <v>-56.6</v>
       </c>
       <c r="AJ19" s="10" t="inlineStr"/>
       <c r="AK19" s="10" t="inlineStr"/>
@@ -3108,7 +3108,7 @@
       <c r="AM19" s="10" t="inlineStr"/>
       <c r="AN19" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO19" s="10" t="inlineStr"/>
@@ -3130,21 +3130,21 @@
       <c r="BE19" s="10" t="inlineStr"/>
       <c r="BF19" s="10" t="inlineStr"/>
       <c r="BG19" s="11" t="n">
-        <v>46174.30836805556</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH19" s="10" t="n">
-        <v>4541.35</v>
+        <v>4453</v>
       </c>
       <c r="BI19" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ19" s="10" t="n">
-        <v>701.95</v>
+        <v>84.42</v>
       </c>
       <c r="BK19" s="10" t="n">
-        <v>33.52</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="20">
@@ -3186,24 +3186,24 @@
       <c r="AB20" s="10" t="inlineStr"/>
       <c r="AC20" s="10" t="inlineStr"/>
       <c r="AD20" s="11" t="n">
-        <v>46175.62569444445</v>
+        <v>46179.00208333333</v>
       </c>
       <c r="AE20" s="11" t="n">
-        <v>46175.82847222222</v>
+        <v>46179.05138888889</v>
       </c>
       <c r="AF20" s="10" t="n">
-        <v>4516.97</v>
+        <v>4322.93</v>
       </c>
       <c r="AG20" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH20" s="10" t="n">
-        <v>4530.94</v>
+        <v>4340.18</v>
       </c>
       <c r="AI20" s="10" t="n">
-        <v>55.88</v>
+        <v>-69</v>
       </c>
       <c r="AJ20" s="10" t="inlineStr"/>
       <c r="AK20" s="10" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       <c r="AM20" s="10" t="inlineStr"/>
       <c r="AN20" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO20" s="10" t="inlineStr"/>
@@ -3233,1364 +3233,25 @@
       <c r="BE20" s="10" t="inlineStr"/>
       <c r="BF20" s="10" t="inlineStr"/>
       <c r="BG20" s="11" t="n">
-        <v>46174.30836805556</v>
+        <v>46179.17710648148</v>
       </c>
       <c r="BH20" s="10" t="n">
-        <v>4541.35</v>
+        <v>4315.54</v>
       </c>
       <c r="BI20" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>PD Zone fill rou</t>
         </is>
       </c>
       <c r="BJ20" s="10" t="n">
-        <v>1896.95</v>
+        <v>252.03</v>
       </c>
       <c r="BK20" s="10" t="n">
-        <v>10.41</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr"/>
-      <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="10" t="inlineStr"/>
-      <c r="Q21" s="10" t="inlineStr"/>
-      <c r="R21" s="10" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr"/>
-      <c r="T21" s="10" t="inlineStr"/>
-      <c r="U21" s="10" t="inlineStr"/>
-      <c r="V21" s="10" t="inlineStr"/>
-      <c r="W21" s="10" t="inlineStr"/>
-      <c r="X21" s="10" t="inlineStr"/>
-      <c r="Y21" s="10" t="inlineStr"/>
-      <c r="Z21" s="10" t="inlineStr"/>
-      <c r="AA21" s="10" t="inlineStr"/>
-      <c r="AB21" s="10" t="inlineStr"/>
-      <c r="AC21" s="10" t="inlineStr"/>
-      <c r="AD21" s="11" t="n">
-        <v>46175.72291666667</v>
-      </c>
-      <c r="AE21" s="11" t="n">
-        <v>46175.82430555556</v>
-      </c>
-      <c r="AF21" s="10" t="n">
-        <v>4521.52</v>
-      </c>
-      <c r="AG21" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH21" s="10" t="n">
-        <v>4526.71</v>
-      </c>
-      <c r="AI21" s="10" t="n">
-        <v>-20.76</v>
-      </c>
-      <c r="AJ21" s="10" t="inlineStr"/>
-      <c r="AK21" s="10" t="inlineStr"/>
-      <c r="AL21" s="10" t="inlineStr"/>
-      <c r="AM21" s="10" t="inlineStr"/>
-      <c r="AN21" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO21" s="10" t="inlineStr"/>
-      <c r="AP21" s="10" t="inlineStr"/>
-      <c r="AQ21" s="10" t="inlineStr"/>
-      <c r="AR21" s="10" t="inlineStr"/>
-      <c r="AS21" s="10" t="inlineStr"/>
-      <c r="AT21" s="10" t="inlineStr"/>
-      <c r="AU21" s="10" t="inlineStr"/>
-      <c r="AV21" s="10" t="inlineStr"/>
-      <c r="AW21" s="10" t="inlineStr"/>
-      <c r="AX21" s="10" t="inlineStr"/>
-      <c r="AY21" s="10" t="inlineStr"/>
-      <c r="AZ21" s="10" t="inlineStr"/>
-      <c r="BA21" s="10" t="inlineStr"/>
-      <c r="BB21" s="10" t="inlineStr"/>
-      <c r="BC21" s="10" t="inlineStr"/>
-      <c r="BD21" s="10" t="inlineStr"/>
-      <c r="BE21" s="10" t="inlineStr"/>
-      <c r="BF21" s="10" t="inlineStr"/>
-      <c r="BG21" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH21" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI21" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="10" t="n">
-        <v>3844.42</v>
-      </c>
-      <c r="BK21" s="10" t="n">
-        <v>73.70999999999999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr"/>
-      <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="10" t="inlineStr"/>
-      <c r="P22" s="10" t="inlineStr"/>
-      <c r="Q22" s="10" t="inlineStr"/>
-      <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
-      <c r="T22" s="10" t="inlineStr"/>
-      <c r="U22" s="10" t="inlineStr"/>
-      <c r="V22" s="10" t="inlineStr"/>
-      <c r="W22" s="10" t="inlineStr"/>
-      <c r="X22" s="10" t="inlineStr"/>
-      <c r="Y22" s="10" t="inlineStr"/>
-      <c r="Z22" s="10" t="inlineStr"/>
-      <c r="AA22" s="10" t="inlineStr"/>
-      <c r="AB22" s="10" t="inlineStr"/>
-      <c r="AC22" s="10" t="inlineStr"/>
-      <c r="AD22" s="11" t="n">
-        <v>46177.01944444444</v>
-      </c>
-      <c r="AE22" s="11" t="n">
-        <v>46177.14791666667</v>
-      </c>
-      <c r="AF22" s="10" t="n">
-        <v>4433.27</v>
-      </c>
-      <c r="AG22" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH22" s="10" t="n">
-        <v>4439.15</v>
-      </c>
-      <c r="AI22" s="10" t="n">
-        <v>-23.52</v>
-      </c>
-      <c r="AJ22" s="10" t="inlineStr"/>
-      <c r="AK22" s="10" t="inlineStr"/>
-      <c r="AL22" s="10" t="inlineStr"/>
-      <c r="AM22" s="10" t="inlineStr"/>
-      <c r="AN22" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO22" s="10" t="inlineStr"/>
-      <c r="AP22" s="10" t="inlineStr"/>
-      <c r="AQ22" s="10" t="inlineStr"/>
-      <c r="AR22" s="10" t="inlineStr"/>
-      <c r="AS22" s="10" t="inlineStr"/>
-      <c r="AT22" s="10" t="inlineStr"/>
-      <c r="AU22" s="10" t="inlineStr"/>
-      <c r="AV22" s="10" t="inlineStr"/>
-      <c r="AW22" s="10" t="inlineStr"/>
-      <c r="AX22" s="10" t="inlineStr"/>
-      <c r="AY22" s="10" t="inlineStr"/>
-      <c r="AZ22" s="10" t="inlineStr"/>
-      <c r="BA22" s="10" t="inlineStr"/>
-      <c r="BB22" s="10" t="inlineStr"/>
-      <c r="BC22" s="10" t="inlineStr"/>
-      <c r="BD22" s="10" t="inlineStr"/>
-      <c r="BE22" s="10" t="inlineStr"/>
-      <c r="BF22" s="10" t="inlineStr"/>
-      <c r="BG22" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH22" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI22" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="10" t="n">
-        <v>1977.42</v>
-      </c>
-      <c r="BK22" s="10" t="n">
-        <v>13.85</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr"/>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="10" t="inlineStr"/>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="10" t="inlineStr"/>
-      <c r="Q23" s="10" t="inlineStr"/>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
-      <c r="T23" s="10" t="inlineStr"/>
-      <c r="U23" s="10" t="inlineStr"/>
-      <c r="V23" s="10" t="inlineStr"/>
-      <c r="W23" s="10" t="inlineStr"/>
-      <c r="X23" s="10" t="inlineStr"/>
-      <c r="Y23" s="10" t="inlineStr"/>
-      <c r="Z23" s="10" t="inlineStr"/>
-      <c r="AA23" s="10" t="inlineStr"/>
-      <c r="AB23" s="10" t="inlineStr"/>
-      <c r="AC23" s="10" t="inlineStr"/>
-      <c r="AD23" s="11" t="n">
-        <v>46177.33402777778</v>
-      </c>
-      <c r="AE23" s="11" t="n">
-        <v>46177.34166666667</v>
-      </c>
-      <c r="AF23" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG23" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH23" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI23" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ23" s="10" t="inlineStr"/>
-      <c r="AK23" s="10" t="inlineStr"/>
-      <c r="AL23" s="10" t="inlineStr"/>
-      <c r="AM23" s="10" t="inlineStr"/>
-      <c r="AN23" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO23" s="10" t="inlineStr"/>
-      <c r="AP23" s="10" t="inlineStr"/>
-      <c r="AQ23" s="10" t="inlineStr"/>
-      <c r="AR23" s="10" t="inlineStr"/>
-      <c r="AS23" s="10" t="inlineStr"/>
-      <c r="AT23" s="10" t="inlineStr"/>
-      <c r="AU23" s="10" t="inlineStr"/>
-      <c r="AV23" s="10" t="inlineStr"/>
-      <c r="AW23" s="10" t="inlineStr"/>
-      <c r="AX23" s="10" t="inlineStr"/>
-      <c r="AY23" s="10" t="inlineStr"/>
-      <c r="AZ23" s="10" t="inlineStr"/>
-      <c r="BA23" s="10" t="inlineStr"/>
-      <c r="BB23" s="10" t="inlineStr"/>
-      <c r="BC23" s="10" t="inlineStr"/>
-      <c r="BD23" s="10" t="inlineStr"/>
-      <c r="BE23" s="10" t="inlineStr"/>
-      <c r="BF23" s="10" t="inlineStr"/>
-      <c r="BG23" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH23" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI23" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="10" t="n">
-        <v>4356.95</v>
-      </c>
-      <c r="BK23" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="10" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr"/>
-      <c r="O24" s="10" t="inlineStr"/>
-      <c r="P24" s="10" t="inlineStr"/>
-      <c r="Q24" s="10" t="inlineStr"/>
-      <c r="R24" s="10" t="inlineStr"/>
-      <c r="S24" s="10" t="inlineStr"/>
-      <c r="T24" s="10" t="inlineStr"/>
-      <c r="U24" s="10" t="inlineStr"/>
-      <c r="V24" s="10" t="inlineStr"/>
-      <c r="W24" s="10" t="inlineStr"/>
-      <c r="X24" s="10" t="inlineStr"/>
-      <c r="Y24" s="10" t="inlineStr"/>
-      <c r="Z24" s="10" t="inlineStr"/>
-      <c r="AA24" s="10" t="inlineStr"/>
-      <c r="AB24" s="10" t="inlineStr"/>
-      <c r="AC24" s="10" t="inlineStr"/>
-      <c r="AD24" s="11" t="n">
-        <v>46177.34583333333</v>
-      </c>
-      <c r="AE24" s="11" t="n">
-        <v>46177.34722222222</v>
-      </c>
-      <c r="AF24" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG24" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH24" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI24" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ24" s="10" t="inlineStr"/>
-      <c r="AK24" s="10" t="inlineStr"/>
-      <c r="AL24" s="10" t="inlineStr"/>
-      <c r="AM24" s="10" t="inlineStr"/>
-      <c r="AN24" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO24" s="10" t="inlineStr"/>
-      <c r="AP24" s="10" t="inlineStr"/>
-      <c r="AQ24" s="10" t="inlineStr"/>
-      <c r="AR24" s="10" t="inlineStr"/>
-      <c r="AS24" s="10" t="inlineStr"/>
-      <c r="AT24" s="10" t="inlineStr"/>
-      <c r="AU24" s="10" t="inlineStr"/>
-      <c r="AV24" s="10" t="inlineStr"/>
-      <c r="AW24" s="10" t="inlineStr"/>
-      <c r="AX24" s="10" t="inlineStr"/>
-      <c r="AY24" s="10" t="inlineStr"/>
-      <c r="AZ24" s="10" t="inlineStr"/>
-      <c r="BA24" s="10" t="inlineStr"/>
-      <c r="BB24" s="10" t="inlineStr"/>
-      <c r="BC24" s="10" t="inlineStr"/>
-      <c r="BD24" s="10" t="inlineStr"/>
-      <c r="BE24" s="10" t="inlineStr"/>
-      <c r="BF24" s="10" t="inlineStr"/>
-      <c r="BG24" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH24" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI24" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ24" s="10" t="n">
-        <v>4373.95</v>
-      </c>
-      <c r="BK24" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="10" t="inlineStr"/>
-      <c r="P25" s="10" t="inlineStr"/>
-      <c r="Q25" s="10" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
-      <c r="T25" s="10" t="inlineStr"/>
-      <c r="U25" s="10" t="inlineStr"/>
-      <c r="V25" s="10" t="inlineStr"/>
-      <c r="W25" s="10" t="inlineStr"/>
-      <c r="X25" s="10" t="inlineStr"/>
-      <c r="Y25" s="10" t="inlineStr"/>
-      <c r="Z25" s="10" t="inlineStr"/>
-      <c r="AA25" s="10" t="inlineStr"/>
-      <c r="AB25" s="10" t="inlineStr"/>
-      <c r="AC25" s="10" t="inlineStr"/>
-      <c r="AD25" s="11" t="n">
-        <v>46177.35347222222</v>
-      </c>
-      <c r="AE25" s="11" t="n">
-        <v>46177.35416666666</v>
-      </c>
-      <c r="AF25" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG25" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH25" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI25" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ25" s="10" t="inlineStr"/>
-      <c r="AK25" s="10" t="inlineStr"/>
-      <c r="AL25" s="10" t="inlineStr"/>
-      <c r="AM25" s="10" t="inlineStr"/>
-      <c r="AN25" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO25" s="10" t="inlineStr"/>
-      <c r="AP25" s="10" t="inlineStr"/>
-      <c r="AQ25" s="10" t="inlineStr"/>
-      <c r="AR25" s="10" t="inlineStr"/>
-      <c r="AS25" s="10" t="inlineStr"/>
-      <c r="AT25" s="10" t="inlineStr"/>
-      <c r="AU25" s="10" t="inlineStr"/>
-      <c r="AV25" s="10" t="inlineStr"/>
-      <c r="AW25" s="10" t="inlineStr"/>
-      <c r="AX25" s="10" t="inlineStr"/>
-      <c r="AY25" s="10" t="inlineStr"/>
-      <c r="AZ25" s="10" t="inlineStr"/>
-      <c r="BA25" s="10" t="inlineStr"/>
-      <c r="BB25" s="10" t="inlineStr"/>
-      <c r="BC25" s="10" t="inlineStr"/>
-      <c r="BD25" s="10" t="inlineStr"/>
-      <c r="BE25" s="10" t="inlineStr"/>
-      <c r="BF25" s="10" t="inlineStr"/>
-      <c r="BG25" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH25" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI25" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ25" s="10" t="n">
-        <v>4384.95</v>
-      </c>
-      <c r="BK25" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr"/>
-      <c r="L26" s="10" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="10" t="inlineStr"/>
-      <c r="P26" s="10" t="inlineStr"/>
-      <c r="Q26" s="10" t="inlineStr"/>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
-      <c r="T26" s="10" t="inlineStr"/>
-      <c r="U26" s="10" t="inlineStr"/>
-      <c r="V26" s="10" t="inlineStr"/>
-      <c r="W26" s="10" t="inlineStr"/>
-      <c r="X26" s="10" t="inlineStr"/>
-      <c r="Y26" s="10" t="inlineStr"/>
-      <c r="Z26" s="10" t="inlineStr"/>
-      <c r="AA26" s="10" t="inlineStr"/>
-      <c r="AB26" s="10" t="inlineStr"/>
-      <c r="AC26" s="10" t="inlineStr"/>
-      <c r="AD26" s="11" t="n">
-        <v>46177.3625</v>
-      </c>
-      <c r="AE26" s="11" t="n">
-        <v>46177.36597222222</v>
-      </c>
-      <c r="AF26" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG26" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH26" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI26" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ26" s="10" t="inlineStr"/>
-      <c r="AK26" s="10" t="inlineStr"/>
-      <c r="AL26" s="10" t="inlineStr"/>
-      <c r="AM26" s="10" t="inlineStr"/>
-      <c r="AN26" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO26" s="10" t="inlineStr"/>
-      <c r="AP26" s="10" t="inlineStr"/>
-      <c r="AQ26" s="10" t="inlineStr"/>
-      <c r="AR26" s="10" t="inlineStr"/>
-      <c r="AS26" s="10" t="inlineStr"/>
-      <c r="AT26" s="10" t="inlineStr"/>
-      <c r="AU26" s="10" t="inlineStr"/>
-      <c r="AV26" s="10" t="inlineStr"/>
-      <c r="AW26" s="10" t="inlineStr"/>
-      <c r="AX26" s="10" t="inlineStr"/>
-      <c r="AY26" s="10" t="inlineStr"/>
-      <c r="AZ26" s="10" t="inlineStr"/>
-      <c r="BA26" s="10" t="inlineStr"/>
-      <c r="BB26" s="10" t="inlineStr"/>
-      <c r="BC26" s="10" t="inlineStr"/>
-      <c r="BD26" s="10" t="inlineStr"/>
-      <c r="BE26" s="10" t="inlineStr"/>
-      <c r="BF26" s="10" t="inlineStr"/>
-      <c r="BG26" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH26" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI26" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ26" s="10" t="n">
-        <v>4397.95</v>
-      </c>
-      <c r="BK26" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr"/>
-      <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" s="10" t="inlineStr"/>
-      <c r="O27" s="10" t="inlineStr"/>
-      <c r="P27" s="10" t="inlineStr"/>
-      <c r="Q27" s="10" t="inlineStr"/>
-      <c r="R27" s="10" t="inlineStr"/>
-      <c r="S27" s="10" t="inlineStr"/>
-      <c r="T27" s="10" t="inlineStr"/>
-      <c r="U27" s="10" t="inlineStr"/>
-      <c r="V27" s="10" t="inlineStr"/>
-      <c r="W27" s="10" t="inlineStr"/>
-      <c r="X27" s="10" t="inlineStr"/>
-      <c r="Y27" s="10" t="inlineStr"/>
-      <c r="Z27" s="10" t="inlineStr"/>
-      <c r="AA27" s="10" t="inlineStr"/>
-      <c r="AB27" s="10" t="inlineStr"/>
-      <c r="AC27" s="10" t="inlineStr"/>
-      <c r="AD27" s="11" t="n">
-        <v>46177.37152777778</v>
-      </c>
-      <c r="AE27" s="11" t="n">
-        <v>46177.37222222222</v>
-      </c>
-      <c r="AF27" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG27" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH27" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI27" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ27" s="10" t="inlineStr"/>
-      <c r="AK27" s="10" t="inlineStr"/>
-      <c r="AL27" s="10" t="inlineStr"/>
-      <c r="AM27" s="10" t="inlineStr"/>
-      <c r="AN27" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO27" s="10" t="inlineStr"/>
-      <c r="AP27" s="10" t="inlineStr"/>
-      <c r="AQ27" s="10" t="inlineStr"/>
-      <c r="AR27" s="10" t="inlineStr"/>
-      <c r="AS27" s="10" t="inlineStr"/>
-      <c r="AT27" s="10" t="inlineStr"/>
-      <c r="AU27" s="10" t="inlineStr"/>
-      <c r="AV27" s="10" t="inlineStr"/>
-      <c r="AW27" s="10" t="inlineStr"/>
-      <c r="AX27" s="10" t="inlineStr"/>
-      <c r="AY27" s="10" t="inlineStr"/>
-      <c r="AZ27" s="10" t="inlineStr"/>
-      <c r="BA27" s="10" t="inlineStr"/>
-      <c r="BB27" s="10" t="inlineStr"/>
-      <c r="BC27" s="10" t="inlineStr"/>
-      <c r="BD27" s="10" t="inlineStr"/>
-      <c r="BE27" s="10" t="inlineStr"/>
-      <c r="BF27" s="10" t="inlineStr"/>
-      <c r="BG27" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH27" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI27" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ27" s="10" t="n">
-        <v>4410.95</v>
-      </c>
-      <c r="BK27" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr"/>
-      <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr"/>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
-      <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" s="10" t="inlineStr"/>
-      <c r="O28" s="10" t="inlineStr"/>
-      <c r="P28" s="10" t="inlineStr"/>
-      <c r="Q28" s="10" t="inlineStr"/>
-      <c r="R28" s="10" t="inlineStr"/>
-      <c r="S28" s="10" t="inlineStr"/>
-      <c r="T28" s="10" t="inlineStr"/>
-      <c r="U28" s="10" t="inlineStr"/>
-      <c r="V28" s="10" t="inlineStr"/>
-      <c r="W28" s="10" t="inlineStr"/>
-      <c r="X28" s="10" t="inlineStr"/>
-      <c r="Y28" s="10" t="inlineStr"/>
-      <c r="Z28" s="10" t="inlineStr"/>
-      <c r="AA28" s="10" t="inlineStr"/>
-      <c r="AB28" s="10" t="inlineStr"/>
-      <c r="AC28" s="10" t="inlineStr"/>
-      <c r="AD28" s="11" t="n">
-        <v>46177.66736111111</v>
-      </c>
-      <c r="AE28" s="11" t="n">
-        <v>46177.7</v>
-      </c>
-      <c r="AF28" s="10" t="n">
-        <v>4470.76</v>
-      </c>
-      <c r="AG28" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH28" s="10" t="n">
-        <v>4463.7</v>
-      </c>
-      <c r="AI28" s="10" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="AJ28" s="10" t="inlineStr"/>
-      <c r="AK28" s="10" t="inlineStr"/>
-      <c r="AL28" s="10" t="inlineStr"/>
-      <c r="AM28" s="10" t="inlineStr"/>
-      <c r="AN28" s="10" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO28" s="10" t="inlineStr"/>
-      <c r="AP28" s="10" t="inlineStr"/>
-      <c r="AQ28" s="10" t="inlineStr"/>
-      <c r="AR28" s="10" t="inlineStr"/>
-      <c r="AS28" s="10" t="inlineStr"/>
-      <c r="AT28" s="10" t="inlineStr"/>
-      <c r="AU28" s="10" t="inlineStr"/>
-      <c r="AV28" s="10" t="inlineStr"/>
-      <c r="AW28" s="10" t="inlineStr"/>
-      <c r="AX28" s="10" t="inlineStr"/>
-      <c r="AY28" s="10" t="inlineStr"/>
-      <c r="AZ28" s="10" t="inlineStr"/>
-      <c r="BA28" s="10" t="inlineStr"/>
-      <c r="BB28" s="10" t="inlineStr"/>
-      <c r="BC28" s="10" t="inlineStr"/>
-      <c r="BD28" s="10" t="inlineStr"/>
-      <c r="BE28" s="10" t="inlineStr"/>
-      <c r="BF28" s="10" t="inlineStr"/>
-      <c r="BG28" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH28" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI28" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ28" s="10" t="n">
-        <v>1044.42</v>
-      </c>
-      <c r="BK28" s="10" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr"/>
-      <c r="D29" s="10" t="inlineStr"/>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="10" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" s="10" t="inlineStr"/>
-      <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="10" t="inlineStr"/>
-      <c r="Q29" s="10" t="inlineStr"/>
-      <c r="R29" s="10" t="inlineStr"/>
-      <c r="S29" s="10" t="inlineStr"/>
-      <c r="T29" s="10" t="inlineStr"/>
-      <c r="U29" s="10" t="inlineStr"/>
-      <c r="V29" s="10" t="inlineStr"/>
-      <c r="W29" s="10" t="inlineStr"/>
-      <c r="X29" s="10" t="inlineStr"/>
-      <c r="Y29" s="10" t="inlineStr"/>
-      <c r="Z29" s="10" t="inlineStr"/>
-      <c r="AA29" s="10" t="inlineStr"/>
-      <c r="AB29" s="10" t="inlineStr"/>
-      <c r="AC29" s="10" t="inlineStr"/>
-      <c r="AD29" s="11" t="n">
-        <v>46178.33402777778</v>
-      </c>
-      <c r="AE29" s="11" t="n">
-        <v>46178.35138888889</v>
-      </c>
-      <c r="AF29" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG29" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH29" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI29" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ29" s="10" t="inlineStr"/>
-      <c r="AK29" s="10" t="inlineStr"/>
-      <c r="AL29" s="10" t="inlineStr"/>
-      <c r="AM29" s="10" t="inlineStr"/>
-      <c r="AN29" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO29" s="10" t="inlineStr"/>
-      <c r="AP29" s="10" t="inlineStr"/>
-      <c r="AQ29" s="10" t="inlineStr"/>
-      <c r="AR29" s="10" t="inlineStr"/>
-      <c r="AS29" s="10" t="inlineStr"/>
-      <c r="AT29" s="10" t="inlineStr"/>
-      <c r="AU29" s="10" t="inlineStr"/>
-      <c r="AV29" s="10" t="inlineStr"/>
-      <c r="AW29" s="10" t="inlineStr"/>
-      <c r="AX29" s="10" t="inlineStr"/>
-      <c r="AY29" s="10" t="inlineStr"/>
-      <c r="AZ29" s="10" t="inlineStr"/>
-      <c r="BA29" s="10" t="inlineStr"/>
-      <c r="BB29" s="10" t="inlineStr"/>
-      <c r="BC29" s="10" t="inlineStr"/>
-      <c r="BD29" s="10" t="inlineStr"/>
-      <c r="BE29" s="10" t="inlineStr"/>
-      <c r="BF29" s="10" t="inlineStr"/>
-      <c r="BG29" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH29" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI29" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ29" s="10" t="n">
-        <v>84.42</v>
-      </c>
-      <c r="BK29" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr"/>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr"/>
-      <c r="G30" s="10" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
-      <c r="K30" s="10" t="inlineStr"/>
-      <c r="L30" s="10" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" s="10" t="inlineStr"/>
-      <c r="O30" s="10" t="inlineStr"/>
-      <c r="P30" s="10" t="inlineStr"/>
-      <c r="Q30" s="10" t="inlineStr"/>
-      <c r="R30" s="10" t="inlineStr"/>
-      <c r="S30" s="10" t="inlineStr"/>
-      <c r="T30" s="10" t="inlineStr"/>
-      <c r="U30" s="10" t="inlineStr"/>
-      <c r="V30" s="10" t="inlineStr"/>
-      <c r="W30" s="10" t="inlineStr"/>
-      <c r="X30" s="10" t="inlineStr"/>
-      <c r="Y30" s="10" t="inlineStr"/>
-      <c r="Z30" s="10" t="inlineStr"/>
-      <c r="AA30" s="10" t="inlineStr"/>
-      <c r="AB30" s="10" t="inlineStr"/>
-      <c r="AC30" s="10" t="inlineStr"/>
-      <c r="AD30" s="11" t="n">
-        <v>46178.35555555556</v>
-      </c>
-      <c r="AE30" s="11" t="n">
-        <v>46178.36041666667</v>
-      </c>
-      <c r="AF30" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG30" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH30" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI30" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ30" s="10" t="inlineStr"/>
-      <c r="AK30" s="10" t="inlineStr"/>
-      <c r="AL30" s="10" t="inlineStr"/>
-      <c r="AM30" s="10" t="inlineStr"/>
-      <c r="AN30" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO30" s="10" t="inlineStr"/>
-      <c r="AP30" s="10" t="inlineStr"/>
-      <c r="AQ30" s="10" t="inlineStr"/>
-      <c r="AR30" s="10" t="inlineStr"/>
-      <c r="AS30" s="10" t="inlineStr"/>
-      <c r="AT30" s="10" t="inlineStr"/>
-      <c r="AU30" s="10" t="inlineStr"/>
-      <c r="AV30" s="10" t="inlineStr"/>
-      <c r="AW30" s="10" t="inlineStr"/>
-      <c r="AX30" s="10" t="inlineStr"/>
-      <c r="AY30" s="10" t="inlineStr"/>
-      <c r="AZ30" s="10" t="inlineStr"/>
-      <c r="BA30" s="10" t="inlineStr"/>
-      <c r="BB30" s="10" t="inlineStr"/>
-      <c r="BC30" s="10" t="inlineStr"/>
-      <c r="BD30" s="10" t="inlineStr"/>
-      <c r="BE30" s="10" t="inlineStr"/>
-      <c r="BF30" s="10" t="inlineStr"/>
-      <c r="BG30" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH30" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI30" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ30" s="10" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="BK30" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr"/>
-      <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr"/>
-      <c r="P31" s="10" t="inlineStr"/>
-      <c r="Q31" s="10" t="inlineStr"/>
-      <c r="R31" s="10" t="inlineStr"/>
-      <c r="S31" s="10" t="inlineStr"/>
-      <c r="T31" s="10" t="inlineStr"/>
-      <c r="U31" s="10" t="inlineStr"/>
-      <c r="V31" s="10" t="inlineStr"/>
-      <c r="W31" s="10" t="inlineStr"/>
-      <c r="X31" s="10" t="inlineStr"/>
-      <c r="Y31" s="10" t="inlineStr"/>
-      <c r="Z31" s="10" t="inlineStr"/>
-      <c r="AA31" s="10" t="inlineStr"/>
-      <c r="AB31" s="10" t="inlineStr"/>
-      <c r="AC31" s="10" t="inlineStr"/>
-      <c r="AD31" s="11" t="n">
-        <v>46178.36875</v>
-      </c>
-      <c r="AE31" s="11" t="n">
-        <v>46178.36944444444</v>
-      </c>
-      <c r="AF31" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG31" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH31" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI31" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ31" s="10" t="inlineStr"/>
-      <c r="AK31" s="10" t="inlineStr"/>
-      <c r="AL31" s="10" t="inlineStr"/>
-      <c r="AM31" s="10" t="inlineStr"/>
-      <c r="AN31" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO31" s="10" t="inlineStr"/>
-      <c r="AP31" s="10" t="inlineStr"/>
-      <c r="AQ31" s="10" t="inlineStr"/>
-      <c r="AR31" s="10" t="inlineStr"/>
-      <c r="AS31" s="10" t="inlineStr"/>
-      <c r="AT31" s="10" t="inlineStr"/>
-      <c r="AU31" s="10" t="inlineStr"/>
-      <c r="AV31" s="10" t="inlineStr"/>
-      <c r="AW31" s="10" t="inlineStr"/>
-      <c r="AX31" s="10" t="inlineStr"/>
-      <c r="AY31" s="10" t="inlineStr"/>
-      <c r="AZ31" s="10" t="inlineStr"/>
-      <c r="BA31" s="10" t="inlineStr"/>
-      <c r="BB31" s="10" t="inlineStr"/>
-      <c r="BC31" s="10" t="inlineStr"/>
-      <c r="BD31" s="10" t="inlineStr"/>
-      <c r="BE31" s="10" t="inlineStr"/>
-      <c r="BF31" s="10" t="inlineStr"/>
-      <c r="BG31" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH31" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI31" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ31" s="10" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="BK31" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr"/>
-      <c r="L32" s="10" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" s="10" t="inlineStr"/>
-      <c r="O32" s="10" t="inlineStr"/>
-      <c r="P32" s="10" t="inlineStr"/>
-      <c r="Q32" s="10" t="inlineStr"/>
-      <c r="R32" s="10" t="inlineStr"/>
-      <c r="S32" s="10" t="inlineStr"/>
-      <c r="T32" s="10" t="inlineStr"/>
-      <c r="U32" s="10" t="inlineStr"/>
-      <c r="V32" s="10" t="inlineStr"/>
-      <c r="W32" s="10" t="inlineStr"/>
-      <c r="X32" s="10" t="inlineStr"/>
-      <c r="Y32" s="10" t="inlineStr"/>
-      <c r="Z32" s="10" t="inlineStr"/>
-      <c r="AA32" s="10" t="inlineStr"/>
-      <c r="AB32" s="10" t="inlineStr"/>
-      <c r="AC32" s="10" t="inlineStr"/>
-      <c r="AD32" s="11" t="n">
-        <v>46178.37361111111</v>
-      </c>
-      <c r="AE32" s="11" t="n">
-        <v>46178.37430555555</v>
-      </c>
-      <c r="AF32" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG32" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH32" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI32" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ32" s="10" t="inlineStr"/>
-      <c r="AK32" s="10" t="inlineStr"/>
-      <c r="AL32" s="10" t="inlineStr"/>
-      <c r="AM32" s="10" t="inlineStr"/>
-      <c r="AN32" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO32" s="10" t="inlineStr"/>
-      <c r="AP32" s="10" t="inlineStr"/>
-      <c r="AQ32" s="10" t="inlineStr"/>
-      <c r="AR32" s="10" t="inlineStr"/>
-      <c r="AS32" s="10" t="inlineStr"/>
-      <c r="AT32" s="10" t="inlineStr"/>
-      <c r="AU32" s="10" t="inlineStr"/>
-      <c r="AV32" s="10" t="inlineStr"/>
-      <c r="AW32" s="10" t="inlineStr"/>
-      <c r="AX32" s="10" t="inlineStr"/>
-      <c r="AY32" s="10" t="inlineStr"/>
-      <c r="AZ32" s="10" t="inlineStr"/>
-      <c r="BA32" s="10" t="inlineStr"/>
-      <c r="BB32" s="10" t="inlineStr"/>
-      <c r="BC32" s="10" t="inlineStr"/>
-      <c r="BD32" s="10" t="inlineStr"/>
-      <c r="BE32" s="10" t="inlineStr"/>
-      <c r="BF32" s="10" t="inlineStr"/>
-      <c r="BG32" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH32" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI32" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ32" s="10" t="n">
-        <v>27.42</v>
-      </c>
-      <c r="BK32" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr"/>
-      <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" s="10" t="inlineStr"/>
-      <c r="O33" s="10" t="inlineStr"/>
-      <c r="P33" s="10" t="inlineStr"/>
-      <c r="Q33" s="10" t="inlineStr"/>
-      <c r="R33" s="10" t="inlineStr"/>
-      <c r="S33" s="10" t="inlineStr"/>
-      <c r="T33" s="10" t="inlineStr"/>
-      <c r="U33" s="10" t="inlineStr"/>
-      <c r="V33" s="10" t="inlineStr"/>
-      <c r="W33" s="10" t="inlineStr"/>
-      <c r="X33" s="10" t="inlineStr"/>
-      <c r="Y33" s="10" t="inlineStr"/>
-      <c r="Z33" s="10" t="inlineStr"/>
-      <c r="AA33" s="10" t="inlineStr"/>
-      <c r="AB33" s="10" t="inlineStr"/>
-      <c r="AC33" s="10" t="inlineStr"/>
-      <c r="AD33" s="11" t="n">
-        <v>46179.00208333333</v>
-      </c>
-      <c r="AE33" s="11" t="n">
-        <v>46179.05138888889</v>
-      </c>
-      <c r="AF33" s="10" t="n">
-        <v>4322.93</v>
-      </c>
-      <c r="AG33" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH33" s="10" t="n">
-        <v>4340.18</v>
-      </c>
-      <c r="AI33" s="10" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AJ33" s="10" t="inlineStr"/>
-      <c r="AK33" s="10" t="inlineStr"/>
-      <c r="AL33" s="10" t="inlineStr"/>
-      <c r="AM33" s="10" t="inlineStr"/>
-      <c r="AN33" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO33" s="10" t="inlineStr"/>
-      <c r="AP33" s="10" t="inlineStr"/>
-      <c r="AQ33" s="10" t="inlineStr"/>
-      <c r="AR33" s="10" t="inlineStr"/>
-      <c r="AS33" s="10" t="inlineStr"/>
-      <c r="AT33" s="10" t="inlineStr"/>
-      <c r="AU33" s="10" t="inlineStr"/>
-      <c r="AV33" s="10" t="inlineStr"/>
-      <c r="AW33" s="10" t="inlineStr"/>
-      <c r="AX33" s="10" t="inlineStr"/>
-      <c r="AY33" s="10" t="inlineStr"/>
-      <c r="AZ33" s="10" t="inlineStr"/>
-      <c r="BA33" s="10" t="inlineStr"/>
-      <c r="BB33" s="10" t="inlineStr"/>
-      <c r="BC33" s="10" t="inlineStr"/>
-      <c r="BD33" s="10" t="inlineStr"/>
-      <c r="BE33" s="10" t="inlineStr"/>
-      <c r="BF33" s="10" t="inlineStr"/>
-      <c r="BG33" s="11" t="n">
-        <v>46179.17710648148</v>
-      </c>
-      <c r="BH33" s="10" t="n">
-        <v>4315.54</v>
-      </c>
-      <c r="BI33" s="10" t="inlineStr">
-        <is>
-          <t>PD Zone fill rou</t>
-        </is>
-      </c>
-      <c r="BJ33" s="10" t="n">
-        <v>252.03</v>
-      </c>
-      <c r="BK33" s="10" t="n">
         <v>24.64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK33"/>
+  <autoFilter ref="A1:BK20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5976,7 +4637,7 @@
       <c r="AZ5" s="10" t="inlineStr"/>
       <c r="BA5" s="10" t="inlineStr"/>
       <c r="BB5" s="11" t="n">
-        <v>46178.37361111111</v>
+        <v>46178.33402777778</v>
       </c>
       <c r="BC5" s="10" t="n">
         <v>4464.44</v>
@@ -5987,7 +4648,7 @@
         </is>
       </c>
       <c r="BE5" s="10" t="n">
-        <v>27.42</v>
+        <v>84.42</v>
       </c>
       <c r="BF5" s="10" t="n">
         <v>11.44</v>
@@ -6095,7 +4756,7 @@
       <c r="AZ6" s="10" t="inlineStr"/>
       <c r="BA6" s="10" t="inlineStr"/>
       <c r="BB6" s="11" t="n">
-        <v>46178.37361111111</v>
+        <v>46178.33402777778</v>
       </c>
       <c r="BC6" s="10" t="n">
         <v>4464.44</v>
@@ -6106,7 +4767,7 @@
         </is>
       </c>
       <c r="BE6" s="10" t="n">
-        <v>27.98</v>
+        <v>84.98</v>
       </c>
       <c r="BF6" s="10" t="n">
         <v>12.22</v>
@@ -6248,7 +4909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK26"/>
+  <dimension ref="A1:BK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6775,13 +5436,13 @@
       <c r="AB3" s="10" t="inlineStr"/>
       <c r="AC3" s="10" t="inlineStr"/>
       <c r="AD3" s="11" t="n">
-        <v>46171.04791666667</v>
+        <v>46171.33402777778</v>
       </c>
       <c r="AE3" s="11" t="n">
-        <v>46171.3375</v>
+        <v>46171.33611111111</v>
       </c>
       <c r="AF3" s="10" t="n">
-        <v>4500.15</v>
+        <v>4501.1</v>
       </c>
       <c r="AG3" s="10" t="inlineStr">
         <is>
@@ -6789,10 +5450,10 @@
         </is>
       </c>
       <c r="AH3" s="10" t="n">
-        <v>4505.02</v>
+        <v>4496.55</v>
       </c>
       <c r="AI3" s="10" t="n">
-        <v>19.48</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ3" s="10" t="inlineStr"/>
       <c r="AK3" s="10" t="inlineStr"/>
@@ -6800,7 +5461,7 @@
       <c r="AM3" s="10" t="inlineStr"/>
       <c r="AN3" s="10" t="inlineStr">
         <is>
-          <t>SL_GUARD_CLOSE</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO3" s="10" t="inlineStr"/>
@@ -6833,10 +5494,10 @@
         </is>
       </c>
       <c r="BJ3" s="10" t="n">
-        <v>292.87</v>
+        <v>704.87</v>
       </c>
       <c r="BK3" s="10" t="n">
-        <v>113.78</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="4">
@@ -6878,13 +5539,13 @@
       <c r="AB4" s="10" t="inlineStr"/>
       <c r="AC4" s="10" t="inlineStr"/>
       <c r="AD4" s="11" t="n">
-        <v>46171.33402777778</v>
+        <v>46171.75069444445</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>46171.33611111111</v>
+        <v>46171.82083333333</v>
       </c>
       <c r="AF4" s="10" t="n">
-        <v>4501.1</v>
+        <v>4513.3</v>
       </c>
       <c r="AG4" s="10" t="inlineStr">
         <is>
@@ -6892,10 +5553,10 @@
         </is>
       </c>
       <c r="AH4" s="10" t="n">
-        <v>4496.55</v>
+        <v>4537.98</v>
       </c>
       <c r="AI4" s="10" t="n">
-        <v>-18.2</v>
+        <v>98.72</v>
       </c>
       <c r="AJ4" s="10" t="inlineStr"/>
       <c r="AK4" s="10" t="inlineStr"/>
@@ -6903,7 +5564,7 @@
       <c r="AM4" s="10" t="inlineStr"/>
       <c r="AN4" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO4" s="10" t="inlineStr"/>
@@ -6936,10 +5597,10 @@
         </is>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>704.87</v>
+        <v>1304.87</v>
       </c>
       <c r="BK4" s="10" t="n">
-        <v>105.31</v>
+        <v>146.74</v>
       </c>
     </row>
     <row r="5">
@@ -6981,24 +5642,24 @@
       <c r="AB5" s="10" t="inlineStr"/>
       <c r="AC5" s="10" t="inlineStr"/>
       <c r="AD5" s="11" t="n">
-        <v>46171.33680555555</v>
+        <v>46174.62847222222</v>
       </c>
       <c r="AE5" s="11" t="n">
-        <v>46171.3375</v>
+        <v>46174.63611111111</v>
       </c>
       <c r="AF5" s="10" t="n">
-        <v>4501.1</v>
+        <v>4491.92</v>
       </c>
       <c r="AG5" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH5" s="10" t="n">
-        <v>4496.55</v>
+        <v>4494.38</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>-18.2</v>
+        <v>-9.84</v>
       </c>
       <c r="AJ5" s="10" t="inlineStr"/>
       <c r="AK5" s="10" t="inlineStr"/>
@@ -7028,21 +5689,21 @@
       <c r="BE5" s="10" t="inlineStr"/>
       <c r="BF5" s="10" t="inlineStr"/>
       <c r="BG5" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46172.20594907407</v>
       </c>
       <c r="BH5" s="10" t="n">
-        <v>4391.24</v>
+        <v>4541.96</v>
       </c>
       <c r="BI5" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4540.52]</t>
         </is>
       </c>
       <c r="BJ5" s="10" t="n">
-        <v>708.87</v>
+        <v>3488.43</v>
       </c>
       <c r="BK5" s="10" t="n">
-        <v>105.31</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="6">
@@ -7084,13 +5745,13 @@
       <c r="AB6" s="10" t="inlineStr"/>
       <c r="AC6" s="10" t="inlineStr"/>
       <c r="AD6" s="11" t="n">
-        <v>46171.35</v>
+        <v>46174.79583333333</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>46171.35069444445</v>
+        <v>46174.83541666667</v>
       </c>
       <c r="AF6" s="10" t="n">
-        <v>4501.1</v>
+        <v>4496.2</v>
       </c>
       <c r="AG6" s="10" t="inlineStr">
         <is>
@@ -7098,10 +5759,10 @@
         </is>
       </c>
       <c r="AH6" s="10" t="n">
-        <v>4496.55</v>
+        <v>4507.83</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>-18.2</v>
+        <v>46.52</v>
       </c>
       <c r="AJ6" s="10" t="inlineStr"/>
       <c r="AK6" s="10" t="inlineStr"/>
@@ -7109,7 +5770,7 @@
       <c r="AM6" s="10" t="inlineStr"/>
       <c r="AN6" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO6" s="10" t="inlineStr"/>
@@ -7131,21 +5792,21 @@
       <c r="BE6" s="10" t="inlineStr"/>
       <c r="BF6" s="10" t="inlineStr"/>
       <c r="BG6" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH6" s="10" t="n">
-        <v>4391.24</v>
+        <v>4541.35</v>
       </c>
       <c r="BI6" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ6" s="10" t="n">
-        <v>727.87</v>
+        <v>701.95</v>
       </c>
       <c r="BK6" s="10" t="n">
-        <v>105.31</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="7">
@@ -7187,13 +5848,13 @@
       <c r="AB7" s="10" t="inlineStr"/>
       <c r="AC7" s="10" t="inlineStr"/>
       <c r="AD7" s="11" t="n">
-        <v>46171.36736111111</v>
+        <v>46175.62569444445</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>46171.36805555555</v>
+        <v>46175.82847222222</v>
       </c>
       <c r="AF7" s="10" t="n">
-        <v>4501.1</v>
+        <v>4516.97</v>
       </c>
       <c r="AG7" s="10" t="inlineStr">
         <is>
@@ -7201,10 +5862,10 @@
         </is>
       </c>
       <c r="AH7" s="10" t="n">
-        <v>4496.55</v>
+        <v>4530.94</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>-18.2</v>
+        <v>55.88</v>
       </c>
       <c r="AJ7" s="10" t="inlineStr"/>
       <c r="AK7" s="10" t="inlineStr"/>
@@ -7212,7 +5873,7 @@
       <c r="AM7" s="10" t="inlineStr"/>
       <c r="AN7" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO7" s="10" t="inlineStr"/>
@@ -7234,21 +5895,21 @@
       <c r="BE7" s="10" t="inlineStr"/>
       <c r="BF7" s="10" t="inlineStr"/>
       <c r="BG7" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH7" s="10" t="n">
-        <v>4391.24</v>
+        <v>4541.35</v>
       </c>
       <c r="BI7" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ7" s="10" t="n">
-        <v>752.87</v>
+        <v>1896.95</v>
       </c>
       <c r="BK7" s="10" t="n">
-        <v>105.31</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="8">
@@ -7290,24 +5951,24 @@
       <c r="AB8" s="10" t="inlineStr"/>
       <c r="AC8" s="10" t="inlineStr"/>
       <c r="AD8" s="11" t="n">
-        <v>46171.75069444445</v>
+        <v>46175.72291666667</v>
       </c>
       <c r="AE8" s="11" t="n">
-        <v>46171.82083333333</v>
+        <v>46175.82430555556</v>
       </c>
       <c r="AF8" s="10" t="n">
-        <v>4513.3</v>
+        <v>4521.52</v>
       </c>
       <c r="AG8" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>4537.98</v>
+        <v>4526.71</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>98.72</v>
+        <v>-20.76</v>
       </c>
       <c r="AJ8" s="10" t="inlineStr"/>
       <c r="AK8" s="10" t="inlineStr"/>
@@ -7315,7 +5976,7 @@
       <c r="AM8" s="10" t="inlineStr"/>
       <c r="AN8" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO8" s="10" t="inlineStr"/>
@@ -7337,21 +5998,21 @@
       <c r="BE8" s="10" t="inlineStr"/>
       <c r="BF8" s="10" t="inlineStr"/>
       <c r="BG8" s="11" t="n">
-        <v>46170.84453703704</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH8" s="10" t="n">
-        <v>4391.24</v>
+        <v>4453</v>
       </c>
       <c r="BI8" s="10" t="inlineStr">
         <is>
-          <t>[tp 4381.00]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ8" s="10" t="n">
-        <v>1304.87</v>
+        <v>3844.42</v>
       </c>
       <c r="BK8" s="10" t="n">
-        <v>146.74</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -7393,13 +6054,13 @@
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="10" t="inlineStr"/>
       <c r="AD9" s="11" t="n">
-        <v>46174.62847222222</v>
+        <v>46177.01944444444</v>
       </c>
       <c r="AE9" s="11" t="n">
-        <v>46174.63611111111</v>
+        <v>46177.02083333334</v>
       </c>
       <c r="AF9" s="10" t="n">
-        <v>4491.92</v>
+        <v>4435.71</v>
       </c>
       <c r="AG9" s="10" t="inlineStr">
         <is>
@@ -7407,10 +6068,10 @@
         </is>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>4494.38</v>
+        <v>4439.15</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>-9.84</v>
+        <v>-13.76</v>
       </c>
       <c r="AJ9" s="10" t="inlineStr"/>
       <c r="AK9" s="10" t="inlineStr"/>
@@ -7418,7 +6079,7 @@
       <c r="AM9" s="10" t="inlineStr"/>
       <c r="AN9" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>SL_GUARD_CLOSE</t>
         </is>
       </c>
       <c r="AO9" s="10" t="inlineStr"/>
@@ -7440,21 +6101,21 @@
       <c r="BE9" s="10" t="inlineStr"/>
       <c r="BF9" s="10" t="inlineStr"/>
       <c r="BG9" s="11" t="n">
-        <v>46172.20594907407</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH9" s="10" t="n">
-        <v>4541.96</v>
+        <v>4453</v>
       </c>
       <c r="BI9" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>3488.43</v>
+        <v>1977.42</v>
       </c>
       <c r="BK9" s="10" t="n">
-        <v>47.58</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="10">
@@ -7496,24 +6157,24 @@
       <c r="AB10" s="10" t="inlineStr"/>
       <c r="AC10" s="10" t="inlineStr"/>
       <c r="AD10" s="11" t="n">
-        <v>46174.64027777778</v>
+        <v>46177.33402777778</v>
       </c>
       <c r="AE10" s="11" t="n">
-        <v>46174.64097222222</v>
+        <v>46177.34166666667</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>4491.92</v>
+        <v>4465.22</v>
       </c>
       <c r="AG10" s="10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH10" s="10" t="n">
-        <v>4494.38</v>
+        <v>4451.86</v>
       </c>
       <c r="AI10" s="10" t="n">
-        <v>-9.84</v>
+        <v>-53.44</v>
       </c>
       <c r="AJ10" s="10" t="inlineStr"/>
       <c r="AK10" s="10" t="inlineStr"/>
@@ -7543,21 +6204,21 @@
       <c r="BE10" s="10" t="inlineStr"/>
       <c r="BF10" s="10" t="inlineStr"/>
       <c r="BG10" s="11" t="n">
-        <v>46172.20594907407</v>
+        <v>46174.30836805556</v>
       </c>
       <c r="BH10" s="10" t="n">
-        <v>4541.96</v>
+        <v>4541.35</v>
       </c>
       <c r="BI10" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[sl 4543.72]</t>
         </is>
       </c>
       <c r="BJ10" s="10" t="n">
-        <v>3505.43</v>
+        <v>4356.95</v>
       </c>
       <c r="BK10" s="10" t="n">
-        <v>47.58</v>
+        <v>89.48999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -7599,13 +6260,13 @@
       <c r="AB11" s="10" t="inlineStr"/>
       <c r="AC11" s="10" t="inlineStr"/>
       <c r="AD11" s="11" t="n">
-        <v>46174.64513888889</v>
+        <v>46177.66736111111</v>
       </c>
       <c r="AE11" s="11" t="n">
-        <v>46174.68888888889</v>
+        <v>46177.7</v>
       </c>
       <c r="AF11" s="10" t="n">
-        <v>4491.92</v>
+        <v>4470.76</v>
       </c>
       <c r="AG11" s="10" t="inlineStr">
         <is>
@@ -7613,10 +6274,10 @@
         </is>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>4494.38</v>
+        <v>4463.7</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>-9.84</v>
+        <v>28.24</v>
       </c>
       <c r="AJ11" s="10" t="inlineStr"/>
       <c r="AK11" s="10" t="inlineStr"/>
@@ -7624,7 +6285,7 @@
       <c r="AM11" s="10" t="inlineStr"/>
       <c r="AN11" s="10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO11" s="10" t="inlineStr"/>
@@ -7646,21 +6307,21 @@
       <c r="BE11" s="10" t="inlineStr"/>
       <c r="BF11" s="10" t="inlineStr"/>
       <c r="BG11" s="11" t="n">
-        <v>46172.20594907407</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH11" s="10" t="n">
-        <v>4541.96</v>
+        <v>4453</v>
       </c>
       <c r="BI11" s="10" t="inlineStr">
         <is>
-          <t>[sl 4540.52]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ11" s="10" t="n">
-        <v>3512.43</v>
+        <v>1044.42</v>
       </c>
       <c r="BK11" s="10" t="n">
-        <v>47.58</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="12">
@@ -7671,7 +6332,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
+          <t>ENTRY_TOO_FAR</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr"/>
@@ -7702,24 +6363,24 @@
       <c r="AB12" s="10" t="inlineStr"/>
       <c r="AC12" s="10" t="inlineStr"/>
       <c r="AD12" s="11" t="n">
-        <v>46174.79583333333</v>
+        <v>46178.33402777778</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>46174.83541666667</v>
+        <v>46178.35138888889</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>4496.2</v>
+        <v>4450.29</v>
       </c>
       <c r="AG12" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>4507.83</v>
+        <v>4464.44</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>46.52</v>
+        <v>-56.6</v>
       </c>
       <c r="AJ12" s="10" t="inlineStr"/>
       <c r="AK12" s="10" t="inlineStr"/>
@@ -7727,7 +6388,7 @@
       <c r="AM12" s="10" t="inlineStr"/>
       <c r="AN12" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO12" s="10" t="inlineStr"/>
@@ -7749,21 +6410,21 @@
       <c r="BE12" s="10" t="inlineStr"/>
       <c r="BF12" s="10" t="inlineStr"/>
       <c r="BG12" s="11" t="n">
-        <v>46174.30836805556</v>
+        <v>46178.39265046296</v>
       </c>
       <c r="BH12" s="10" t="n">
-        <v>4541.35</v>
+        <v>4453</v>
       </c>
       <c r="BI12" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>[sl 4450.29]</t>
         </is>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>701.95</v>
+        <v>84.42</v>
       </c>
       <c r="BK12" s="10" t="n">
-        <v>33.52</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="13">
@@ -7805,24 +6466,24 @@
       <c r="AB13" s="10" t="inlineStr"/>
       <c r="AC13" s="10" t="inlineStr"/>
       <c r="AD13" s="11" t="n">
-        <v>46175.62569444445</v>
+        <v>46179.00208333333</v>
       </c>
       <c r="AE13" s="11" t="n">
-        <v>46175.82847222222</v>
+        <v>46179.05138888889</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>4516.97</v>
+        <v>4322.93</v>
       </c>
       <c r="AG13" s="10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>4530.94</v>
+        <v>4340.18</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>55.88</v>
+        <v>-69</v>
       </c>
       <c r="AJ13" s="10" t="inlineStr"/>
       <c r="AK13" s="10" t="inlineStr"/>
@@ -7830,7 +6491,7 @@
       <c r="AM13" s="10" t="inlineStr"/>
       <c r="AN13" s="10" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO13" s="10" t="inlineStr"/>
@@ -7852,1364 +6513,25 @@
       <c r="BE13" s="10" t="inlineStr"/>
       <c r="BF13" s="10" t="inlineStr"/>
       <c r="BG13" s="11" t="n">
-        <v>46174.30836805556</v>
+        <v>46179.17710648148</v>
       </c>
       <c r="BH13" s="10" t="n">
-        <v>4541.35</v>
+        <v>4315.54</v>
       </c>
       <c r="BI13" s="10" t="inlineStr">
         <is>
-          <t>[sl 4543.72]</t>
+          <t>PD Zone fill rou</t>
         </is>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>1896.95</v>
+        <v>252.03</v>
       </c>
       <c r="BK13" s="10" t="n">
-        <v>10.41</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="10" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr"/>
-      <c r="P14" s="10" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr"/>
-      <c r="R14" s="10" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr"/>
-      <c r="T14" s="10" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr"/>
-      <c r="V14" s="10" t="inlineStr"/>
-      <c r="W14" s="10" t="inlineStr"/>
-      <c r="X14" s="10" t="inlineStr"/>
-      <c r="Y14" s="10" t="inlineStr"/>
-      <c r="Z14" s="10" t="inlineStr"/>
-      <c r="AA14" s="10" t="inlineStr"/>
-      <c r="AB14" s="10" t="inlineStr"/>
-      <c r="AC14" s="10" t="inlineStr"/>
-      <c r="AD14" s="11" t="n">
-        <v>46175.72291666667</v>
-      </c>
-      <c r="AE14" s="11" t="n">
-        <v>46175.82430555556</v>
-      </c>
-      <c r="AF14" s="10" t="n">
-        <v>4521.52</v>
-      </c>
-      <c r="AG14" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH14" s="10" t="n">
-        <v>4526.71</v>
-      </c>
-      <c r="AI14" s="10" t="n">
-        <v>-20.76</v>
-      </c>
-      <c r="AJ14" s="10" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr"/>
-      <c r="AL14" s="10" t="inlineStr"/>
-      <c r="AM14" s="10" t="inlineStr"/>
-      <c r="AN14" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO14" s="10" t="inlineStr"/>
-      <c r="AP14" s="10" t="inlineStr"/>
-      <c r="AQ14" s="10" t="inlineStr"/>
-      <c r="AR14" s="10" t="inlineStr"/>
-      <c r="AS14" s="10" t="inlineStr"/>
-      <c r="AT14" s="10" t="inlineStr"/>
-      <c r="AU14" s="10" t="inlineStr"/>
-      <c r="AV14" s="10" t="inlineStr"/>
-      <c r="AW14" s="10" t="inlineStr"/>
-      <c r="AX14" s="10" t="inlineStr"/>
-      <c r="AY14" s="10" t="inlineStr"/>
-      <c r="AZ14" s="10" t="inlineStr"/>
-      <c r="BA14" s="10" t="inlineStr"/>
-      <c r="BB14" s="10" t="inlineStr"/>
-      <c r="BC14" s="10" t="inlineStr"/>
-      <c r="BD14" s="10" t="inlineStr"/>
-      <c r="BE14" s="10" t="inlineStr"/>
-      <c r="BF14" s="10" t="inlineStr"/>
-      <c r="BG14" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH14" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI14" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ14" s="10" t="n">
-        <v>3844.42</v>
-      </c>
-      <c r="BK14" s="10" t="n">
-        <v>73.70999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="10" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr"/>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
-      <c r="T15" s="10" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr"/>
-      <c r="V15" s="10" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr"/>
-      <c r="X15" s="10" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr"/>
-      <c r="Z15" s="10" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr"/>
-      <c r="AB15" s="10" t="inlineStr"/>
-      <c r="AC15" s="10" t="inlineStr"/>
-      <c r="AD15" s="11" t="n">
-        <v>46177.01944444444</v>
-      </c>
-      <c r="AE15" s="11" t="n">
-        <v>46177.14791666667</v>
-      </c>
-      <c r="AF15" s="10" t="n">
-        <v>4433.27</v>
-      </c>
-      <c r="AG15" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH15" s="10" t="n">
-        <v>4439.15</v>
-      </c>
-      <c r="AI15" s="10" t="n">
-        <v>-23.52</v>
-      </c>
-      <c r="AJ15" s="10" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr"/>
-      <c r="AL15" s="10" t="inlineStr"/>
-      <c r="AM15" s="10" t="inlineStr"/>
-      <c r="AN15" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO15" s="10" t="inlineStr"/>
-      <c r="AP15" s="10" t="inlineStr"/>
-      <c r="AQ15" s="10" t="inlineStr"/>
-      <c r="AR15" s="10" t="inlineStr"/>
-      <c r="AS15" s="10" t="inlineStr"/>
-      <c r="AT15" s="10" t="inlineStr"/>
-      <c r="AU15" s="10" t="inlineStr"/>
-      <c r="AV15" s="10" t="inlineStr"/>
-      <c r="AW15" s="10" t="inlineStr"/>
-      <c r="AX15" s="10" t="inlineStr"/>
-      <c r="AY15" s="10" t="inlineStr"/>
-      <c r="AZ15" s="10" t="inlineStr"/>
-      <c r="BA15" s="10" t="inlineStr"/>
-      <c r="BB15" s="10" t="inlineStr"/>
-      <c r="BC15" s="10" t="inlineStr"/>
-      <c r="BD15" s="10" t="inlineStr"/>
-      <c r="BE15" s="10" t="inlineStr"/>
-      <c r="BF15" s="10" t="inlineStr"/>
-      <c r="BG15" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH15" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI15" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="10" t="n">
-        <v>1977.42</v>
-      </c>
-      <c r="BK15" s="10" t="n">
-        <v>13.85</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr"/>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="10" t="inlineStr"/>
-      <c r="O16" s="10" t="inlineStr"/>
-      <c r="P16" s="10" t="inlineStr"/>
-      <c r="Q16" s="10" t="inlineStr"/>
-      <c r="R16" s="10" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr"/>
-      <c r="T16" s="10" t="inlineStr"/>
-      <c r="U16" s="10" t="inlineStr"/>
-      <c r="V16" s="10" t="inlineStr"/>
-      <c r="W16" s="10" t="inlineStr"/>
-      <c r="X16" s="10" t="inlineStr"/>
-      <c r="Y16" s="10" t="inlineStr"/>
-      <c r="Z16" s="10" t="inlineStr"/>
-      <c r="AA16" s="10" t="inlineStr"/>
-      <c r="AB16" s="10" t="inlineStr"/>
-      <c r="AC16" s="10" t="inlineStr"/>
-      <c r="AD16" s="11" t="n">
-        <v>46177.33402777778</v>
-      </c>
-      <c r="AE16" s="11" t="n">
-        <v>46177.34166666667</v>
-      </c>
-      <c r="AF16" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG16" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH16" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI16" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ16" s="10" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr"/>
-      <c r="AL16" s="10" t="inlineStr"/>
-      <c r="AM16" s="10" t="inlineStr"/>
-      <c r="AN16" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO16" s="10" t="inlineStr"/>
-      <c r="AP16" s="10" t="inlineStr"/>
-      <c r="AQ16" s="10" t="inlineStr"/>
-      <c r="AR16" s="10" t="inlineStr"/>
-      <c r="AS16" s="10" t="inlineStr"/>
-      <c r="AT16" s="10" t="inlineStr"/>
-      <c r="AU16" s="10" t="inlineStr"/>
-      <c r="AV16" s="10" t="inlineStr"/>
-      <c r="AW16" s="10" t="inlineStr"/>
-      <c r="AX16" s="10" t="inlineStr"/>
-      <c r="AY16" s="10" t="inlineStr"/>
-      <c r="AZ16" s="10" t="inlineStr"/>
-      <c r="BA16" s="10" t="inlineStr"/>
-      <c r="BB16" s="10" t="inlineStr"/>
-      <c r="BC16" s="10" t="inlineStr"/>
-      <c r="BD16" s="10" t="inlineStr"/>
-      <c r="BE16" s="10" t="inlineStr"/>
-      <c r="BF16" s="10" t="inlineStr"/>
-      <c r="BG16" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH16" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI16" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ16" s="10" t="n">
-        <v>4356.95</v>
-      </c>
-      <c r="BK16" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
-      <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="10" t="inlineStr"/>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr"/>
-      <c r="P17" s="10" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr"/>
-      <c r="R17" s="10" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr"/>
-      <c r="T17" s="10" t="inlineStr"/>
-      <c r="U17" s="10" t="inlineStr"/>
-      <c r="V17" s="10" t="inlineStr"/>
-      <c r="W17" s="10" t="inlineStr"/>
-      <c r="X17" s="10" t="inlineStr"/>
-      <c r="Y17" s="10" t="inlineStr"/>
-      <c r="Z17" s="10" t="inlineStr"/>
-      <c r="AA17" s="10" t="inlineStr"/>
-      <c r="AB17" s="10" t="inlineStr"/>
-      <c r="AC17" s="10" t="inlineStr"/>
-      <c r="AD17" s="11" t="n">
-        <v>46177.34583333333</v>
-      </c>
-      <c r="AE17" s="11" t="n">
-        <v>46177.34722222222</v>
-      </c>
-      <c r="AF17" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG17" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH17" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI17" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ17" s="10" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr"/>
-      <c r="AL17" s="10" t="inlineStr"/>
-      <c r="AM17" s="10" t="inlineStr"/>
-      <c r="AN17" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO17" s="10" t="inlineStr"/>
-      <c r="AP17" s="10" t="inlineStr"/>
-      <c r="AQ17" s="10" t="inlineStr"/>
-      <c r="AR17" s="10" t="inlineStr"/>
-      <c r="AS17" s="10" t="inlineStr"/>
-      <c r="AT17" s="10" t="inlineStr"/>
-      <c r="AU17" s="10" t="inlineStr"/>
-      <c r="AV17" s="10" t="inlineStr"/>
-      <c r="AW17" s="10" t="inlineStr"/>
-      <c r="AX17" s="10" t="inlineStr"/>
-      <c r="AY17" s="10" t="inlineStr"/>
-      <c r="AZ17" s="10" t="inlineStr"/>
-      <c r="BA17" s="10" t="inlineStr"/>
-      <c r="BB17" s="10" t="inlineStr"/>
-      <c r="BC17" s="10" t="inlineStr"/>
-      <c r="BD17" s="10" t="inlineStr"/>
-      <c r="BE17" s="10" t="inlineStr"/>
-      <c r="BF17" s="10" t="inlineStr"/>
-      <c r="BG17" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH17" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI17" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ17" s="10" t="n">
-        <v>4373.95</v>
-      </c>
-      <c r="BK17" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr"/>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr"/>
-      <c r="P18" s="10" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr"/>
-      <c r="R18" s="10" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr"/>
-      <c r="T18" s="10" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr"/>
-      <c r="V18" s="10" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr"/>
-      <c r="X18" s="10" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr"/>
-      <c r="Z18" s="10" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr"/>
-      <c r="AB18" s="10" t="inlineStr"/>
-      <c r="AC18" s="10" t="inlineStr"/>
-      <c r="AD18" s="11" t="n">
-        <v>46177.35347222222</v>
-      </c>
-      <c r="AE18" s="11" t="n">
-        <v>46177.35416666666</v>
-      </c>
-      <c r="AF18" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG18" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH18" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI18" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ18" s="10" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr"/>
-      <c r="AL18" s="10" t="inlineStr"/>
-      <c r="AM18" s="10" t="inlineStr"/>
-      <c r="AN18" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO18" s="10" t="inlineStr"/>
-      <c r="AP18" s="10" t="inlineStr"/>
-      <c r="AQ18" s="10" t="inlineStr"/>
-      <c r="AR18" s="10" t="inlineStr"/>
-      <c r="AS18" s="10" t="inlineStr"/>
-      <c r="AT18" s="10" t="inlineStr"/>
-      <c r="AU18" s="10" t="inlineStr"/>
-      <c r="AV18" s="10" t="inlineStr"/>
-      <c r="AW18" s="10" t="inlineStr"/>
-      <c r="AX18" s="10" t="inlineStr"/>
-      <c r="AY18" s="10" t="inlineStr"/>
-      <c r="AZ18" s="10" t="inlineStr"/>
-      <c r="BA18" s="10" t="inlineStr"/>
-      <c r="BB18" s="10" t="inlineStr"/>
-      <c r="BC18" s="10" t="inlineStr"/>
-      <c r="BD18" s="10" t="inlineStr"/>
-      <c r="BE18" s="10" t="inlineStr"/>
-      <c r="BF18" s="10" t="inlineStr"/>
-      <c r="BG18" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH18" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI18" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ18" s="10" t="n">
-        <v>4384.95</v>
-      </c>
-      <c r="BK18" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="10" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr"/>
-      <c r="P19" s="10" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr"/>
-      <c r="R19" s="10" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr"/>
-      <c r="T19" s="10" t="inlineStr"/>
-      <c r="U19" s="10" t="inlineStr"/>
-      <c r="V19" s="10" t="inlineStr"/>
-      <c r="W19" s="10" t="inlineStr"/>
-      <c r="X19" s="10" t="inlineStr"/>
-      <c r="Y19" s="10" t="inlineStr"/>
-      <c r="Z19" s="10" t="inlineStr"/>
-      <c r="AA19" s="10" t="inlineStr"/>
-      <c r="AB19" s="10" t="inlineStr"/>
-      <c r="AC19" s="10" t="inlineStr"/>
-      <c r="AD19" s="11" t="n">
-        <v>46177.3625</v>
-      </c>
-      <c r="AE19" s="11" t="n">
-        <v>46177.36597222222</v>
-      </c>
-      <c r="AF19" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG19" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH19" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI19" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ19" s="10" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr"/>
-      <c r="AL19" s="10" t="inlineStr"/>
-      <c r="AM19" s="10" t="inlineStr"/>
-      <c r="AN19" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO19" s="10" t="inlineStr"/>
-      <c r="AP19" s="10" t="inlineStr"/>
-      <c r="AQ19" s="10" t="inlineStr"/>
-      <c r="AR19" s="10" t="inlineStr"/>
-      <c r="AS19" s="10" t="inlineStr"/>
-      <c r="AT19" s="10" t="inlineStr"/>
-      <c r="AU19" s="10" t="inlineStr"/>
-      <c r="AV19" s="10" t="inlineStr"/>
-      <c r="AW19" s="10" t="inlineStr"/>
-      <c r="AX19" s="10" t="inlineStr"/>
-      <c r="AY19" s="10" t="inlineStr"/>
-      <c r="AZ19" s="10" t="inlineStr"/>
-      <c r="BA19" s="10" t="inlineStr"/>
-      <c r="BB19" s="10" t="inlineStr"/>
-      <c r="BC19" s="10" t="inlineStr"/>
-      <c r="BD19" s="10" t="inlineStr"/>
-      <c r="BE19" s="10" t="inlineStr"/>
-      <c r="BF19" s="10" t="inlineStr"/>
-      <c r="BG19" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH19" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI19" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ19" s="10" t="n">
-        <v>4397.95</v>
-      </c>
-      <c r="BK19" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr"/>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
-      <c r="O20" s="10" t="inlineStr"/>
-      <c r="P20" s="10" t="inlineStr"/>
-      <c r="Q20" s="10" t="inlineStr"/>
-      <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr"/>
-      <c r="T20" s="10" t="inlineStr"/>
-      <c r="U20" s="10" t="inlineStr"/>
-      <c r="V20" s="10" t="inlineStr"/>
-      <c r="W20" s="10" t="inlineStr"/>
-      <c r="X20" s="10" t="inlineStr"/>
-      <c r="Y20" s="10" t="inlineStr"/>
-      <c r="Z20" s="10" t="inlineStr"/>
-      <c r="AA20" s="10" t="inlineStr"/>
-      <c r="AB20" s="10" t="inlineStr"/>
-      <c r="AC20" s="10" t="inlineStr"/>
-      <c r="AD20" s="11" t="n">
-        <v>46177.37152777778</v>
-      </c>
-      <c r="AE20" s="11" t="n">
-        <v>46177.37222222222</v>
-      </c>
-      <c r="AF20" s="10" t="n">
-        <v>4465.22</v>
-      </c>
-      <c r="AG20" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AH20" s="10" t="n">
-        <v>4451.86</v>
-      </c>
-      <c r="AI20" s="10" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AJ20" s="10" t="inlineStr"/>
-      <c r="AK20" s="10" t="inlineStr"/>
-      <c r="AL20" s="10" t="inlineStr"/>
-      <c r="AM20" s="10" t="inlineStr"/>
-      <c r="AN20" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO20" s="10" t="inlineStr"/>
-      <c r="AP20" s="10" t="inlineStr"/>
-      <c r="AQ20" s="10" t="inlineStr"/>
-      <c r="AR20" s="10" t="inlineStr"/>
-      <c r="AS20" s="10" t="inlineStr"/>
-      <c r="AT20" s="10" t="inlineStr"/>
-      <c r="AU20" s="10" t="inlineStr"/>
-      <c r="AV20" s="10" t="inlineStr"/>
-      <c r="AW20" s="10" t="inlineStr"/>
-      <c r="AX20" s="10" t="inlineStr"/>
-      <c r="AY20" s="10" t="inlineStr"/>
-      <c r="AZ20" s="10" t="inlineStr"/>
-      <c r="BA20" s="10" t="inlineStr"/>
-      <c r="BB20" s="10" t="inlineStr"/>
-      <c r="BC20" s="10" t="inlineStr"/>
-      <c r="BD20" s="10" t="inlineStr"/>
-      <c r="BE20" s="10" t="inlineStr"/>
-      <c r="BF20" s="10" t="inlineStr"/>
-      <c r="BG20" s="11" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="BH20" s="10" t="n">
-        <v>4541.35</v>
-      </c>
-      <c r="BI20" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4543.72]</t>
-        </is>
-      </c>
-      <c r="BJ20" s="10" t="n">
-        <v>4410.95</v>
-      </c>
-      <c r="BK20" s="10" t="n">
-        <v>89.48999999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr"/>
-      <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="10" t="inlineStr"/>
-      <c r="Q21" s="10" t="inlineStr"/>
-      <c r="R21" s="10" t="inlineStr"/>
-      <c r="S21" s="10" t="inlineStr"/>
-      <c r="T21" s="10" t="inlineStr"/>
-      <c r="U21" s="10" t="inlineStr"/>
-      <c r="V21" s="10" t="inlineStr"/>
-      <c r="W21" s="10" t="inlineStr"/>
-      <c r="X21" s="10" t="inlineStr"/>
-      <c r="Y21" s="10" t="inlineStr"/>
-      <c r="Z21" s="10" t="inlineStr"/>
-      <c r="AA21" s="10" t="inlineStr"/>
-      <c r="AB21" s="10" t="inlineStr"/>
-      <c r="AC21" s="10" t="inlineStr"/>
-      <c r="AD21" s="11" t="n">
-        <v>46177.66736111111</v>
-      </c>
-      <c r="AE21" s="11" t="n">
-        <v>46177.7</v>
-      </c>
-      <c r="AF21" s="10" t="n">
-        <v>4470.76</v>
-      </c>
-      <c r="AG21" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH21" s="10" t="n">
-        <v>4463.7</v>
-      </c>
-      <c r="AI21" s="10" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="AJ21" s="10" t="inlineStr"/>
-      <c r="AK21" s="10" t="inlineStr"/>
-      <c r="AL21" s="10" t="inlineStr"/>
-      <c r="AM21" s="10" t="inlineStr"/>
-      <c r="AN21" s="10" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="AO21" s="10" t="inlineStr"/>
-      <c r="AP21" s="10" t="inlineStr"/>
-      <c r="AQ21" s="10" t="inlineStr"/>
-      <c r="AR21" s="10" t="inlineStr"/>
-      <c r="AS21" s="10" t="inlineStr"/>
-      <c r="AT21" s="10" t="inlineStr"/>
-      <c r="AU21" s="10" t="inlineStr"/>
-      <c r="AV21" s="10" t="inlineStr"/>
-      <c r="AW21" s="10" t="inlineStr"/>
-      <c r="AX21" s="10" t="inlineStr"/>
-      <c r="AY21" s="10" t="inlineStr"/>
-      <c r="AZ21" s="10" t="inlineStr"/>
-      <c r="BA21" s="10" t="inlineStr"/>
-      <c r="BB21" s="10" t="inlineStr"/>
-      <c r="BC21" s="10" t="inlineStr"/>
-      <c r="BD21" s="10" t="inlineStr"/>
-      <c r="BE21" s="10" t="inlineStr"/>
-      <c r="BF21" s="10" t="inlineStr"/>
-      <c r="BG21" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH21" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI21" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="10" t="n">
-        <v>1044.42</v>
-      </c>
-      <c r="BK21" s="10" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr"/>
-      <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="10" t="inlineStr"/>
-      <c r="P22" s="10" t="inlineStr"/>
-      <c r="Q22" s="10" t="inlineStr"/>
-      <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
-      <c r="T22" s="10" t="inlineStr"/>
-      <c r="U22" s="10" t="inlineStr"/>
-      <c r="V22" s="10" t="inlineStr"/>
-      <c r="W22" s="10" t="inlineStr"/>
-      <c r="X22" s="10" t="inlineStr"/>
-      <c r="Y22" s="10" t="inlineStr"/>
-      <c r="Z22" s="10" t="inlineStr"/>
-      <c r="AA22" s="10" t="inlineStr"/>
-      <c r="AB22" s="10" t="inlineStr"/>
-      <c r="AC22" s="10" t="inlineStr"/>
-      <c r="AD22" s="11" t="n">
-        <v>46178.33402777778</v>
-      </c>
-      <c r="AE22" s="11" t="n">
-        <v>46178.35138888889</v>
-      </c>
-      <c r="AF22" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG22" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH22" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI22" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ22" s="10" t="inlineStr"/>
-      <c r="AK22" s="10" t="inlineStr"/>
-      <c r="AL22" s="10" t="inlineStr"/>
-      <c r="AM22" s="10" t="inlineStr"/>
-      <c r="AN22" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO22" s="10" t="inlineStr"/>
-      <c r="AP22" s="10" t="inlineStr"/>
-      <c r="AQ22" s="10" t="inlineStr"/>
-      <c r="AR22" s="10" t="inlineStr"/>
-      <c r="AS22" s="10" t="inlineStr"/>
-      <c r="AT22" s="10" t="inlineStr"/>
-      <c r="AU22" s="10" t="inlineStr"/>
-      <c r="AV22" s="10" t="inlineStr"/>
-      <c r="AW22" s="10" t="inlineStr"/>
-      <c r="AX22" s="10" t="inlineStr"/>
-      <c r="AY22" s="10" t="inlineStr"/>
-      <c r="AZ22" s="10" t="inlineStr"/>
-      <c r="BA22" s="10" t="inlineStr"/>
-      <c r="BB22" s="10" t="inlineStr"/>
-      <c r="BC22" s="10" t="inlineStr"/>
-      <c r="BD22" s="10" t="inlineStr"/>
-      <c r="BE22" s="10" t="inlineStr"/>
-      <c r="BF22" s="10" t="inlineStr"/>
-      <c r="BG22" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH22" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI22" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="10" t="n">
-        <v>84.42</v>
-      </c>
-      <c r="BK22" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr"/>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="10" t="inlineStr"/>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="10" t="inlineStr"/>
-      <c r="Q23" s="10" t="inlineStr"/>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
-      <c r="T23" s="10" t="inlineStr"/>
-      <c r="U23" s="10" t="inlineStr"/>
-      <c r="V23" s="10" t="inlineStr"/>
-      <c r="W23" s="10" t="inlineStr"/>
-      <c r="X23" s="10" t="inlineStr"/>
-      <c r="Y23" s="10" t="inlineStr"/>
-      <c r="Z23" s="10" t="inlineStr"/>
-      <c r="AA23" s="10" t="inlineStr"/>
-      <c r="AB23" s="10" t="inlineStr"/>
-      <c r="AC23" s="10" t="inlineStr"/>
-      <c r="AD23" s="11" t="n">
-        <v>46178.35555555556</v>
-      </c>
-      <c r="AE23" s="11" t="n">
-        <v>46178.36041666667</v>
-      </c>
-      <c r="AF23" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG23" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH23" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI23" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ23" s="10" t="inlineStr"/>
-      <c r="AK23" s="10" t="inlineStr"/>
-      <c r="AL23" s="10" t="inlineStr"/>
-      <c r="AM23" s="10" t="inlineStr"/>
-      <c r="AN23" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO23" s="10" t="inlineStr"/>
-      <c r="AP23" s="10" t="inlineStr"/>
-      <c r="AQ23" s="10" t="inlineStr"/>
-      <c r="AR23" s="10" t="inlineStr"/>
-      <c r="AS23" s="10" t="inlineStr"/>
-      <c r="AT23" s="10" t="inlineStr"/>
-      <c r="AU23" s="10" t="inlineStr"/>
-      <c r="AV23" s="10" t="inlineStr"/>
-      <c r="AW23" s="10" t="inlineStr"/>
-      <c r="AX23" s="10" t="inlineStr"/>
-      <c r="AY23" s="10" t="inlineStr"/>
-      <c r="AZ23" s="10" t="inlineStr"/>
-      <c r="BA23" s="10" t="inlineStr"/>
-      <c r="BB23" s="10" t="inlineStr"/>
-      <c r="BC23" s="10" t="inlineStr"/>
-      <c r="BD23" s="10" t="inlineStr"/>
-      <c r="BE23" s="10" t="inlineStr"/>
-      <c r="BF23" s="10" t="inlineStr"/>
-      <c r="BG23" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH23" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI23" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="10" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="BK23" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="10" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr"/>
-      <c r="O24" s="10" t="inlineStr"/>
-      <c r="P24" s="10" t="inlineStr"/>
-      <c r="Q24" s="10" t="inlineStr"/>
-      <c r="R24" s="10" t="inlineStr"/>
-      <c r="S24" s="10" t="inlineStr"/>
-      <c r="T24" s="10" t="inlineStr"/>
-      <c r="U24" s="10" t="inlineStr"/>
-      <c r="V24" s="10" t="inlineStr"/>
-      <c r="W24" s="10" t="inlineStr"/>
-      <c r="X24" s="10" t="inlineStr"/>
-      <c r="Y24" s="10" t="inlineStr"/>
-      <c r="Z24" s="10" t="inlineStr"/>
-      <c r="AA24" s="10" t="inlineStr"/>
-      <c r="AB24" s="10" t="inlineStr"/>
-      <c r="AC24" s="10" t="inlineStr"/>
-      <c r="AD24" s="11" t="n">
-        <v>46178.36875</v>
-      </c>
-      <c r="AE24" s="11" t="n">
-        <v>46178.36944444444</v>
-      </c>
-      <c r="AF24" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG24" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH24" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI24" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ24" s="10" t="inlineStr"/>
-      <c r="AK24" s="10" t="inlineStr"/>
-      <c r="AL24" s="10" t="inlineStr"/>
-      <c r="AM24" s="10" t="inlineStr"/>
-      <c r="AN24" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO24" s="10" t="inlineStr"/>
-      <c r="AP24" s="10" t="inlineStr"/>
-      <c r="AQ24" s="10" t="inlineStr"/>
-      <c r="AR24" s="10" t="inlineStr"/>
-      <c r="AS24" s="10" t="inlineStr"/>
-      <c r="AT24" s="10" t="inlineStr"/>
-      <c r="AU24" s="10" t="inlineStr"/>
-      <c r="AV24" s="10" t="inlineStr"/>
-      <c r="AW24" s="10" t="inlineStr"/>
-      <c r="AX24" s="10" t="inlineStr"/>
-      <c r="AY24" s="10" t="inlineStr"/>
-      <c r="AZ24" s="10" t="inlineStr"/>
-      <c r="BA24" s="10" t="inlineStr"/>
-      <c r="BB24" s="10" t="inlineStr"/>
-      <c r="BC24" s="10" t="inlineStr"/>
-      <c r="BD24" s="10" t="inlineStr"/>
-      <c r="BE24" s="10" t="inlineStr"/>
-      <c r="BF24" s="10" t="inlineStr"/>
-      <c r="BG24" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH24" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI24" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ24" s="10" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="BK24" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="10" t="inlineStr"/>
-      <c r="P25" s="10" t="inlineStr"/>
-      <c r="Q25" s="10" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
-      <c r="T25" s="10" t="inlineStr"/>
-      <c r="U25" s="10" t="inlineStr"/>
-      <c r="V25" s="10" t="inlineStr"/>
-      <c r="W25" s="10" t="inlineStr"/>
-      <c r="X25" s="10" t="inlineStr"/>
-      <c r="Y25" s="10" t="inlineStr"/>
-      <c r="Z25" s="10" t="inlineStr"/>
-      <c r="AA25" s="10" t="inlineStr"/>
-      <c r="AB25" s="10" t="inlineStr"/>
-      <c r="AC25" s="10" t="inlineStr"/>
-      <c r="AD25" s="11" t="n">
-        <v>46178.37361111111</v>
-      </c>
-      <c r="AE25" s="11" t="n">
-        <v>46178.37430555555</v>
-      </c>
-      <c r="AF25" s="10" t="n">
-        <v>4450.29</v>
-      </c>
-      <c r="AG25" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH25" s="10" t="n">
-        <v>4464.44</v>
-      </c>
-      <c r="AI25" s="10" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="AJ25" s="10" t="inlineStr"/>
-      <c r="AK25" s="10" t="inlineStr"/>
-      <c r="AL25" s="10" t="inlineStr"/>
-      <c r="AM25" s="10" t="inlineStr"/>
-      <c r="AN25" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO25" s="10" t="inlineStr"/>
-      <c r="AP25" s="10" t="inlineStr"/>
-      <c r="AQ25" s="10" t="inlineStr"/>
-      <c r="AR25" s="10" t="inlineStr"/>
-      <c r="AS25" s="10" t="inlineStr"/>
-      <c r="AT25" s="10" t="inlineStr"/>
-      <c r="AU25" s="10" t="inlineStr"/>
-      <c r="AV25" s="10" t="inlineStr"/>
-      <c r="AW25" s="10" t="inlineStr"/>
-      <c r="AX25" s="10" t="inlineStr"/>
-      <c r="AY25" s="10" t="inlineStr"/>
-      <c r="AZ25" s="10" t="inlineStr"/>
-      <c r="BA25" s="10" t="inlineStr"/>
-      <c r="BB25" s="10" t="inlineStr"/>
-      <c r="BC25" s="10" t="inlineStr"/>
-      <c r="BD25" s="10" t="inlineStr"/>
-      <c r="BE25" s="10" t="inlineStr"/>
-      <c r="BF25" s="10" t="inlineStr"/>
-      <c r="BG25" s="11" t="n">
-        <v>46178.39265046296</v>
-      </c>
-      <c r="BH25" s="10" t="n">
-        <v>4453</v>
-      </c>
-      <c r="BI25" s="10" t="inlineStr">
-        <is>
-          <t>[sl 4450.29]</t>
-        </is>
-      </c>
-      <c r="BJ25" s="10" t="n">
-        <v>27.42</v>
-      </c>
-      <c r="BK25" s="10" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>TIME_TOO_FAR+ENTRY_TOO_FAR</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr"/>
-      <c r="L26" s="10" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="10" t="inlineStr"/>
-      <c r="P26" s="10" t="inlineStr"/>
-      <c r="Q26" s="10" t="inlineStr"/>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
-      <c r="T26" s="10" t="inlineStr"/>
-      <c r="U26" s="10" t="inlineStr"/>
-      <c r="V26" s="10" t="inlineStr"/>
-      <c r="W26" s="10" t="inlineStr"/>
-      <c r="X26" s="10" t="inlineStr"/>
-      <c r="Y26" s="10" t="inlineStr"/>
-      <c r="Z26" s="10" t="inlineStr"/>
-      <c r="AA26" s="10" t="inlineStr"/>
-      <c r="AB26" s="10" t="inlineStr"/>
-      <c r="AC26" s="10" t="inlineStr"/>
-      <c r="AD26" s="11" t="n">
-        <v>46179.00208333333</v>
-      </c>
-      <c r="AE26" s="11" t="n">
-        <v>46179.05138888889</v>
-      </c>
-      <c r="AF26" s="10" t="n">
-        <v>4322.93</v>
-      </c>
-      <c r="AG26" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH26" s="10" t="n">
-        <v>4340.18</v>
-      </c>
-      <c r="AI26" s="10" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AJ26" s="10" t="inlineStr"/>
-      <c r="AK26" s="10" t="inlineStr"/>
-      <c r="AL26" s="10" t="inlineStr"/>
-      <c r="AM26" s="10" t="inlineStr"/>
-      <c r="AN26" s="10" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO26" s="10" t="inlineStr"/>
-      <c r="AP26" s="10" t="inlineStr"/>
-      <c r="AQ26" s="10" t="inlineStr"/>
-      <c r="AR26" s="10" t="inlineStr"/>
-      <c r="AS26" s="10" t="inlineStr"/>
-      <c r="AT26" s="10" t="inlineStr"/>
-      <c r="AU26" s="10" t="inlineStr"/>
-      <c r="AV26" s="10" t="inlineStr"/>
-      <c r="AW26" s="10" t="inlineStr"/>
-      <c r="AX26" s="10" t="inlineStr"/>
-      <c r="AY26" s="10" t="inlineStr"/>
-      <c r="AZ26" s="10" t="inlineStr"/>
-      <c r="BA26" s="10" t="inlineStr"/>
-      <c r="BB26" s="10" t="inlineStr"/>
-      <c r="BC26" s="10" t="inlineStr"/>
-      <c r="BD26" s="10" t="inlineStr"/>
-      <c r="BE26" s="10" t="inlineStr"/>
-      <c r="BF26" s="10" t="inlineStr"/>
-      <c r="BG26" s="11" t="n">
-        <v>46179.17710648148</v>
-      </c>
-      <c r="BH26" s="10" t="n">
-        <v>4315.54</v>
-      </c>
-      <c r="BI26" s="10" t="inlineStr">
-        <is>
-          <t>PD Zone fill rou</t>
-        </is>
-      </c>
-      <c r="BJ26" s="10" t="n">
-        <v>252.03</v>
-      </c>
-      <c r="BK26" s="10" t="n">
         <v>24.64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK26"/>
+  <autoFilter ref="A1:BK13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9682,7 +7004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9893,10 +7215,10 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-369.2</v>
+        <v>-156.2</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>46174.62847222222</v>
@@ -9922,16 +7244,16 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-380.28</v>
+        <v>-111.92</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>46171.04236111111</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>46177.37152777778</v>
+        <v>46177.33402777778</v>
       </c>
     </row>
     <row r="9">
@@ -9976,20 +7298,20 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>19.48</v>
+        <v>-13.76</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>46171.04791666667</v>
+        <v>46177.01944444444</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>46171.04791666667</v>
+        <v>46177.01944444444</v>
       </c>
     </row>
     <row r="11">
@@ -10150,10 +7472,10 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-274.24</v>
+        <v>4.08</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>46171.04236111111</v>
@@ -10179,16 +7501,16 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>-226.4</v>
+        <v>-56.6</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>46178.33402777778</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>46178.37361111111</v>
+        <v>46178.33402777778</v>
       </c>
     </row>
     <row r="18">
@@ -10336,182 +7658,8 @@
         <v>46174.30836805556</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>live_s14_family</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>-22.01</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>46170.43255787037</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>46179.17710648148</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>live_s14_family</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>46170.84453703704</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>46170.84453703704</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>-159.68</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>46171.04236111111</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>46177.37152777778</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>-340.96</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>46174.62847222222</v>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>46179.00208333333</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>mismatch_s14_family</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>-95.95999999999999</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>46174.30836805556</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>s14_family_mismatch</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>-95.95999999999999</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>46174.30836805556</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>46174.30836805556</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:G22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>